--- a/input_processing/clean_excel_files_PL/reg_employmentSelection.xlsx
+++ b/input_processing/clean_excel_files_PL/reg_employmentSelection.xlsx
@@ -100,22 +100,22 @@
     <t>Dag_sq</t>
   </si>
   <si>
-    <t>Deh_c3_Medium</t>
+    <t>Deh_c4_Medium</t>
   </si>
   <si>
-    <t>Deh_c3_Low</t>
+    <t>Deh_c4_Low</t>
   </si>
   <si>
-    <t>Deh_c3_Medium_Dag</t>
+    <t>Deh_c4_Medium_Dag</t>
   </si>
   <si>
-    <t>Deh_c3_Low_Dag</t>
+    <t>Deh_c4_Low_Dag</t>
   </si>
   <si>
-    <t>Dcpst_Partnered</t>
+    <t>Dcpst_Partnered_L1</t>
   </si>
   <si>
-    <t>D_Children</t>
+    <t>D_Children_L1</t>
   </si>
   <si>
     <t>Dhe_Fair</t>
@@ -413,70 +413,70 @@
         <v>23</v>
       </c>
       <c r="B2" s="1">
-        <v>-1.6743364063069137</v>
+        <v>-1.6231124915084674</v>
       </c>
       <c r="C2" s="1">
-        <v>0.0011719773924760506</v>
+        <v>0.0012012871604455617</v>
       </c>
       <c r="D2" s="1">
-        <v>0.00010156422457016809</v>
+        <v>0.00010055986977541468</v>
       </c>
       <c r="E2" s="1">
-        <v>4.944148653441584e-05</v>
+        <v>4.7147328240750973e-05</v>
       </c>
       <c r="F2" s="1">
-        <v>-4.9775605363917165e-07</v>
+        <v>-4.7136717541511262e-07</v>
       </c>
       <c r="G2" s="1">
-        <v>-4.6493118817943686e-06</v>
+        <v>-7.2674772420120326e-06</v>
       </c>
       <c r="H2" s="1">
-        <v>-0.00033245011990130376</v>
+        <v>-0.00019710272217600254</v>
       </c>
       <c r="I2" s="1">
-        <v>-4.5741924318749613e-07</v>
+        <v>-4.0603036032904649e-07</v>
       </c>
       <c r="J2" s="1">
-        <v>5.5885823381056244e-06</v>
+        <v>3.0874294977324786e-06</v>
       </c>
       <c r="K2" s="1">
-        <v>5.6839424853557922e-05</v>
+        <v>5.6204633581223347e-05</v>
       </c>
       <c r="L2" s="1">
-        <v>0.0001089453119628335</v>
+        <v>-0.00029153125164678022</v>
       </c>
       <c r="M2" s="1">
-        <v>-3.7360467119149066e-06</v>
+        <v>-1.98162673167e-06</v>
       </c>
       <c r="N2" s="1">
-        <v>-3.6456001712306727e-06</v>
+        <v>-1.6647596124567737e-06</v>
       </c>
       <c r="O2" s="1">
-        <v>4.8222781277397261e-06</v>
+        <v>6.5996842673235034e-06</v>
       </c>
       <c r="P2" s="1">
-        <v>-1.5095211150809926e-05</v>
+        <v>-1.380496130332998e-05</v>
       </c>
       <c r="Q2" s="1">
-        <v>7.242118320708494e-06</v>
+        <v>7.5403151689304017e-06</v>
       </c>
       <c r="R2" s="1">
-        <v>4.5044516540850116e-06</v>
+        <v>4.5727824596310993e-06</v>
       </c>
       <c r="S2" s="1">
-        <v>2.707181254504445e-06</v>
+        <v>2.1700089071435109e-06</v>
       </c>
       <c r="T2" s="1">
-        <v>-1.3953452314826435e-06</v>
+        <v>-1.8420825670243646e-06</v>
       </c>
       <c r="U2" s="1">
-        <v>8.1934567489098656e-06</v>
+        <v>6.694968335608059e-06</v>
       </c>
       <c r="V2" s="1">
-        <v>1.2209756840042442e-06</v>
+        <v>1.1828212784639151e-06</v>
       </c>
       <c r="W2" s="1">
-        <v>-0.0012330088038144972</v>
+        <v>-0.0011886594020446141</v>
       </c>
     </row>
     <row r="3">
@@ -484,70 +484,70 @@
         <v>24</v>
       </c>
       <c r="B3" s="1">
-        <v>-2.5230855199301025</v>
+        <v>-2.5241881443022347</v>
       </c>
       <c r="C3" s="1">
-        <v>0.00010156422457016809</v>
+        <v>0.00010055986977541468</v>
       </c>
       <c r="D3" s="1">
-        <v>0.0001763774649375578</v>
+        <v>0.00017633814686008353</v>
       </c>
       <c r="E3" s="1">
-        <v>6.283204609035375e-06</v>
+        <v>6.6162541748706538e-06</v>
       </c>
       <c r="F3" s="1">
-        <v>-6.059687708271965e-08</v>
+        <v>-6.4502717203972043e-08</v>
       </c>
       <c r="G3" s="1">
-        <v>-1.4422878180065715e-05</v>
+        <v>-1.4623243001438374e-05</v>
       </c>
       <c r="H3" s="1">
-        <v>4.0925395220297294e-06</v>
+        <v>-8.1657581063267117e-06</v>
       </c>
       <c r="I3" s="1">
-        <v>-4.1818378833333307e-07</v>
+        <v>-4.1178116483219376e-07</v>
       </c>
       <c r="J3" s="1">
-        <v>-1.1083448472931954e-06</v>
+        <v>-8.7204433200683424e-07</v>
       </c>
       <c r="K3" s="1">
-        <v>4.0292572052781461e-07</v>
+        <v>-1.2268743077588019e-06</v>
       </c>
       <c r="L3" s="1">
-        <v>-2.9545973143004297e-06</v>
+        <v>1.7252231471935606e-05</v>
       </c>
       <c r="M3" s="1">
-        <v>4.6314788066063884e-06</v>
+        <v>4.4308580176230121e-06</v>
       </c>
       <c r="N3" s="1">
-        <v>8.3808631080248326e-06</v>
+        <v>8.2574196957376216e-06</v>
       </c>
       <c r="O3" s="1">
-        <v>1.582525504493674e-05</v>
+        <v>1.5817695030519264e-05</v>
       </c>
       <c r="P3" s="1">
-        <v>1.6883321629788606e-05</v>
+        <v>1.6901720471742195e-05</v>
       </c>
       <c r="Q3" s="1">
-        <v>2.1064515962938622e-06</v>
+        <v>2.0792681766556301e-06</v>
       </c>
       <c r="R3" s="1">
-        <v>3.8913871761079176e-08</v>
+        <v>3.4556389647186684e-08</v>
       </c>
       <c r="S3" s="1">
-        <v>-1.1178748205787355e-07</v>
+        <v>-4.9756284019680556e-08</v>
       </c>
       <c r="T3" s="1">
-        <v>5.6196150282453145e-06</v>
+        <v>5.6457649163608449e-06</v>
       </c>
       <c r="U3" s="1">
-        <v>5.3491343403439333e-06</v>
+        <v>5.5367422780267181e-06</v>
       </c>
       <c r="V3" s="1">
-        <v>3.6579077506735717e-07</v>
+        <v>2.9574604515451896e-07</v>
       </c>
       <c r="W3" s="1">
-        <v>-0.00020973896094931071</v>
+        <v>-0.00021497861891994373</v>
       </c>
     </row>
     <row r="4">
@@ -555,70 +555,70 @@
         <v>25</v>
       </c>
       <c r="B4" s="1">
-        <v>0.16183002633247709</v>
+        <v>0.15725144978176656</v>
       </c>
       <c r="C4" s="1">
-        <v>4.944148653441584e-05</v>
+        <v>4.7147328240750973e-05</v>
       </c>
       <c r="D4" s="1">
-        <v>6.283204609035375e-06</v>
+        <v>6.6162541748706538e-06</v>
       </c>
       <c r="E4" s="1">
-        <v>1.4414469750270071e-05</v>
+        <v>1.4611416675432486e-05</v>
       </c>
       <c r="F4" s="1">
-        <v>-1.4862833889847128e-07</v>
+        <v>-1.5065028662843878e-07</v>
       </c>
       <c r="G4" s="1">
-        <v>4.8764160518864865e-05</v>
+        <v>4.8869698560555066e-05</v>
       </c>
       <c r="H4" s="1">
-        <v>4.4052896881121391e-05</v>
+        <v>3.7239453396367265e-05</v>
       </c>
       <c r="I4" s="1">
-        <v>-1.1065981220629338e-06</v>
+        <v>-1.1080709525143067e-06</v>
       </c>
       <c r="J4" s="1">
-        <v>-9.0512881595828336e-07</v>
+        <v>-7.8839674528650518e-07</v>
       </c>
       <c r="K4" s="1">
-        <v>-1.6359405796427379e-05</v>
+        <v>-1.6498656031636502e-05</v>
       </c>
       <c r="L4" s="1">
-        <v>5.2495055465725713e-05</v>
+        <v>4.1882999322433834e-05</v>
       </c>
       <c r="M4" s="1">
-        <v>9.5806758363867557e-07</v>
+        <v>8.7534256013971313e-07</v>
       </c>
       <c r="N4" s="1">
-        <v>3.9160094464932299e-06</v>
+        <v>3.7665148119305164e-06</v>
       </c>
       <c r="O4" s="1">
-        <v>5.4228583317074241e-06</v>
+        <v>5.2916190001257477e-06</v>
       </c>
       <c r="P4" s="1">
-        <v>1.5546579947153455e-05</v>
+        <v>1.5437499957791727e-05</v>
       </c>
       <c r="Q4" s="1">
-        <v>1.9156092510950892e-07</v>
+        <v>2.8228688774800654e-07</v>
       </c>
       <c r="R4" s="1">
-        <v>1.0392530094083049e-06</v>
+        <v>1.1068926075111271e-06</v>
       </c>
       <c r="S4" s="1">
-        <v>-8.5212545566272808e-07</v>
+        <v>-7.1849675516165726e-07</v>
       </c>
       <c r="T4" s="1">
-        <v>2.9009450456572029e-07</v>
+        <v>3.9643110384434699e-07</v>
       </c>
       <c r="U4" s="1">
-        <v>5.5087231736968663e-07</v>
+        <v>6.0664714592178325e-07</v>
       </c>
       <c r="V4" s="1">
-        <v>5.973093367326624e-07</v>
+        <v>5.0687182970802388e-07</v>
       </c>
       <c r="W4" s="1">
-        <v>-0.00031832107696344787</v>
+        <v>-0.00032278124532339865</v>
       </c>
     </row>
     <row r="5">
@@ -626,70 +626,70 @@
         <v>26</v>
       </c>
       <c r="B5" s="1">
-        <v>-0.0020629734979311456</v>
+        <v>-0.0020101697618689291</v>
       </c>
       <c r="C5" s="1">
-        <v>-4.9775605363917165e-07</v>
+        <v>-4.7136717541511262e-07</v>
       </c>
       <c r="D5" s="1">
-        <v>-6.059687708271965e-08</v>
+        <v>-6.4502717203972043e-08</v>
       </c>
       <c r="E5" s="1">
-        <v>-1.4862833889847128e-07</v>
+        <v>-1.5065028662843878e-07</v>
       </c>
       <c r="F5" s="1">
-        <v>1.6340726940655337e-09</v>
+        <v>1.654928258149984e-09</v>
       </c>
       <c r="G5" s="1">
-        <v>-1.5684286796499654e-07</v>
+        <v>-1.5688645958664776e-07</v>
       </c>
       <c r="H5" s="1">
-        <v>-1.2295224693860962e-07</v>
+        <v>-3.9856570124761004e-08</v>
       </c>
       <c r="I5" s="1">
-        <v>3.1159939446642062e-09</v>
+        <v>3.1185465823162565e-09</v>
       </c>
       <c r="J5" s="1">
-        <v>1.2391730459744113e-09</v>
+        <v>-1.835675861742349e-10</v>
       </c>
       <c r="K5" s="1">
-        <v>1.7636146203141461e-07</v>
+        <v>1.7657359487383017e-07</v>
       </c>
       <c r="L5" s="1">
-        <v>-5.63594998402744e-07</v>
+        <v>-4.7047418769770257e-07</v>
       </c>
       <c r="M5" s="1">
-        <v>-1.4255806483140496e-08</v>
+        <v>-1.319744294827919e-08</v>
       </c>
       <c r="N5" s="1">
-        <v>-4.8484753478111113e-08</v>
+        <v>-4.6615530368592225e-08</v>
       </c>
       <c r="O5" s="1">
-        <v>-4.5987441051491555e-08</v>
+        <v>-4.4264645285581726e-08</v>
       </c>
       <c r="P5" s="1">
-        <v>-1.2954472966082137e-07</v>
+        <v>-1.279524324633138e-07</v>
       </c>
       <c r="Q5" s="1">
-        <v>-6.8967493322986294e-09</v>
+        <v>-7.860008453480967e-09</v>
       </c>
       <c r="R5" s="1">
-        <v>-1.5272969313622208e-08</v>
+        <v>-1.5927764423163062e-08</v>
       </c>
       <c r="S5" s="1">
-        <v>5.3509628627501231e-09</v>
+        <v>3.9619362260631861e-09</v>
       </c>
       <c r="T5" s="1">
-        <v>-6.1396327455173514e-09</v>
+        <v>-7.2006798823988158e-09</v>
       </c>
       <c r="U5" s="1">
-        <v>-9.5129913968081113e-09</v>
+        <v>-1.0220290600665668e-08</v>
       </c>
       <c r="V5" s="1">
-        <v>-1.2441434262836421e-08</v>
+        <v>-1.1538434135244887e-08</v>
       </c>
       <c r="W5" s="1">
-        <v>3.0742413399562382e-06</v>
+        <v>3.1200288304482765e-06</v>
       </c>
     </row>
     <row r="6">
@@ -697,70 +697,70 @@
         <v>27</v>
       </c>
       <c r="B6" s="1">
-        <v>-0.024086860814872137</v>
+        <v>-0.022469622583688863</v>
       </c>
       <c r="C6" s="1">
-        <v>-4.6493118817943686e-06</v>
+        <v>-7.2674772420120326e-06</v>
       </c>
       <c r="D6" s="1">
-        <v>-1.4422878180065715e-05</v>
+        <v>-1.4623243001438374e-05</v>
       </c>
       <c r="E6" s="1">
-        <v>4.8764160518864865e-05</v>
+        <v>4.8869698560555066e-05</v>
       </c>
       <c r="F6" s="1">
-        <v>-1.5684286796499654e-07</v>
+        <v>-1.5688645958664776e-07</v>
       </c>
       <c r="G6" s="1">
-        <v>0.0023145927341431585</v>
+        <v>0.0023219471296754748</v>
       </c>
       <c r="H6" s="1">
-        <v>0.0016310057294276305</v>
+        <v>0.0016404559123081295</v>
       </c>
       <c r="I6" s="1">
-        <v>-4.950873083259228e-05</v>
+        <v>-4.9624865921147426e-05</v>
       </c>
       <c r="J6" s="1">
-        <v>-3.5296246044729379e-05</v>
+        <v>-3.5476922073933609e-05</v>
       </c>
       <c r="K6" s="1">
-        <v>1.4006816408471715e-05</v>
+        <v>1.2618220630381193e-05</v>
       </c>
       <c r="L6" s="1">
-        <v>0.00011076794489617018</v>
+        <v>2.063023078264859e-05</v>
       </c>
       <c r="M6" s="1">
-        <v>-1.6191474892414748e-06</v>
+        <v>-1.5503119315552491e-06</v>
       </c>
       <c r="N6" s="1">
-        <v>-1.1454635585954648e-06</v>
+        <v>-8.1485783416613763e-07</v>
       </c>
       <c r="O6" s="1">
-        <v>-2.0861721506631827e-05</v>
+        <v>-2.0372463135206347e-05</v>
       </c>
       <c r="P6" s="1">
-        <v>2.1746718884894113e-05</v>
+        <v>2.2140570177479587e-05</v>
       </c>
       <c r="Q6" s="1">
-        <v>-1.8842412787086451e-05</v>
+        <v>-1.87389386265843e-05</v>
       </c>
       <c r="R6" s="1">
-        <v>-5.2832881719327419e-06</v>
+        <v>-5.1200026964584046e-06</v>
       </c>
       <c r="S6" s="1">
-        <v>-2.0652863578085969e-05</v>
+        <v>-2.0248791830273588e-05</v>
       </c>
       <c r="T6" s="1">
-        <v>-1.7328122599601455e-08</v>
+        <v>2.6828743549490514e-07</v>
       </c>
       <c r="U6" s="1">
-        <v>9.0225445971640376e-06</v>
+        <v>8.8183122139683383e-06</v>
       </c>
       <c r="V6" s="1">
-        <v>1.0729346708445609e-05</v>
+        <v>1.0221043622181648e-05</v>
       </c>
       <c r="W6" s="1">
-        <v>-0.0018671512810167063</v>
+        <v>-0.0018725550922736329</v>
       </c>
     </row>
     <row r="7">
@@ -768,70 +768,70 @@
         <v>28</v>
       </c>
       <c r="B7" s="1">
-        <v>-0.84752684688200053</v>
+        <v>-0.65156389114054736</v>
       </c>
       <c r="C7" s="1">
-        <v>-0.00033245011990130376</v>
+        <v>-0.00019710272217600254</v>
       </c>
       <c r="D7" s="1">
-        <v>4.0925395220297294e-06</v>
+        <v>-8.1657581063267117e-06</v>
       </c>
       <c r="E7" s="1">
-        <v>4.4052896881121391e-05</v>
+        <v>3.7239453396367265e-05</v>
       </c>
       <c r="F7" s="1">
-        <v>-1.2295224693860962e-07</v>
+        <v>-3.9856570124761004e-08</v>
       </c>
       <c r="G7" s="1">
-        <v>0.0016310057294276305</v>
+        <v>0.0016404559123081295</v>
       </c>
       <c r="H7" s="1">
-        <v>0.0051857827148108736</v>
+        <v>0.0057481415059368783</v>
       </c>
       <c r="I7" s="1">
-        <v>-3.5526705230850177e-05</v>
+        <v>-3.5663699874652733e-05</v>
       </c>
       <c r="J7" s="1">
-        <v>-0.00010430753426680029</v>
+        <v>-0.00011488897095594004</v>
       </c>
       <c r="K7" s="1">
-        <v>2.6376953332679573e-05</v>
+        <v>3.4981308518367283e-05</v>
       </c>
       <c r="L7" s="1">
-        <v>-0.0016412443109475616</v>
+        <v>-0.0018056466121749916</v>
       </c>
       <c r="M7" s="1">
-        <v>2.8503585508700431e-05</v>
+        <v>3.6776635144041285e-05</v>
       </c>
       <c r="N7" s="1">
-        <v>2.3441753727045727e-05</v>
+        <v>3.2978543855047824e-05</v>
       </c>
       <c r="O7" s="1">
-        <v>3.4616021888941025e-06</v>
+        <v>1.2204694072490596e-05</v>
       </c>
       <c r="P7" s="1">
-        <v>5.5943880444968705e-05</v>
+        <v>6.722528872278458e-05</v>
       </c>
       <c r="Q7" s="1">
-        <v>-3.2368797636016338e-05</v>
+        <v>-3.2478193458073843e-05</v>
       </c>
       <c r="R7" s="1">
-        <v>-2.0805176997775325e-05</v>
+        <v>-2.0461542879546214e-05</v>
       </c>
       <c r="S7" s="1">
-        <v>-3.4643295026317755e-05</v>
+        <v>-3.7790689232335215e-05</v>
       </c>
       <c r="T7" s="1">
-        <v>-1.1753853043433366e-06</v>
+        <v>-1.4855988358132972e-06</v>
       </c>
       <c r="U7" s="1">
-        <v>1.4256257417752475e-05</v>
+        <v>8.9389765393892133e-06</v>
       </c>
       <c r="V7" s="1">
-        <v>-4.2739003591800623e-06</v>
+        <v>1.4039326074559113e-06</v>
       </c>
       <c r="W7" s="1">
-        <v>-0.0017518716524618325</v>
+        <v>-0.0016440967270642329</v>
       </c>
     </row>
     <row r="8">
@@ -839,70 +839,70 @@
         <v>29</v>
       </c>
       <c r="B8" s="1">
-        <v>-0.00056549800400807284</v>
+        <v>-0.00059723400777149437</v>
       </c>
       <c r="C8" s="1">
-        <v>-4.5741924318749613e-07</v>
+        <v>-4.0603036032904649e-07</v>
       </c>
       <c r="D8" s="1">
-        <v>-4.1818378833333307e-07</v>
+        <v>-4.1178116483219376e-07</v>
       </c>
       <c r="E8" s="1">
-        <v>-1.1065981220629338e-06</v>
+        <v>-1.1080709525143067e-06</v>
       </c>
       <c r="F8" s="1">
-        <v>3.1159939446642062e-09</v>
+        <v>3.1185465823162565e-09</v>
       </c>
       <c r="G8" s="1">
-        <v>-4.950873083259228e-05</v>
+        <v>-4.9624865921147426e-05</v>
       </c>
       <c r="H8" s="1">
-        <v>-3.5526705230850177e-05</v>
+        <v>-3.5663699874652733e-05</v>
       </c>
       <c r="I8" s="1">
-        <v>1.1633421271661722e-06</v>
+        <v>1.1645804280856348e-06</v>
       </c>
       <c r="J8" s="1">
-        <v>8.4872004152588409e-07</v>
+        <v>8.5094084582192468e-07</v>
       </c>
       <c r="K8" s="1">
-        <v>-3.0857288742872632e-07</v>
+        <v>-2.7862247148785229e-07</v>
       </c>
       <c r="L8" s="1">
-        <v>-2.1870602937836631e-06</v>
+        <v>-4.4129185800040342e-07</v>
       </c>
       <c r="M8" s="1">
-        <v>-8.5782577055365285e-09</v>
+        <v>-1.0604280843227033e-08</v>
       </c>
       <c r="N8" s="1">
-        <v>1.0964114326692476e-07</v>
+        <v>1.0106403598526942e-07</v>
       </c>
       <c r="O8" s="1">
-        <v>1.0338692769271211e-06</v>
+        <v>1.0201626149714698e-06</v>
       </c>
       <c r="P8" s="1">
-        <v>4.1318610801153513e-07</v>
+        <v>4.02753128989315e-07</v>
       </c>
       <c r="Q8" s="1">
-        <v>3.4469010474826886e-07</v>
+        <v>3.4255989491453047e-07</v>
       </c>
       <c r="R8" s="1">
-        <v>1.6092860719758071e-07</v>
+        <v>1.580168725894926e-07</v>
       </c>
       <c r="S8" s="1">
-        <v>4.3433910700034405e-07</v>
+        <v>4.2666974512478799e-07</v>
       </c>
       <c r="T8" s="1">
-        <v>1.9002151002039221e-07</v>
+        <v>1.8440352853273732e-07</v>
       </c>
       <c r="U8" s="1">
-        <v>-8.7167637748239892e-08</v>
+        <v>-8.3571658523797941e-08</v>
       </c>
       <c r="V8" s="1">
-        <v>-7.2406530507970393e-08</v>
+        <v>-6.1874923908773538e-08</v>
       </c>
       <c r="W8" s="1">
-        <v>3.9732815692934975e-05</v>
+        <v>3.9822789489834008e-05</v>
       </c>
     </row>
     <row r="9">
@@ -910,70 +910,70 @@
         <v>30</v>
       </c>
       <c r="B9" s="1">
-        <v>0.011745537201306602</v>
+        <v>0.0081399060195679676</v>
       </c>
       <c r="C9" s="1">
-        <v>5.5885823381056244e-06</v>
+        <v>3.0874294977324786e-06</v>
       </c>
       <c r="D9" s="1">
-        <v>-1.1083448472931954e-06</v>
+        <v>-8.7204433200683424e-07</v>
       </c>
       <c r="E9" s="1">
-        <v>-9.0512881595828336e-07</v>
+        <v>-7.8839674528650518e-07</v>
       </c>
       <c r="F9" s="1">
-        <v>1.2391730459744113e-09</v>
+        <v>-1.835675861742349e-10</v>
       </c>
       <c r="G9" s="1">
-        <v>-3.5296246044729379e-05</v>
+        <v>-3.5476922073933609e-05</v>
       </c>
       <c r="H9" s="1">
-        <v>-0.00010430753426680029</v>
+        <v>-0.00011488897095594004</v>
       </c>
       <c r="I9" s="1">
-        <v>8.4872004152588409e-07</v>
+        <v>8.5094084582192468e-07</v>
       </c>
       <c r="J9" s="1">
-        <v>2.3511117560000679e-06</v>
+        <v>2.5521609261579499e-06</v>
       </c>
       <c r="K9" s="1">
-        <v>-3.9136386626843938e-07</v>
+        <v>-5.4916758861061242e-07</v>
       </c>
       <c r="L9" s="1">
-        <v>3.0421869174517901e-05</v>
+        <v>3.333340669909736e-05</v>
       </c>
       <c r="M9" s="1">
-        <v>-1.7641384238073405e-07</v>
+        <v>-3.2086538851258452e-07</v>
       </c>
       <c r="N9" s="1">
-        <v>3.4724416361186658e-07</v>
+        <v>1.823162157993687e-07</v>
       </c>
       <c r="O9" s="1">
-        <v>1.7103016154289762e-06</v>
+        <v>1.5601278645409008e-06</v>
       </c>
       <c r="P9" s="1">
-        <v>9.4546296813828439e-07</v>
+        <v>7.5011113847745573e-07</v>
       </c>
       <c r="Q9" s="1">
-        <v>2.7085641944059807e-07</v>
+        <v>2.7214047083857793e-07</v>
       </c>
       <c r="R9" s="1">
-        <v>3.9344831622197832e-07</v>
+        <v>3.8646976445492682e-07</v>
       </c>
       <c r="S9" s="1">
-        <v>2.5417449190452678e-07</v>
+        <v>3.1035945744303584e-07</v>
       </c>
       <c r="T9" s="1">
-        <v>-3.4921128740913884e-09</v>
+        <v>1.0251967715352005e-09</v>
       </c>
       <c r="U9" s="1">
-        <v>-2.0453968324348757e-08</v>
+        <v>7.6429164691572016e-08</v>
       </c>
       <c r="V9" s="1">
-        <v>3.8876887080584521e-07</v>
+        <v>2.8609900653638784e-07</v>
       </c>
       <c r="W9" s="1">
-        <v>3.4332521095418317e-05</v>
+        <v>3.2508610719808493e-05</v>
       </c>
     </row>
     <row r="10">
@@ -981,70 +981,70 @@
         <v>31</v>
       </c>
       <c r="B10" s="1">
-        <v>-0.13442856466882061</v>
+        <v>-0.12473996461900837</v>
       </c>
       <c r="C10" s="1">
-        <v>5.6839424853557922e-05</v>
+        <v>5.6204633581223347e-05</v>
       </c>
       <c r="D10" s="1">
-        <v>4.0292572052781461e-07</v>
+        <v>-1.2268743077588019e-06</v>
       </c>
       <c r="E10" s="1">
-        <v>-1.6359405796427379e-05</v>
+        <v>-1.6498656031636502e-05</v>
       </c>
       <c r="F10" s="1">
-        <v>1.7636146203141461e-07</v>
+        <v>1.7657359487383017e-07</v>
       </c>
       <c r="G10" s="1">
-        <v>1.4006816408471715e-05</v>
+        <v>1.2618220630381193e-05</v>
       </c>
       <c r="H10" s="1">
-        <v>2.6376953332679573e-05</v>
+        <v>3.4981308518367283e-05</v>
       </c>
       <c r="I10" s="1">
-        <v>-3.0857288742872632e-07</v>
+        <v>-2.7862247148785229e-07</v>
       </c>
       <c r="J10" s="1">
-        <v>-3.9136386626843938e-07</v>
+        <v>-5.4916758861061242e-07</v>
       </c>
       <c r="K10" s="1">
-        <v>0.00021704130029205534</v>
+        <v>0.00021578984780704473</v>
       </c>
       <c r="L10" s="1">
-        <v>-6.8212731741658199e-06</v>
+        <v>-2.2095926416613203e-05</v>
       </c>
       <c r="M10" s="1">
-        <v>-1.0417616328061141e-05</v>
+        <v>-1.0826593177484732e-05</v>
       </c>
       <c r="N10" s="1">
-        <v>-2.5908400676912296e-05</v>
+        <v>-2.5434524584085305e-05</v>
       </c>
       <c r="O10" s="1">
-        <v>-3.85903053514472e-05</v>
+        <v>-3.8103278207212853e-05</v>
       </c>
       <c r="P10" s="1">
-        <v>-3.3652821693033197e-05</v>
+        <v>-3.3431850655201049e-05</v>
       </c>
       <c r="Q10" s="1">
-        <v>3.8799650688343753e-07</v>
+        <v>-9.4974197812852455e-08</v>
       </c>
       <c r="R10" s="1">
-        <v>-2.5800624064674299e-06</v>
+        <v>-2.6101618387920824e-06</v>
       </c>
       <c r="S10" s="1">
-        <v>-3.0333879819866866e-06</v>
+        <v>-3.201876724242149e-06</v>
       </c>
       <c r="T10" s="1">
-        <v>-1.1887491469223373e-06</v>
+        <v>-1.4336351395065886e-06</v>
       </c>
       <c r="U10" s="1">
-        <v>-5.9392879828338155e-07</v>
+        <v>-5.0840868979359559e-07</v>
       </c>
       <c r="V10" s="1">
-        <v>1.3314176161533297e-06</v>
+        <v>1.0962343440291996e-06</v>
       </c>
       <c r="W10" s="1">
-        <v>0.0002256817482865712</v>
+        <v>0.00023362734683500424</v>
       </c>
     </row>
     <row r="11">
@@ -1052,70 +1052,70 @@
         <v>32</v>
       </c>
       <c r="B11" s="1">
-        <v>-0.48953766750375327</v>
+        <v>-0.74788370446438723</v>
       </c>
       <c r="C11" s="1">
-        <v>0.0001089453119628335</v>
+        <v>-0.00029153125164678022</v>
       </c>
       <c r="D11" s="1">
-        <v>-2.9545973143004297e-06</v>
+        <v>1.7252231471935606e-05</v>
       </c>
       <c r="E11" s="1">
-        <v>5.2495055465725713e-05</v>
+        <v>4.1882999322433834e-05</v>
       </c>
       <c r="F11" s="1">
-        <v>-5.63594998402744e-07</v>
+        <v>-4.7047418769770257e-07</v>
       </c>
       <c r="G11" s="1">
-        <v>0.00011076794489617018</v>
+        <v>2.063023078264859e-05</v>
       </c>
       <c r="H11" s="1">
-        <v>-0.0016412443109475616</v>
+        <v>-0.0018056466121749916</v>
       </c>
       <c r="I11" s="1">
-        <v>-2.1870602937836631e-06</v>
+        <v>-4.4129185800040342e-07</v>
       </c>
       <c r="J11" s="1">
-        <v>3.0421869174517901e-05</v>
+        <v>3.333340669909736e-05</v>
       </c>
       <c r="K11" s="1">
-        <v>-6.8212731741658199e-06</v>
+        <v>-2.2095926416613203e-05</v>
       </c>
       <c r="L11" s="1">
-        <v>0.014433644958079651</v>
+        <v>0.0064080575404160617</v>
       </c>
       <c r="M11" s="1">
-        <v>-2.3037145894146593e-05</v>
+        <v>-2.5330322007950147e-05</v>
       </c>
       <c r="N11" s="1">
-        <v>-1.9992976216043116e-05</v>
+        <v>-2.4089293224143946e-05</v>
       </c>
       <c r="O11" s="1">
-        <v>-1.5091408785629595e-05</v>
+        <v>-1.9403556520030394e-05</v>
       </c>
       <c r="P11" s="1">
-        <v>-1.284525040725833e-05</v>
+        <v>-1.9526978912640255e-05</v>
       </c>
       <c r="Q11" s="1">
-        <v>-9.6166420583206344e-06</v>
+        <v>-4.5773208390664117e-06</v>
       </c>
       <c r="R11" s="1">
-        <v>-4.6327370957248545e-06</v>
+        <v>-4.2793962394230028e-06</v>
       </c>
       <c r="S11" s="1">
-        <v>-3.2753477427249543e-06</v>
+        <v>4.5682425433004786e-06</v>
       </c>
       <c r="T11" s="1">
-        <v>6.9502102707221855e-06</v>
+        <v>6.0564452277078891e-06</v>
       </c>
       <c r="U11" s="1">
-        <v>2.6885759637287356e-06</v>
+        <v>1.5097743673338664e-05</v>
       </c>
       <c r="V11" s="1">
-        <v>1.5109422661962023e-05</v>
+        <v>-2.8537422348930768e-06</v>
       </c>
       <c r="W11" s="1">
-        <v>-0.0011178327009573024</v>
+        <v>-0.00082115879604104276</v>
       </c>
     </row>
     <row r="12">
@@ -1123,70 +1123,70 @@
         <v>33</v>
       </c>
       <c r="B12" s="1">
-        <v>0.26790129710491084</v>
+        <v>0.27063816836641191</v>
       </c>
       <c r="C12" s="1">
-        <v>-3.7360467119149066e-06</v>
+        <v>-1.98162673167e-06</v>
       </c>
       <c r="D12" s="1">
-        <v>4.6314788066063884e-06</v>
+        <v>4.4308580176230121e-06</v>
       </c>
       <c r="E12" s="1">
-        <v>9.5806758363867557e-07</v>
+        <v>8.7534256013971313e-07</v>
       </c>
       <c r="F12" s="1">
-        <v>-1.4255806483140496e-08</v>
+        <v>-1.319744294827919e-08</v>
       </c>
       <c r="G12" s="1">
-        <v>-1.6191474892414748e-06</v>
+        <v>-1.5503119315552491e-06</v>
       </c>
       <c r="H12" s="1">
-        <v>2.8503585508700431e-05</v>
+        <v>3.6776635144041285e-05</v>
       </c>
       <c r="I12" s="1">
-        <v>-8.5782577055365285e-09</v>
+        <v>-1.0604280843227033e-08</v>
       </c>
       <c r="J12" s="1">
-        <v>-1.7641384238073405e-07</v>
+        <v>-3.2086538851258452e-07</v>
       </c>
       <c r="K12" s="1">
-        <v>-1.0417616328061141e-05</v>
+        <v>-1.0826593177484732e-05</v>
       </c>
       <c r="L12" s="1">
-        <v>-2.3037145894146593e-05</v>
+        <v>-2.5330322007950147e-05</v>
       </c>
       <c r="M12" s="1">
-        <v>0.0062705958879695203</v>
+        <v>0.0062757946330852521</v>
       </c>
       <c r="N12" s="1">
-        <v>0.0056169998938396613</v>
+        <v>0.0056226644091075667</v>
       </c>
       <c r="O12" s="1">
-        <v>0.0056156715055076661</v>
+        <v>0.0056213094302583096</v>
       </c>
       <c r="P12" s="1">
-        <v>0.005612127205413711</v>
+        <v>0.005617709708777157</v>
       </c>
       <c r="Q12" s="1">
-        <v>-1.4521458986586364e-06</v>
+        <v>-1.5349061207981478e-06</v>
       </c>
       <c r="R12" s="1">
-        <v>-9.5852490956752141e-06</v>
+        <v>-9.6559314746394334e-06</v>
       </c>
       <c r="S12" s="1">
-        <v>-6.0715595430479166e-06</v>
+        <v>-6.0687000759821673e-06</v>
       </c>
       <c r="T12" s="1">
-        <v>-2.6182216523857197e-06</v>
+        <v>-2.6058051008210595e-06</v>
       </c>
       <c r="U12" s="1">
-        <v>-2.4831437149844949e-06</v>
+        <v>-2.4099906940750413e-06</v>
       </c>
       <c r="V12" s="1">
-        <v>1.8766594716098065e-07</v>
+        <v>2.0941684284322803e-07</v>
       </c>
       <c r="W12" s="1">
-        <v>-0.0056190133460342915</v>
+        <v>-0.005622985317533323</v>
       </c>
     </row>
     <row r="13">
@@ -1194,70 +1194,70 @@
         <v>34</v>
       </c>
       <c r="B13" s="1">
-        <v>0.60038673859366642</v>
+        <v>0.60199875478337439</v>
       </c>
       <c r="C13" s="1">
-        <v>-3.6456001712306727e-06</v>
+        <v>-1.6647596124567737e-06</v>
       </c>
       <c r="D13" s="1">
-        <v>8.3808631080248326e-06</v>
+        <v>8.2574196957376216e-06</v>
       </c>
       <c r="E13" s="1">
-        <v>3.9160094464932299e-06</v>
+        <v>3.7665148119305164e-06</v>
       </c>
       <c r="F13" s="1">
-        <v>-4.8484753478111113e-08</v>
+        <v>-4.6615530368592225e-08</v>
       </c>
       <c r="G13" s="1">
-        <v>-1.1454635585954648e-06</v>
+        <v>-8.1485783416613763e-07</v>
       </c>
       <c r="H13" s="1">
-        <v>2.3441753727045727e-05</v>
+        <v>3.2978543855047824e-05</v>
       </c>
       <c r="I13" s="1">
-        <v>1.0964114326692476e-07</v>
+        <v>1.0106403598526942e-07</v>
       </c>
       <c r="J13" s="1">
-        <v>3.4724416361186658e-07</v>
+        <v>1.823162157993687e-07</v>
       </c>
       <c r="K13" s="1">
-        <v>-2.5908400676912296e-05</v>
+        <v>-2.5434524584085305e-05</v>
       </c>
       <c r="L13" s="1">
-        <v>-1.9992976216043116e-05</v>
+        <v>-2.4089293224143946e-05</v>
       </c>
       <c r="M13" s="1">
-        <v>0.0056169998938396613</v>
+        <v>0.0056226644091075667</v>
       </c>
       <c r="N13" s="1">
-        <v>0.0057644435779904465</v>
+        <v>0.0057699077782941491</v>
       </c>
       <c r="O13" s="1">
-        <v>0.0056223531748618959</v>
+        <v>0.0056277737314951162</v>
       </c>
       <c r="P13" s="1">
-        <v>0.0056203788535698785</v>
+        <v>0.0056256796969816518</v>
       </c>
       <c r="Q13" s="1">
-        <v>7.0541802217397347e-07</v>
+        <v>6.6425429113561255e-07</v>
       </c>
       <c r="R13" s="1">
-        <v>-7.357229477342118e-06</v>
+        <v>-7.3860917922933709e-06</v>
       </c>
       <c r="S13" s="1">
-        <v>-3.3954089836170159e-06</v>
+        <v>-3.4505221116705508e-06</v>
       </c>
       <c r="T13" s="1">
-        <v>-1.7158422838309244e-06</v>
+        <v>-1.6771204594124553e-06</v>
       </c>
       <c r="U13" s="1">
-        <v>-7.2421027662876555e-06</v>
+        <v>-7.1855654498169131e-06</v>
       </c>
       <c r="V13" s="1">
-        <v>-1.0170283716604918e-06</v>
+        <v>-9.3705729008939815e-07</v>
       </c>
       <c r="W13" s="1">
-        <v>-0.005679488957244334</v>
+        <v>-0.0056828050509451656</v>
       </c>
     </row>
     <row r="14">
@@ -1265,70 +1265,70 @@
         <v>35</v>
       </c>
       <c r="B14" s="1">
-        <v>0.72472309005210711</v>
+        <v>0.72545916982199676</v>
       </c>
       <c r="C14" s="1">
-        <v>4.8222781277397261e-06</v>
+        <v>6.5996842673235034e-06</v>
       </c>
       <c r="D14" s="1">
-        <v>1.582525504493674e-05</v>
+        <v>1.5817695030519264e-05</v>
       </c>
       <c r="E14" s="1">
-        <v>5.4228583317074241e-06</v>
+        <v>5.2916190001257477e-06</v>
       </c>
       <c r="F14" s="1">
-        <v>-4.5987441051491555e-08</v>
+        <v>-4.4264645285581726e-08</v>
       </c>
       <c r="G14" s="1">
-        <v>-2.0861721506631827e-05</v>
+        <v>-2.0372463135206347e-05</v>
       </c>
       <c r="H14" s="1">
-        <v>3.4616021888941025e-06</v>
+        <v>1.2204694072490596e-05</v>
       </c>
       <c r="I14" s="1">
-        <v>1.0338692769271211e-06</v>
+        <v>1.0201626149714698e-06</v>
       </c>
       <c r="J14" s="1">
-        <v>1.7103016154289762e-06</v>
+        <v>1.5601278645409008e-06</v>
       </c>
       <c r="K14" s="1">
-        <v>-3.85903053514472e-05</v>
+        <v>-3.8103278207212853e-05</v>
       </c>
       <c r="L14" s="1">
-        <v>-1.5091408785629595e-05</v>
+        <v>-1.9403556520030394e-05</v>
       </c>
       <c r="M14" s="1">
-        <v>0.0056156715055076661</v>
+        <v>0.0056213094302583096</v>
       </c>
       <c r="N14" s="1">
-        <v>0.0056223531748618959</v>
+        <v>0.0056277737314951162</v>
       </c>
       <c r="O14" s="1">
-        <v>0.0057242344263879639</v>
+        <v>0.005729314318249178</v>
       </c>
       <c r="P14" s="1">
-        <v>0.0056733542806859027</v>
+        <v>0.0056781650950756477</v>
       </c>
       <c r="Q14" s="1">
-        <v>-2.4079269577846436e-06</v>
+        <v>-2.406364877923913e-06</v>
       </c>
       <c r="R14" s="1">
-        <v>-8.9560650867856894e-06</v>
+        <v>-8.9616402307103366e-06</v>
       </c>
       <c r="S14" s="1">
-        <v>-6.994124256003829e-06</v>
+        <v>-6.9664913490974774e-06</v>
       </c>
       <c r="T14" s="1">
-        <v>7.487001092653517e-07</v>
+        <v>8.2926262900072899e-07</v>
       </c>
       <c r="U14" s="1">
-        <v>-1.4047001323023962e-05</v>
+        <v>-1.3957878594015977e-05</v>
       </c>
       <c r="V14" s="1">
-        <v>-1.288644188473316e-05</v>
+        <v>-1.2791385780241081e-05</v>
       </c>
       <c r="W14" s="1">
-        <v>-0.005786070279192603</v>
+        <v>-0.0057897399482080714</v>
       </c>
     </row>
     <row r="15">
@@ -1336,70 +1336,70 @@
         <v>36</v>
       </c>
       <c r="B15" s="1">
-        <v>0.7566467621915387</v>
+        <v>0.7580819030310143</v>
       </c>
       <c r="C15" s="1">
-        <v>-1.5095211150809926e-05</v>
+        <v>-1.380496130332998e-05</v>
       </c>
       <c r="D15" s="1">
-        <v>1.6883321629788606e-05</v>
+        <v>1.6901720471742195e-05</v>
       </c>
       <c r="E15" s="1">
-        <v>1.5546579947153455e-05</v>
+        <v>1.5437499957791727e-05</v>
       </c>
       <c r="F15" s="1">
-        <v>-1.2954472966082137e-07</v>
+        <v>-1.279524324633138e-07</v>
       </c>
       <c r="G15" s="1">
-        <v>2.1746718884894113e-05</v>
+        <v>2.2140570177479587e-05</v>
       </c>
       <c r="H15" s="1">
-        <v>5.5943880444968705e-05</v>
+        <v>6.722528872278458e-05</v>
       </c>
       <c r="I15" s="1">
-        <v>4.1318610801153513e-07</v>
+        <v>4.02753128989315e-07</v>
       </c>
       <c r="J15" s="1">
-        <v>9.4546296813828439e-07</v>
+        <v>7.5011113847745573e-07</v>
       </c>
       <c r="K15" s="1">
-        <v>-3.3652821693033197e-05</v>
+        <v>-3.3431850655201049e-05</v>
       </c>
       <c r="L15" s="1">
-        <v>-1.284525040725833e-05</v>
+        <v>-1.9526978912640255e-05</v>
       </c>
       <c r="M15" s="1">
-        <v>0.005612127205413711</v>
+        <v>0.005617709708777157</v>
       </c>
       <c r="N15" s="1">
-        <v>0.0056203788535698785</v>
+        <v>0.0056256796969816518</v>
       </c>
       <c r="O15" s="1">
-        <v>0.0056733542806859027</v>
+        <v>0.0056781650950756477</v>
       </c>
       <c r="P15" s="1">
-        <v>0.0059669527986798048</v>
+        <v>0.0059734248798661033</v>
       </c>
       <c r="Q15" s="1">
-        <v>2.7682926549530955e-06</v>
+        <v>2.7960692370743037e-06</v>
       </c>
       <c r="R15" s="1">
-        <v>-1.3453488475114085e-06</v>
+        <v>-1.2261349547603844e-06</v>
       </c>
       <c r="S15" s="1">
-        <v>-6.5193510333540432e-06</v>
+        <v>-6.4360759840657096e-06</v>
       </c>
       <c r="T15" s="1">
-        <v>7.7478604954786832e-06</v>
+        <v>7.9455600571400612e-06</v>
       </c>
       <c r="U15" s="1">
-        <v>-1.7384593485986147e-05</v>
+        <v>-1.7426828043496914e-05</v>
       </c>
       <c r="V15" s="1">
-        <v>-1.3465600376704758e-05</v>
+        <v>-1.3416685542518499e-05</v>
       </c>
       <c r="W15" s="1">
-        <v>-0.0060906509371926355</v>
+        <v>-0.0060949660660578981</v>
       </c>
     </row>
     <row r="16">
@@ -1407,70 +1407,70 @@
         <v>37</v>
       </c>
       <c r="B16" s="1">
-        <v>0.048675521032046545</v>
+        <v>0.048782629923848839</v>
       </c>
       <c r="C16" s="1">
-        <v>7.242118320708494e-06</v>
+        <v>7.5403151689304017e-06</v>
       </c>
       <c r="D16" s="1">
-        <v>2.1064515962938622e-06</v>
+        <v>2.0792681766556301e-06</v>
       </c>
       <c r="E16" s="1">
-        <v>1.9156092510950892e-07</v>
+        <v>2.8228688774800654e-07</v>
       </c>
       <c r="F16" s="1">
-        <v>-6.8967493322986294e-09</v>
+        <v>-7.860008453480967e-09</v>
       </c>
       <c r="G16" s="1">
-        <v>-1.8842412787086451e-05</v>
+        <v>-1.87389386265843e-05</v>
       </c>
       <c r="H16" s="1">
-        <v>-3.2368797636016338e-05</v>
+        <v>-3.2478193458073843e-05</v>
       </c>
       <c r="I16" s="1">
-        <v>3.4469010474826886e-07</v>
+        <v>3.4255989491453047e-07</v>
       </c>
       <c r="J16" s="1">
-        <v>2.7085641944059807e-07</v>
+        <v>2.7214047083857793e-07</v>
       </c>
       <c r="K16" s="1">
-        <v>3.8799650688343753e-07</v>
+        <v>-9.4974197812852455e-08</v>
       </c>
       <c r="L16" s="1">
-        <v>-9.6166420583206344e-06</v>
+        <v>-4.5773208390664117e-06</v>
       </c>
       <c r="M16" s="1">
-        <v>-1.4521458986586364e-06</v>
+        <v>-1.5349061207981478e-06</v>
       </c>
       <c r="N16" s="1">
-        <v>7.0541802217397347e-07</v>
+        <v>6.6425429113561255e-07</v>
       </c>
       <c r="O16" s="1">
-        <v>-2.4079269577846436e-06</v>
+        <v>-2.406364877923913e-06</v>
       </c>
       <c r="P16" s="1">
-        <v>2.7682926549530955e-06</v>
+        <v>2.7960692370743037e-06</v>
       </c>
       <c r="Q16" s="1">
-        <v>0.00045831769923564359</v>
+        <v>0.00045939685467762391</v>
       </c>
       <c r="R16" s="1">
-        <v>0.00021683692070070706</v>
+        <v>0.00021738653909490546</v>
       </c>
       <c r="S16" s="1">
-        <v>0.00021739715236399033</v>
+        <v>0.00021793342842530748</v>
       </c>
       <c r="T16" s="1">
-        <v>0.00021682208307308406</v>
+        <v>0.00021735362111843589</v>
       </c>
       <c r="U16" s="1">
-        <v>-7.4385127250660918e-06</v>
+        <v>-7.3291514156983826e-06</v>
       </c>
       <c r="V16" s="1">
-        <v>-1.1562596408892125e-05</v>
+        <v>-1.1468608560269498e-05</v>
       </c>
       <c r="W16" s="1">
-        <v>-0.00020601899621545792</v>
+        <v>-0.00020819360861913365</v>
       </c>
     </row>
     <row r="17">
@@ -1478,70 +1478,70 @@
         <v>38</v>
       </c>
       <c r="B17" s="1">
-        <v>0.054025314039215205</v>
+        <v>0.053589098171805988</v>
       </c>
       <c r="C17" s="1">
-        <v>4.5044516540850116e-06</v>
+        <v>4.5727824596310993e-06</v>
       </c>
       <c r="D17" s="1">
-        <v>3.8913871761079176e-08</v>
+        <v>3.4556389647186684e-08</v>
       </c>
       <c r="E17" s="1">
-        <v>1.0392530094083049e-06</v>
+        <v>1.1068926075111271e-06</v>
       </c>
       <c r="F17" s="1">
-        <v>-1.5272969313622208e-08</v>
+        <v>-1.5927764423163062e-08</v>
       </c>
       <c r="G17" s="1">
-        <v>-5.2832881719327419e-06</v>
+        <v>-5.1200026964584046e-06</v>
       </c>
       <c r="H17" s="1">
-        <v>-2.0805176997775325e-05</v>
+        <v>-2.0461542879546214e-05</v>
       </c>
       <c r="I17" s="1">
-        <v>1.6092860719758071e-07</v>
+        <v>1.580168725894926e-07</v>
       </c>
       <c r="J17" s="1">
-        <v>3.9344831622197832e-07</v>
+        <v>3.8646976445492682e-07</v>
       </c>
       <c r="K17" s="1">
-        <v>-2.5800624064674299e-06</v>
+        <v>-2.6101618387920824e-06</v>
       </c>
       <c r="L17" s="1">
-        <v>-4.6327370957248545e-06</v>
+        <v>-4.2793962394230028e-06</v>
       </c>
       <c r="M17" s="1">
-        <v>-9.5852490956752141e-06</v>
+        <v>-9.6559314746394334e-06</v>
       </c>
       <c r="N17" s="1">
-        <v>-7.357229477342118e-06</v>
+        <v>-7.3860917922933709e-06</v>
       </c>
       <c r="O17" s="1">
-        <v>-8.9560650867856894e-06</v>
+        <v>-8.9616402307103366e-06</v>
       </c>
       <c r="P17" s="1">
-        <v>-1.3453488475114085e-06</v>
+        <v>-1.2261349547603844e-06</v>
       </c>
       <c r="Q17" s="1">
-        <v>0.00021683692070070706</v>
+        <v>0.00021738653909490546</v>
       </c>
       <c r="R17" s="1">
-        <v>0.00058870283831991433</v>
+        <v>0.00058961205889137647</v>
       </c>
       <c r="S17" s="1">
-        <v>0.00021653803673550367</v>
+        <v>0.00021707669546596777</v>
       </c>
       <c r="T17" s="1">
-        <v>0.00021669267803069652</v>
+        <v>0.00021723316740707017</v>
       </c>
       <c r="U17" s="1">
-        <v>-5.1980929152087674e-06</v>
+        <v>-5.1150034474709898e-06</v>
       </c>
       <c r="V17" s="1">
-        <v>-6.6767548082805252e-06</v>
+        <v>-6.6391128771455318e-06</v>
       </c>
       <c r="W17" s="1">
-        <v>-0.00022112132880905565</v>
+        <v>-0.00022326346847679335</v>
       </c>
     </row>
     <row r="18">
@@ -1549,70 +1549,70 @@
         <v>39</v>
       </c>
       <c r="B18" s="1">
-        <v>0.0071629109881761474</v>
+        <v>0.0057761299948371489</v>
       </c>
       <c r="C18" s="1">
-        <v>2.707181254504445e-06</v>
+        <v>2.1700089071435109e-06</v>
       </c>
       <c r="D18" s="1">
-        <v>-1.1178748205787355e-07</v>
+        <v>-4.9756284019680556e-08</v>
       </c>
       <c r="E18" s="1">
-        <v>-8.5212545566272808e-07</v>
+        <v>-7.1849675516165726e-07</v>
       </c>
       <c r="F18" s="1">
-        <v>5.3509628627501231e-09</v>
+        <v>3.9619362260631861e-09</v>
       </c>
       <c r="G18" s="1">
-        <v>-2.0652863578085969e-05</v>
+        <v>-2.0248791830273588e-05</v>
       </c>
       <c r="H18" s="1">
-        <v>-3.4643295026317755e-05</v>
+        <v>-3.7790689232335215e-05</v>
       </c>
       <c r="I18" s="1">
-        <v>4.3433910700034405e-07</v>
+        <v>4.2666974512478799e-07</v>
       </c>
       <c r="J18" s="1">
-        <v>2.5417449190452678e-07</v>
+        <v>3.1035945744303584e-07</v>
       </c>
       <c r="K18" s="1">
-        <v>-3.0333879819866866e-06</v>
+        <v>-3.201876724242149e-06</v>
       </c>
       <c r="L18" s="1">
-        <v>-3.2753477427249543e-06</v>
+        <v>4.5682425433004786e-06</v>
       </c>
       <c r="M18" s="1">
-        <v>-6.0715595430479166e-06</v>
+        <v>-6.0687000759821673e-06</v>
       </c>
       <c r="N18" s="1">
-        <v>-3.3954089836170159e-06</v>
+        <v>-3.4505221116705508e-06</v>
       </c>
       <c r="O18" s="1">
-        <v>-6.994124256003829e-06</v>
+        <v>-6.9664913490974774e-06</v>
       </c>
       <c r="P18" s="1">
-        <v>-6.5193510333540432e-06</v>
+        <v>-6.4360759840657096e-06</v>
       </c>
       <c r="Q18" s="1">
-        <v>0.00021739715236399033</v>
+        <v>0.00021793342842530748</v>
       </c>
       <c r="R18" s="1">
-        <v>0.00021653803673550367</v>
+        <v>0.00021707669546596777</v>
       </c>
       <c r="S18" s="1">
-        <v>0.00043940062876962626</v>
+        <v>0.00044015818438452263</v>
       </c>
       <c r="T18" s="1">
-        <v>0.00021662454940055454</v>
+        <v>0.00021716318971329684</v>
       </c>
       <c r="U18" s="1">
-        <v>-6.7764967184588356e-06</v>
+        <v>-6.6692999145303537e-06</v>
       </c>
       <c r="V18" s="1">
-        <v>-8.0050299612204422e-06</v>
+        <v>-7.9033658621684457e-06</v>
       </c>
       <c r="W18" s="1">
-        <v>-0.00017878775190088614</v>
+        <v>-0.00018222568965863394</v>
       </c>
     </row>
     <row r="19">
@@ -1620,70 +1620,70 @@
         <v>40</v>
       </c>
       <c r="B19" s="1">
-        <v>0.03366834944583038</v>
+        <v>0.032785731248463471</v>
       </c>
       <c r="C19" s="1">
-        <v>-1.3953452314826435e-06</v>
+        <v>-1.8420825670243646e-06</v>
       </c>
       <c r="D19" s="1">
-        <v>5.6196150282453145e-06</v>
+        <v>5.6457649163608449e-06</v>
       </c>
       <c r="E19" s="1">
-        <v>2.9009450456572029e-07</v>
+        <v>3.9643110384434699e-07</v>
       </c>
       <c r="F19" s="1">
-        <v>-6.1396327455173514e-09</v>
+        <v>-7.2006798823988158e-09</v>
       </c>
       <c r="G19" s="1">
-        <v>-1.7328122599601455e-08</v>
+        <v>2.6828743549490514e-07</v>
       </c>
       <c r="H19" s="1">
-        <v>-1.1753853043433366e-06</v>
+        <v>-1.4855988358132972e-06</v>
       </c>
       <c r="I19" s="1">
-        <v>1.9002151002039221e-07</v>
+        <v>1.8440352853273732e-07</v>
       </c>
       <c r="J19" s="1">
-        <v>-3.4921128740913884e-09</v>
+        <v>1.0251967715352005e-09</v>
       </c>
       <c r="K19" s="1">
-        <v>-1.1887491469223373e-06</v>
+        <v>-1.4336351395065886e-06</v>
       </c>
       <c r="L19" s="1">
-        <v>6.9502102707221855e-06</v>
+        <v>6.0564452277078891e-06</v>
       </c>
       <c r="M19" s="1">
-        <v>-2.6182216523857197e-06</v>
+        <v>-2.6058051008210595e-06</v>
       </c>
       <c r="N19" s="1">
-        <v>-1.7158422838309244e-06</v>
+        <v>-1.6771204594124553e-06</v>
       </c>
       <c r="O19" s="1">
-        <v>7.487001092653517e-07</v>
+        <v>8.2926262900072899e-07</v>
       </c>
       <c r="P19" s="1">
-        <v>7.7478604954786832e-06</v>
+        <v>7.9455600571400612e-06</v>
       </c>
       <c r="Q19" s="1">
-        <v>0.00021682208307308406</v>
+        <v>0.00021735362111843589</v>
       </c>
       <c r="R19" s="1">
-        <v>0.00021669267803069652</v>
+        <v>0.00021723316740707017</v>
       </c>
       <c r="S19" s="1">
-        <v>0.00021662454940055454</v>
+        <v>0.00021716318971329684</v>
       </c>
       <c r="T19" s="1">
-        <v>0.00030976950033411647</v>
+        <v>0.00031040259910735123</v>
       </c>
       <c r="U19" s="1">
-        <v>-8.4199229896414647e-06</v>
+        <v>-8.2673731535228287e-06</v>
       </c>
       <c r="V19" s="1">
-        <v>-1.1338849708603201e-05</v>
+        <v>-1.1287715049396718e-05</v>
       </c>
       <c r="W19" s="1">
-        <v>-0.00022270813499721906</v>
+        <v>-0.00022563509149006831</v>
       </c>
     </row>
     <row r="20">
@@ -1691,70 +1691,70 @@
         <v>41</v>
       </c>
       <c r="B20" s="1">
-        <v>-0.042115425303942404</v>
+        <v>-0.044160084868125428</v>
       </c>
       <c r="C20" s="1">
-        <v>8.1934567489098656e-06</v>
+        <v>6.694968335608059e-06</v>
       </c>
       <c r="D20" s="1">
-        <v>5.3491343403439333e-06</v>
+        <v>5.5367422780267181e-06</v>
       </c>
       <c r="E20" s="1">
-        <v>5.5087231736968663e-07</v>
+        <v>6.0664714592178325e-07</v>
       </c>
       <c r="F20" s="1">
-        <v>-9.5129913968081113e-09</v>
+        <v>-1.0220290600665668e-08</v>
       </c>
       <c r="G20" s="1">
-        <v>9.0225445971640376e-06</v>
+        <v>8.8183122139683383e-06</v>
       </c>
       <c r="H20" s="1">
-        <v>1.4256257417752475e-05</v>
+        <v>8.9389765393892133e-06</v>
       </c>
       <c r="I20" s="1">
-        <v>-8.7167637748239892e-08</v>
+        <v>-8.3571658523797941e-08</v>
       </c>
       <c r="J20" s="1">
-        <v>-2.0453968324348757e-08</v>
+        <v>7.6429164691572016e-08</v>
       </c>
       <c r="K20" s="1">
-        <v>-5.9392879828338155e-07</v>
+        <v>-5.0840868979359559e-07</v>
       </c>
       <c r="L20" s="1">
-        <v>2.6885759637287356e-06</v>
+        <v>1.5097743673338664e-05</v>
       </c>
       <c r="M20" s="1">
-        <v>-2.4831437149844949e-06</v>
+        <v>-2.4099906940750413e-06</v>
       </c>
       <c r="N20" s="1">
-        <v>-7.2421027662876555e-06</v>
+        <v>-7.1855654498169131e-06</v>
       </c>
       <c r="O20" s="1">
-        <v>-1.4047001323023962e-05</v>
+        <v>-1.3957878594015977e-05</v>
       </c>
       <c r="P20" s="1">
-        <v>-1.7384593485986147e-05</v>
+        <v>-1.7426828043496914e-05</v>
       </c>
       <c r="Q20" s="1">
-        <v>-7.4385127250660918e-06</v>
+        <v>-7.3291514156983826e-06</v>
       </c>
       <c r="R20" s="1">
-        <v>-5.1980929152087674e-06</v>
+        <v>-5.1150034474709898e-06</v>
       </c>
       <c r="S20" s="1">
-        <v>-6.7764967184588356e-06</v>
+        <v>-6.6692999145303537e-06</v>
       </c>
       <c r="T20" s="1">
-        <v>-8.4199229896414647e-06</v>
+        <v>-8.2673731535228287e-06</v>
       </c>
       <c r="U20" s="1">
-        <v>0.0006020663349981159</v>
+        <v>0.00060165323535360169</v>
       </c>
       <c r="V20" s="1">
-        <v>4.4478867116107097e-05</v>
+        <v>4.4547701167516686e-05</v>
       </c>
       <c r="W20" s="1">
-        <v>-3.5161675315452794e-05</v>
+        <v>-3.6338329204074811e-05</v>
       </c>
     </row>
     <row r="21">
@@ -1762,70 +1762,70 @@
         <v>42</v>
       </c>
       <c r="B21" s="1">
-        <v>0.015122736924974485</v>
+        <v>0.016393098490702487</v>
       </c>
       <c r="C21" s="1">
-        <v>1.2209756840042442e-06</v>
+        <v>1.1828212784639151e-06</v>
       </c>
       <c r="D21" s="1">
-        <v>3.6579077506735717e-07</v>
+        <v>2.9574604515451896e-07</v>
       </c>
       <c r="E21" s="1">
-        <v>5.973093367326624e-07</v>
+        <v>5.0687182970802388e-07</v>
       </c>
       <c r="F21" s="1">
-        <v>-1.2441434262836421e-08</v>
+        <v>-1.1538434135244887e-08</v>
       </c>
       <c r="G21" s="1">
-        <v>1.0729346708445609e-05</v>
+        <v>1.0221043622181648e-05</v>
       </c>
       <c r="H21" s="1">
-        <v>-4.2739003591800623e-06</v>
+        <v>1.4039326074559113e-06</v>
       </c>
       <c r="I21" s="1">
-        <v>-7.2406530507970393e-08</v>
+        <v>-6.1874923908773538e-08</v>
       </c>
       <c r="J21" s="1">
-        <v>3.8876887080584521e-07</v>
+        <v>2.8609900653638784e-07</v>
       </c>
       <c r="K21" s="1">
-        <v>1.3314176161533297e-06</v>
+        <v>1.0962343440291996e-06</v>
       </c>
       <c r="L21" s="1">
-        <v>1.5109422661962023e-05</v>
+        <v>-2.8537422348930768e-06</v>
       </c>
       <c r="M21" s="1">
-        <v>1.8766594716098065e-07</v>
+        <v>2.0941684284322803e-07</v>
       </c>
       <c r="N21" s="1">
-        <v>-1.0170283716604918e-06</v>
+        <v>-9.3705729008939815e-07</v>
       </c>
       <c r="O21" s="1">
-        <v>-1.288644188473316e-05</v>
+        <v>-1.2791385780241081e-05</v>
       </c>
       <c r="P21" s="1">
-        <v>-1.3465600376704758e-05</v>
+        <v>-1.3416685542518499e-05</v>
       </c>
       <c r="Q21" s="1">
-        <v>-1.1562596408892125e-05</v>
+        <v>-1.1468608560269498e-05</v>
       </c>
       <c r="R21" s="1">
-        <v>-6.6767548082805252e-06</v>
+        <v>-6.6391128771455318e-06</v>
       </c>
       <c r="S21" s="1">
-        <v>-8.0050299612204422e-06</v>
+        <v>-7.9033658621684457e-06</v>
       </c>
       <c r="T21" s="1">
-        <v>-1.1338849708603201e-05</v>
+        <v>-1.1287715049396718e-05</v>
       </c>
       <c r="U21" s="1">
-        <v>4.4478867116107097e-05</v>
+        <v>4.4547701167516686e-05</v>
       </c>
       <c r="V21" s="1">
-        <v>0.00068523396011376165</v>
+        <v>0.00068690364875784637</v>
       </c>
       <c r="W21" s="1">
-        <v>-3.2440750565771326e-05</v>
+        <v>-3.0377565460694786e-05</v>
       </c>
     </row>
     <row r="22">
@@ -1833,70 +1833,70 @@
         <v>43</v>
       </c>
       <c r="B22" s="1">
-        <v>-2.0200010370972508</v>
+        <v>-1.9382625623365031</v>
       </c>
       <c r="C22" s="1">
-        <v>-0.0012330088038144972</v>
+        <v>-0.0011886594020446141</v>
       </c>
       <c r="D22" s="1">
-        <v>-0.00020973896094931071</v>
+        <v>-0.00021497861891994373</v>
       </c>
       <c r="E22" s="1">
-        <v>-0.00031832107696344787</v>
+        <v>-0.00032278124532339865</v>
       </c>
       <c r="F22" s="1">
-        <v>3.0742413399562382e-06</v>
+        <v>3.1200288304482765e-06</v>
       </c>
       <c r="G22" s="1">
-        <v>-0.0018671512810167063</v>
+        <v>-0.0018725550922736329</v>
       </c>
       <c r="H22" s="1">
-        <v>-0.0017518716524618325</v>
+        <v>-0.0016440967270642329</v>
       </c>
       <c r="I22" s="1">
-        <v>3.9732815692934975e-05</v>
+        <v>3.9822789489834008e-05</v>
       </c>
       <c r="J22" s="1">
-        <v>3.4332521095418317e-05</v>
+        <v>3.2508610719808493e-05</v>
       </c>
       <c r="K22" s="1">
-        <v>0.0002256817482865712</v>
+        <v>0.00023362734683500424</v>
       </c>
       <c r="L22" s="1">
-        <v>-0.0011178327009573024</v>
+        <v>-0.00082115879604104276</v>
       </c>
       <c r="M22" s="1">
-        <v>-0.0056190133460342915</v>
+        <v>-0.005622985317533323</v>
       </c>
       <c r="N22" s="1">
-        <v>-0.005679488957244334</v>
+        <v>-0.0056828050509451656</v>
       </c>
       <c r="O22" s="1">
-        <v>-0.005786070279192603</v>
+        <v>-0.0057897399482080714</v>
       </c>
       <c r="P22" s="1">
-        <v>-0.0060906509371926355</v>
+        <v>-0.0060949660660578981</v>
       </c>
       <c r="Q22" s="1">
-        <v>-0.00020601899621545792</v>
+        <v>-0.00020819360861913365</v>
       </c>
       <c r="R22" s="1">
-        <v>-0.00022112132880905565</v>
+        <v>-0.00022326346847679335</v>
       </c>
       <c r="S22" s="1">
-        <v>-0.00017878775190088614</v>
+        <v>-0.00018222568965863394</v>
       </c>
       <c r="T22" s="1">
-        <v>-0.00022270813499721906</v>
+        <v>-0.00022563509149006831</v>
       </c>
       <c r="U22" s="1">
-        <v>-3.5161675315452794e-05</v>
+        <v>-3.6338329204074811e-05</v>
       </c>
       <c r="V22" s="1">
-        <v>-3.2440750565771326e-05</v>
+        <v>-3.0377565460694786e-05</v>
       </c>
       <c r="W22" s="1">
-        <v>0.013507156704364117</v>
+        <v>0.013611100023547595</v>
       </c>
     </row>
   </sheetData>
@@ -1984,70 +1984,70 @@
         <v>23</v>
       </c>
       <c r="B2" s="1">
-        <v>-1.9012715433431546</v>
+        <v>-1.8268501501730756</v>
       </c>
       <c r="C2" s="1">
-        <v>0.0010245586865211772</v>
+        <v>0.0010595190030253583</v>
       </c>
       <c r="D2" s="1">
-        <v>0.00011486954653393276</v>
+        <v>0.00011510522441073493</v>
       </c>
       <c r="E2" s="1">
-        <v>4.4462731297296688e-05</v>
+        <v>4.2275626930874772e-05</v>
       </c>
       <c r="F2" s="1">
-        <v>-4.4239583946529032e-07</v>
+        <v>-4.1839594960781217e-07</v>
       </c>
       <c r="G2" s="1">
-        <v>2.6486099356725311e-06</v>
+        <v>-4.5174365938964228e-06</v>
       </c>
       <c r="H2" s="1">
-        <v>-0.00019516119061429839</v>
+        <v>-9.9037390918094289e-05</v>
       </c>
       <c r="I2" s="1">
-        <v>-5.6128192862334818e-07</v>
+        <v>-4.2932334597557755e-07</v>
       </c>
       <c r="J2" s="1">
-        <v>3.0840952584200057e-06</v>
+        <v>1.321494402496611e-06</v>
       </c>
       <c r="K2" s="1">
-        <v>2.9287076880373222e-05</v>
+        <v>3.2430563078716926e-05</v>
       </c>
       <c r="L2" s="1">
-        <v>0.00011485363005445752</v>
+        <v>-0.0002058067230055862</v>
       </c>
       <c r="M2" s="1">
-        <v>-8.1831053955984303e-06</v>
+        <v>-8.3318607135270204e-06</v>
       </c>
       <c r="N2" s="1">
-        <v>8.3757245336108692e-07</v>
+        <v>-6.5875711980137568e-08</v>
       </c>
       <c r="O2" s="1">
-        <v>8.7989291899335663e-06</v>
+        <v>7.8650465857802842e-06</v>
       </c>
       <c r="P2" s="1">
-        <v>-2.990138706347159e-06</v>
+        <v>-4.5975823345647485e-06</v>
       </c>
       <c r="Q2" s="1">
-        <v>1.418359549836592e-06</v>
+        <v>1.4266481875186667e-06</v>
       </c>
       <c r="R2" s="1">
-        <v>-4.5750497250612499e-06</v>
+        <v>-4.0573417468842996e-06</v>
       </c>
       <c r="S2" s="1">
-        <v>-1.0961822349113866e-06</v>
+        <v>-6.5594393620895463e-07</v>
       </c>
       <c r="T2" s="1">
-        <v>-3.5048309644787845e-06</v>
+        <v>-2.9766305396855075e-06</v>
       </c>
       <c r="U2" s="1">
-        <v>8.8621898141114849e-06</v>
+        <v>7.1232668792709928e-06</v>
       </c>
       <c r="V2" s="1">
-        <v>5.8721384599528764e-06</v>
+        <v>6.5015778228314949e-06</v>
       </c>
       <c r="W2" s="1">
-        <v>-0.0010983983549437441</v>
+        <v>-0.0010554178067847199</v>
       </c>
     </row>
     <row r="3">
@@ -2055,70 +2055,70 @@
         <v>24</v>
       </c>
       <c r="B3" s="1">
-        <v>-2.4294177807329245</v>
+        <v>-2.432562622874793</v>
       </c>
       <c r="C3" s="1">
-        <v>0.00011486954653393276</v>
+        <v>0.00011510522441073493</v>
       </c>
       <c r="D3" s="1">
-        <v>0.0002114845821799663</v>
+        <v>0.00021157918583865104</v>
       </c>
       <c r="E3" s="1">
-        <v>8.1456514179892803e-06</v>
+        <v>8.3838691461603984e-06</v>
       </c>
       <c r="F3" s="1">
-        <v>-8.7675601118908529e-08</v>
+        <v>-9.0522807586081059e-08</v>
       </c>
       <c r="G3" s="1">
-        <v>-8.729476417917802e-06</v>
+        <v>-8.4782354866225207e-06</v>
       </c>
       <c r="H3" s="1">
-        <v>-4.8978051623428355e-06</v>
+        <v>-1.6856349610104561e-05</v>
       </c>
       <c r="I3" s="1">
-        <v>-5.7836030587521971e-07</v>
+        <v>-5.8242625218920034e-07</v>
       </c>
       <c r="J3" s="1">
-        <v>-9.6508230468583607e-07</v>
+        <v>-7.3669917124850944e-07</v>
       </c>
       <c r="K3" s="1">
-        <v>3.6089045134832794e-05</v>
+        <v>3.5644039171861406e-05</v>
       </c>
       <c r="L3" s="1">
-        <v>-3.0030239178656138e-05</v>
+        <v>2.4877812622206022e-06</v>
       </c>
       <c r="M3" s="1">
-        <v>-2.5671027398462573e-06</v>
+        <v>-2.5014634903634483e-06</v>
       </c>
       <c r="N3" s="1">
-        <v>6.7907975910040604e-06</v>
+        <v>6.8868976888263104e-06</v>
       </c>
       <c r="O3" s="1">
-        <v>2.1174173330711869e-05</v>
+        <v>2.1249343137661798e-05</v>
       </c>
       <c r="P3" s="1">
-        <v>2.5269662176656692e-05</v>
+        <v>2.544153472354195e-05</v>
       </c>
       <c r="Q3" s="1">
-        <v>7.2324730301555572e-06</v>
+        <v>7.1507093732333864e-06</v>
       </c>
       <c r="R3" s="1">
-        <v>4.8776483707620862e-06</v>
+        <v>4.7826660039098756e-06</v>
       </c>
       <c r="S3" s="1">
-        <v>5.3134129646330062e-06</v>
+        <v>5.2056130435637417e-06</v>
       </c>
       <c r="T3" s="1">
-        <v>7.9730480868482949e-06</v>
+        <v>7.8669895559767371e-06</v>
       </c>
       <c r="U3" s="1">
-        <v>8.3597404896726454e-06</v>
+        <v>8.4989849641290425e-06</v>
       </c>
       <c r="V3" s="1">
-        <v>-5.3359079183417881e-08</v>
+        <v>-2.6676239598258193e-07</v>
       </c>
       <c r="W3" s="1">
-        <v>-0.00025431523758683071</v>
+        <v>-0.00025830921369182809</v>
       </c>
     </row>
     <row r="4">
@@ -2126,70 +2126,70 @@
         <v>25</v>
       </c>
       <c r="B4" s="1">
-        <v>0.095736621570155916</v>
+        <v>0.090915985608924083</v>
       </c>
       <c r="C4" s="1">
-        <v>4.4462731297296688e-05</v>
+        <v>4.2275626930874772e-05</v>
       </c>
       <c r="D4" s="1">
-        <v>8.1456514179892803e-06</v>
+        <v>8.3838691461603984e-06</v>
       </c>
       <c r="E4" s="1">
-        <v>1.2431171030016836e-05</v>
+        <v>1.2632299607253099e-05</v>
       </c>
       <c r="F4" s="1">
-        <v>-1.1905185802961222e-07</v>
+        <v>-1.2097148452980088e-07</v>
       </c>
       <c r="G4" s="1">
-        <v>6.3457471596722908e-05</v>
+        <v>6.4047472776704781e-05</v>
       </c>
       <c r="H4" s="1">
-        <v>7.1182310774366281e-05</v>
+        <v>6.7087330278745505e-05</v>
       </c>
       <c r="I4" s="1">
-        <v>-1.3762098138907267e-06</v>
+        <v>-1.3869063741790183e-06</v>
       </c>
       <c r="J4" s="1">
-        <v>-1.4720985067300983e-06</v>
+        <v>-1.4065038606064748e-06</v>
       </c>
       <c r="K4" s="1">
-        <v>-1.5246932166012995e-05</v>
+        <v>-1.563401723263831e-05</v>
       </c>
       <c r="L4" s="1">
-        <v>4.1364575931215315e-05</v>
+        <v>3.3470517017792988e-05</v>
       </c>
       <c r="M4" s="1">
-        <v>-2.9042713630381036e-07</v>
+        <v>-3.288418739779477e-07</v>
       </c>
       <c r="N4" s="1">
-        <v>2.783673910759801e-06</v>
+        <v>2.7748099660967676e-06</v>
       </c>
       <c r="O4" s="1">
-        <v>3.4051277630257844e-06</v>
+        <v>3.383482557613705e-06</v>
       </c>
       <c r="P4" s="1">
-        <v>1.3876309071699441e-05</v>
+        <v>1.3850144464894418e-05</v>
       </c>
       <c r="Q4" s="1">
-        <v>1.1472485664569099e-07</v>
+        <v>2.1172909201144521e-07</v>
       </c>
       <c r="R4" s="1">
-        <v>-6.4923327093227776e-07</v>
+        <v>-5.4674310256688788e-07</v>
       </c>
       <c r="S4" s="1">
-        <v>-9.7683301282093545e-07</v>
+        <v>-8.3945386239513907e-07</v>
       </c>
       <c r="T4" s="1">
-        <v>-5.0455676659458948e-07</v>
+        <v>-3.725717720619174e-07</v>
       </c>
       <c r="U4" s="1">
-        <v>1.1399644501848614e-06</v>
+        <v>1.2703234694176648e-06</v>
       </c>
       <c r="V4" s="1">
-        <v>1.5627989592159134e-06</v>
+        <v>1.5125950993133345e-06</v>
       </c>
       <c r="W4" s="1">
-        <v>-0.00029222372958148847</v>
+        <v>-0.00029703520739172268</v>
       </c>
     </row>
     <row r="5">
@@ -2197,70 +2197,70 @@
         <v>26</v>
       </c>
       <c r="B5" s="1">
-        <v>-0.0013490240087094935</v>
+        <v>-0.0012960986902199976</v>
       </c>
       <c r="C5" s="1">
-        <v>-4.4239583946529032e-07</v>
+        <v>-4.1839594960781217e-07</v>
       </c>
       <c r="D5" s="1">
-        <v>-8.7675601118908529e-08</v>
+        <v>-9.0522807586081059e-08</v>
       </c>
       <c r="E5" s="1">
-        <v>-1.1905185802961222e-07</v>
+        <v>-1.2097148452980088e-07</v>
       </c>
       <c r="F5" s="1">
-        <v>1.2514307598159177e-09</v>
+        <v>1.2702863255356179e-09</v>
       </c>
       <c r="G5" s="1">
-        <v>-2.0625154269026654e-07</v>
+        <v>-2.0935502149047645e-07</v>
       </c>
       <c r="H5" s="1">
-        <v>-2.9950151572076373e-07</v>
+        <v>-2.4968324554798258e-07</v>
       </c>
       <c r="I5" s="1">
-        <v>4.1260839425535964e-09</v>
+        <v>4.1855202013851316e-09</v>
       </c>
       <c r="J5" s="1">
-        <v>5.2949202950672547e-09</v>
+        <v>4.4844863223764972e-09</v>
       </c>
       <c r="K5" s="1">
-        <v>1.2618209673935297e-07</v>
+        <v>1.2922383495880879e-07</v>
       </c>
       <c r="L5" s="1">
-        <v>-4.2212831271636065e-07</v>
+        <v>-3.5370929304461633e-07</v>
       </c>
       <c r="M5" s="1">
-        <v>7.7317263633481679e-10</v>
+        <v>1.1439456125808309e-09</v>
       </c>
       <c r="N5" s="1">
-        <v>-3.6853829897446372e-08</v>
+        <v>-3.6773853689195695e-08</v>
       </c>
       <c r="O5" s="1">
-        <v>-2.3451531396040429e-08</v>
+        <v>-2.3355900910179328e-08</v>
       </c>
       <c r="P5" s="1">
-        <v>-1.0640548256306794e-07</v>
+        <v>-1.059280717983693e-07</v>
       </c>
       <c r="Q5" s="1">
-        <v>-6.0164197236917718e-09</v>
+        <v>-6.9446599575316849e-09</v>
       </c>
       <c r="R5" s="1">
-        <v>2.4614601352711343e-09</v>
+        <v>1.4831178916618642e-09</v>
       </c>
       <c r="S5" s="1">
-        <v>8.2969542685938928e-09</v>
+        <v>6.9538663253764381e-09</v>
       </c>
       <c r="T5" s="1">
-        <v>5.4690094933689386e-09</v>
+        <v>4.2157849949445075e-09</v>
       </c>
       <c r="U5" s="1">
-        <v>-1.2346020759130981e-08</v>
+        <v>-1.3713343024618199e-08</v>
       </c>
       <c r="V5" s="1">
-        <v>-1.8537433937113033e-08</v>
+        <v>-1.7970225794690034e-08</v>
       </c>
       <c r="W5" s="1">
-        <v>2.5654461132350549e-06</v>
+        <v>2.6101551615602842e-06</v>
       </c>
     </row>
     <row r="6">
@@ -2268,70 +2268,70 @@
         <v>27</v>
       </c>
       <c r="B6" s="1">
-        <v>0.29002206800520536</v>
+        <v>0.28083957336957405</v>
       </c>
       <c r="C6" s="1">
-        <v>2.6486099356725311e-06</v>
+        <v>-4.5174365938964228e-06</v>
       </c>
       <c r="D6" s="1">
-        <v>-8.729476417917802e-06</v>
+        <v>-8.4782354866225207e-06</v>
       </c>
       <c r="E6" s="1">
-        <v>6.3457471596722908e-05</v>
+        <v>6.4047472776704781e-05</v>
       </c>
       <c r="F6" s="1">
-        <v>-2.0625154269026654e-07</v>
+        <v>-2.0935502149047645e-07</v>
       </c>
       <c r="G6" s="1">
-        <v>0.0028320856786104793</v>
+        <v>0.0028491583355227997</v>
       </c>
       <c r="H6" s="1">
-        <v>0.0022741989305192921</v>
+        <v>0.0022824582437404729</v>
       </c>
       <c r="I6" s="1">
-        <v>-5.7240654029085312e-05</v>
+        <v>-5.7549132339546576e-05</v>
       </c>
       <c r="J6" s="1">
-        <v>-4.6036469797819249e-05</v>
+        <v>-4.6210048488498054e-05</v>
       </c>
       <c r="K6" s="1">
-        <v>3.5577438384185752e-05</v>
+        <v>3.3000792806911459e-05</v>
       </c>
       <c r="L6" s="1">
-        <v>9.494552062322859e-05</v>
+        <v>5.7091140232838497e-05</v>
       </c>
       <c r="M6" s="1">
-        <v>-4.7978680778055626e-06</v>
+        <v>-4.6179040938884586e-06</v>
       </c>
       <c r="N6" s="1">
-        <v>-1.2581961039308362e-05</v>
+        <v>-1.2389563447444971e-05</v>
       </c>
       <c r="O6" s="1">
-        <v>-2.0480352189340429e-05</v>
+        <v>-2.0201016634859904e-05</v>
       </c>
       <c r="P6" s="1">
-        <v>2.7892074583767612e-05</v>
+        <v>2.9014332503549383e-05</v>
       </c>
       <c r="Q6" s="1">
-        <v>-1.1533539992736011e-05</v>
+        <v>-1.1481380313973904e-05</v>
       </c>
       <c r="R6" s="1">
-        <v>-6.7184118269996321e-06</v>
+        <v>-6.3356340882747317e-06</v>
       </c>
       <c r="S6" s="1">
-        <v>-1.4132035989311953e-05</v>
+        <v>-1.4225367649214302e-05</v>
       </c>
       <c r="T6" s="1">
-        <v>2.4104364669811815e-06</v>
+        <v>2.5148972496513776e-06</v>
       </c>
       <c r="U6" s="1">
-        <v>2.1702695458857383e-05</v>
+        <v>2.152657109205947e-05</v>
       </c>
       <c r="V6" s="1">
-        <v>3.197009236947987e-05</v>
+        <v>3.1723533872784327e-05</v>
       </c>
       <c r="W6" s="1">
-        <v>-0.0025832682564928939</v>
+        <v>-0.0026038372942152684</v>
       </c>
     </row>
     <row r="7">
@@ -2339,70 +2339,70 @@
         <v>28</v>
       </c>
       <c r="B7" s="1">
-        <v>-0.52258088661868518</v>
+        <v>-0.33238435150496093</v>
       </c>
       <c r="C7" s="1">
-        <v>-0.00019516119061429839</v>
+        <v>-9.9037390918094289e-05</v>
       </c>
       <c r="D7" s="1">
-        <v>-4.8978051623428355e-06</v>
+        <v>-1.6856349610104561e-05</v>
       </c>
       <c r="E7" s="1">
-        <v>7.1182310774366281e-05</v>
+        <v>6.7087330278745505e-05</v>
       </c>
       <c r="F7" s="1">
-        <v>-2.9950151572076373e-07</v>
+        <v>-2.4968324554798258e-07</v>
       </c>
       <c r="G7" s="1">
-        <v>0.0022741989305192921</v>
+        <v>0.0022824582437404729</v>
       </c>
       <c r="H7" s="1">
-        <v>0.004335204607186679</v>
+        <v>0.0046612325732375663</v>
       </c>
       <c r="I7" s="1">
-        <v>-4.6264032354337535e-05</v>
+        <v>-4.6362960258342244e-05</v>
       </c>
       <c r="J7" s="1">
-        <v>-8.6739429634051301e-05</v>
+        <v>-9.2693137547534331e-05</v>
       </c>
       <c r="K7" s="1">
-        <v>3.1411157731783873e-05</v>
+        <v>3.9679741716525036e-05</v>
       </c>
       <c r="L7" s="1">
-        <v>-0.00085197540636089712</v>
+        <v>-0.0010242370918795006</v>
       </c>
       <c r="M7" s="1">
-        <v>1.4384846084298424e-05</v>
+        <v>1.7422719216543862e-05</v>
       </c>
       <c r="N7" s="1">
-        <v>2.2824608958703406e-06</v>
+        <v>5.1059922726100389e-06</v>
       </c>
       <c r="O7" s="1">
-        <v>-2.6649756888729977e-06</v>
+        <v>6.0699219609405743e-07</v>
       </c>
       <c r="P7" s="1">
-        <v>5.429518397526915e-05</v>
+        <v>6.1891300780379127e-05</v>
       </c>
       <c r="Q7" s="1">
-        <v>-3.6690232187340375e-05</v>
+        <v>-3.6192099519415558e-05</v>
       </c>
       <c r="R7" s="1">
-        <v>-1.3893893935755346e-05</v>
+        <v>-1.327848981164745e-05</v>
       </c>
       <c r="S7" s="1">
-        <v>-3.0082870674029078e-05</v>
+        <v>-3.0375346445064592e-05</v>
       </c>
       <c r="T7" s="1">
-        <v>1.0052562919968829e-05</v>
+        <v>1.1321164600858695e-05</v>
       </c>
       <c r="U7" s="1">
-        <v>2.5935118247703372e-05</v>
+        <v>2.1224202453490372e-05</v>
       </c>
       <c r="V7" s="1">
-        <v>1.2322822344190829e-05</v>
+        <v>1.6810562377383834e-05</v>
       </c>
       <c r="W7" s="1">
-        <v>-0.0027283472661895143</v>
+        <v>-0.0026686146061493123</v>
       </c>
     </row>
     <row r="8">
@@ -2410,70 +2410,70 @@
         <v>29</v>
       </c>
       <c r="B8" s="1">
-        <v>-0.0010293943321120747</v>
+        <v>-0.00085057731051817664</v>
       </c>
       <c r="C8" s="1">
-        <v>-5.6128192862334818e-07</v>
+        <v>-4.2932334597557755e-07</v>
       </c>
       <c r="D8" s="1">
-        <v>-5.7836030587521971e-07</v>
+        <v>-5.8242625218920034e-07</v>
       </c>
       <c r="E8" s="1">
-        <v>-1.3762098138907267e-06</v>
+        <v>-1.3869063741790183e-06</v>
       </c>
       <c r="F8" s="1">
-        <v>4.1260839425535964e-09</v>
+        <v>4.1855202013851316e-09</v>
       </c>
       <c r="G8" s="1">
-        <v>-5.7240654029085312e-05</v>
+        <v>-5.7549132339546576e-05</v>
       </c>
       <c r="H8" s="1">
-        <v>-4.6264032354337535e-05</v>
+        <v>-4.6362960258342244e-05</v>
       </c>
       <c r="I8" s="1">
-        <v>1.2747962322676888e-06</v>
+        <v>1.2798726768696547e-06</v>
       </c>
       <c r="J8" s="1">
-        <v>1.0336192838809502e-06</v>
+        <v>1.0354767679874452e-06</v>
       </c>
       <c r="K8" s="1">
-        <v>-5.3683877950533271e-07</v>
+        <v>-4.8989370758689251e-07</v>
       </c>
       <c r="L8" s="1">
-        <v>-1.715068383229114e-06</v>
+        <v>-1.1020928418889117e-06</v>
       </c>
       <c r="M8" s="1">
-        <v>9.0360889151584929e-08</v>
+        <v>8.5886717330922524e-08</v>
       </c>
       <c r="N8" s="1">
-        <v>4.2514068329513915e-07</v>
+        <v>4.1922518109911971e-07</v>
       </c>
       <c r="O8" s="1">
-        <v>1.0464058484313692e-06</v>
+        <v>1.0366521136565462e-06</v>
       </c>
       <c r="P8" s="1">
-        <v>3.7961348574689442e-07</v>
+        <v>3.5615619050687953e-07</v>
       </c>
       <c r="Q8" s="1">
-        <v>8.2546436280187431e-08</v>
+        <v>8.1895241450170067e-08</v>
       </c>
       <c r="R8" s="1">
-        <v>1.4202754417214848e-07</v>
+        <v>1.3508808191349195e-07</v>
       </c>
       <c r="S8" s="1">
-        <v>1.5103166766703517e-07</v>
+        <v>1.5314358421516996e-07</v>
       </c>
       <c r="T8" s="1">
-        <v>6.4417671425438404e-11</v>
+        <v>-1.5842281852845159e-09</v>
       </c>
       <c r="U8" s="1">
-        <v>-3.7052220080687125e-07</v>
+        <v>-3.6745960787801338e-07</v>
       </c>
       <c r="V8" s="1">
-        <v>-5.2676947358348086e-07</v>
+        <v>-5.2182016222927964e-07</v>
       </c>
       <c r="W8" s="1">
-        <v>5.202091678840161e-05</v>
+        <v>5.2406698980636378e-05</v>
       </c>
     </row>
     <row r="9">
@@ -2481,70 +2481,70 @@
         <v>30</v>
       </c>
       <c r="B9" s="1">
-        <v>0.011532680378518402</v>
+        <v>0.0080874241740541072</v>
       </c>
       <c r="C9" s="1">
-        <v>3.0840952584200057e-06</v>
+        <v>1.321494402496611e-06</v>
       </c>
       <c r="D9" s="1">
-        <v>-9.6508230468583607e-07</v>
+        <v>-7.3669917124850944e-07</v>
       </c>
       <c r="E9" s="1">
-        <v>-1.4720985067300983e-06</v>
+        <v>-1.4065038606064748e-06</v>
       </c>
       <c r="F9" s="1">
-        <v>5.2949202950672547e-09</v>
+        <v>4.4844863223764972e-09</v>
       </c>
       <c r="G9" s="1">
-        <v>-4.6036469797819249e-05</v>
+        <v>-4.6210048488498054e-05</v>
       </c>
       <c r="H9" s="1">
-        <v>-8.6739429634051301e-05</v>
+        <v>-9.2693137547534331e-05</v>
       </c>
       <c r="I9" s="1">
-        <v>1.0336192838809502e-06</v>
+        <v>1.0354767679874452e-06</v>
       </c>
       <c r="J9" s="1">
-        <v>1.9723576540599469e-06</v>
+        <v>2.0826817125743639e-06</v>
       </c>
       <c r="K9" s="1">
-        <v>1.5130116569842105e-08</v>
+        <v>-1.0708057342544892e-07</v>
       </c>
       <c r="L9" s="1">
-        <v>1.5781748692477806e-05</v>
+        <v>1.8615294606862919e-05</v>
       </c>
       <c r="M9" s="1">
-        <v>-4.1341291585408416e-07</v>
+        <v>-4.631627292953052e-07</v>
       </c>
       <c r="N9" s="1">
-        <v>2.5034828064415815e-07</v>
+        <v>2.0561052418220679e-07</v>
       </c>
       <c r="O9" s="1">
-        <v>1.0069633202529128e-06</v>
+        <v>9.5666328646536975e-07</v>
       </c>
       <c r="P9" s="1">
-        <v>2.3916688383191385e-07</v>
+        <v>1.1368910822147471e-07</v>
       </c>
       <c r="Q9" s="1">
-        <v>3.5244097223112287e-07</v>
+        <v>3.435344702962418e-07</v>
       </c>
       <c r="R9" s="1">
-        <v>2.0745952692423794e-07</v>
+        <v>1.9545849693844811e-07</v>
       </c>
       <c r="S9" s="1">
-        <v>1.0291383990149633e-07</v>
+        <v>1.0785612600802441e-07</v>
       </c>
       <c r="T9" s="1">
-        <v>-5.2069376460769636e-07</v>
+        <v>-5.446268964349836e-07</v>
       </c>
       <c r="U9" s="1">
-        <v>-3.4687571972642342e-07</v>
+        <v>-2.6258017616135651e-07</v>
       </c>
       <c r="V9" s="1">
-        <v>-1.5879694057777503e-08</v>
+        <v>-9.6886472762624185e-08</v>
       </c>
       <c r="W9" s="1">
-        <v>5.3497155535246594e-05</v>
+        <v>5.2586470474824166e-05</v>
       </c>
     </row>
     <row r="10">
@@ -2552,70 +2552,70 @@
         <v>31</v>
       </c>
       <c r="B10" s="1">
-        <v>0.094788391822109797</v>
+        <v>0.095361985751672734</v>
       </c>
       <c r="C10" s="1">
-        <v>2.9287076880373222e-05</v>
+        <v>3.2430563078716926e-05</v>
       </c>
       <c r="D10" s="1">
-        <v>3.6089045134832794e-05</v>
+        <v>3.5644039171861406e-05</v>
       </c>
       <c r="E10" s="1">
-        <v>-1.5246932166012995e-05</v>
+        <v>-1.563401723263831e-05</v>
       </c>
       <c r="F10" s="1">
-        <v>1.2618209673935297e-07</v>
+        <v>1.2922383495880879e-07</v>
       </c>
       <c r="G10" s="1">
-        <v>3.5577438384185752e-05</v>
+        <v>3.3000792806911459e-05</v>
       </c>
       <c r="H10" s="1">
-        <v>3.1411157731783873e-05</v>
+        <v>3.9679741716525036e-05</v>
       </c>
       <c r="I10" s="1">
-        <v>-5.3683877950533271e-07</v>
+        <v>-4.8989370758689251e-07</v>
       </c>
       <c r="J10" s="1">
-        <v>1.5130116569842105e-08</v>
+        <v>-1.0708057342544892e-07</v>
       </c>
       <c r="K10" s="1">
-        <v>0.00026954353798823975</v>
+        <v>0.00027091324825128922</v>
       </c>
       <c r="L10" s="1">
-        <v>-4.3499082238004084e-05</v>
+        <v>-4.5960192870050985e-05</v>
       </c>
       <c r="M10" s="1">
-        <v>-3.5596067716509743e-06</v>
+        <v>-3.3997585887278708e-06</v>
       </c>
       <c r="N10" s="1">
-        <v>-1.2219199791975057e-05</v>
+        <v>-1.2184396624705386e-05</v>
       </c>
       <c r="O10" s="1">
-        <v>-1.6603055110125072e-05</v>
+        <v>-1.6240768286287922e-05</v>
       </c>
       <c r="P10" s="1">
-        <v>-1.3307436847531686e-05</v>
+        <v>-1.3008530014251178e-05</v>
       </c>
       <c r="Q10" s="1">
-        <v>3.619221005362895e-06</v>
+        <v>3.3159510649391313e-06</v>
       </c>
       <c r="R10" s="1">
-        <v>3.8604986917157608e-06</v>
+        <v>3.9550658782637565e-06</v>
       </c>
       <c r="S10" s="1">
-        <v>-2.3528696799529254e-06</v>
+        <v>-2.6670268528999865e-06</v>
       </c>
       <c r="T10" s="1">
-        <v>3.5218691613598335e-06</v>
+        <v>3.4161505258312362e-06</v>
       </c>
       <c r="U10" s="1">
-        <v>2.2253493842377868e-06</v>
+        <v>1.6329331867519496e-06</v>
       </c>
       <c r="V10" s="1">
-        <v>5.0220430512963217e-06</v>
+        <v>4.6057638523645746e-06</v>
       </c>
       <c r="W10" s="1">
-        <v>0.00021763482056469854</v>
+        <v>0.00022835663284615957</v>
       </c>
     </row>
     <row r="11">
@@ -2623,70 +2623,70 @@
         <v>32</v>
       </c>
       <c r="B11" s="1">
-        <v>-0.75990169542638331</v>
+        <v>-0.90772271484316924</v>
       </c>
       <c r="C11" s="1">
-        <v>0.00011485363005445752</v>
+        <v>-0.0002058067230055862</v>
       </c>
       <c r="D11" s="1">
-        <v>-3.0030239178656138e-05</v>
+        <v>2.4877812622206022e-06</v>
       </c>
       <c r="E11" s="1">
-        <v>4.1364575931215315e-05</v>
+        <v>3.3470517017792988e-05</v>
       </c>
       <c r="F11" s="1">
-        <v>-4.2212831271636065e-07</v>
+        <v>-3.5370929304461633e-07</v>
       </c>
       <c r="G11" s="1">
-        <v>9.494552062322859e-05</v>
+        <v>5.7091140232838497e-05</v>
       </c>
       <c r="H11" s="1">
-        <v>-0.00085197540636089712</v>
+        <v>-0.0010242370918795006</v>
       </c>
       <c r="I11" s="1">
-        <v>-1.715068383229114e-06</v>
+        <v>-1.1020928418889117e-06</v>
       </c>
       <c r="J11" s="1">
-        <v>1.5781748692477806e-05</v>
+        <v>1.8615294606862919e-05</v>
       </c>
       <c r="K11" s="1">
-        <v>-4.3499082238004084e-05</v>
+        <v>-4.5960192870050985e-05</v>
       </c>
       <c r="L11" s="1">
-        <v>0.008191651783558105</v>
+        <v>0.0037620625257864079</v>
       </c>
       <c r="M11" s="1">
-        <v>-1.0588475748229509e-05</v>
+        <v>-9.1262855069901272e-06</v>
       </c>
       <c r="N11" s="1">
-        <v>-8.1960887204834618e-06</v>
+        <v>-4.9771657460124315e-06</v>
       </c>
       <c r="O11" s="1">
-        <v>-4.8339761371643574e-06</v>
+        <v>-2.7704626009684389e-06</v>
       </c>
       <c r="P11" s="1">
-        <v>-2.9238300895993784e-06</v>
+        <v>-8.6291668334251823e-06</v>
       </c>
       <c r="Q11" s="1">
-        <v>-6.2256024842299172e-06</v>
+        <v>-5.2649060319684455e-06</v>
       </c>
       <c r="R11" s="1">
-        <v>-2.6087041758414092e-06</v>
+        <v>-1.3790383762453034e-06</v>
       </c>
       <c r="S11" s="1">
-        <v>-1.9676499004460388e-06</v>
+        <v>-3.396625038331445e-07</v>
       </c>
       <c r="T11" s="1">
-        <v>-7.144508944303271e-07</v>
+        <v>5.9649518845548608e-08</v>
       </c>
       <c r="U11" s="1">
-        <v>7.1057984517335621e-06</v>
+        <v>1.713885512262643e-05</v>
       </c>
       <c r="V11" s="1">
-        <v>2.8667155208742676e-06</v>
+        <v>-3.5125612236070241e-06</v>
       </c>
       <c r="W11" s="1">
-        <v>-0.00089901271810866273</v>
+        <v>-0.00068623586667491249</v>
       </c>
     </row>
     <row r="12">
@@ -2694,70 +2694,70 @@
         <v>33</v>
       </c>
       <c r="B12" s="1">
-        <v>0.33069790080692624</v>
+        <v>0.3318700125312451</v>
       </c>
       <c r="C12" s="1">
-        <v>-8.1831053955984303e-06</v>
+        <v>-8.3318607135270204e-06</v>
       </c>
       <c r="D12" s="1">
-        <v>-2.5671027398462573e-06</v>
+        <v>-2.5014634903634483e-06</v>
       </c>
       <c r="E12" s="1">
-        <v>-2.9042713630381036e-07</v>
+        <v>-3.288418739779477e-07</v>
       </c>
       <c r="F12" s="1">
-        <v>7.7317263633481679e-10</v>
+        <v>1.1439456125808309e-09</v>
       </c>
       <c r="G12" s="1">
-        <v>-4.7978680778055626e-06</v>
+        <v>-4.6179040938884586e-06</v>
       </c>
       <c r="H12" s="1">
-        <v>1.4384846084298424e-05</v>
+        <v>1.7422719216543862e-05</v>
       </c>
       <c r="I12" s="1">
-        <v>9.0360889151584929e-08</v>
+        <v>8.5886717330922524e-08</v>
       </c>
       <c r="J12" s="1">
-        <v>-4.1341291585408416e-07</v>
+        <v>-4.631627292953052e-07</v>
       </c>
       <c r="K12" s="1">
-        <v>-3.5596067716509743e-06</v>
+        <v>-3.3997585887278708e-06</v>
       </c>
       <c r="L12" s="1">
-        <v>-1.0588475748229509e-05</v>
+        <v>-9.1262855069901272e-06</v>
       </c>
       <c r="M12" s="1">
-        <v>0.0043567988705918541</v>
+        <v>0.0043511206374305554</v>
       </c>
       <c r="N12" s="1">
-        <v>0.0038472106926365985</v>
+        <v>0.0038418415525775292</v>
       </c>
       <c r="O12" s="1">
-        <v>0.0038441904401582431</v>
+        <v>0.0038387996919326097</v>
       </c>
       <c r="P12" s="1">
-        <v>0.0038414293420322805</v>
+        <v>0.0038360567734635194</v>
       </c>
       <c r="Q12" s="1">
-        <v>3.5560028920604428e-07</v>
+        <v>3.1017900878349287e-07</v>
       </c>
       <c r="R12" s="1">
-        <v>5.4341302991553925e-06</v>
+        <v>5.6374451354898158e-06</v>
       </c>
       <c r="S12" s="1">
-        <v>3.1399886148356505e-06</v>
+        <v>3.0245656729448362e-06</v>
       </c>
       <c r="T12" s="1">
-        <v>-1.9096844517154906e-06</v>
+        <v>-1.9795025279182199e-06</v>
       </c>
       <c r="U12" s="1">
-        <v>-8.7428123848013825e-07</v>
+        <v>-8.8476075686785125e-07</v>
       </c>
       <c r="V12" s="1">
-        <v>1.3192201966005016e-05</v>
+        <v>1.3404696272107716e-05</v>
       </c>
       <c r="W12" s="1">
-        <v>-0.003829995812902626</v>
+        <v>-0.0038238282309933486</v>
       </c>
     </row>
     <row r="13">
@@ -2765,70 +2765,70 @@
         <v>34</v>
       </c>
       <c r="B13" s="1">
-        <v>0.76299180376116338</v>
+        <v>0.76326666284586153</v>
       </c>
       <c r="C13" s="1">
-        <v>8.3757245336108692e-07</v>
+        <v>-6.5875711980137568e-08</v>
       </c>
       <c r="D13" s="1">
-        <v>6.7907975910040604e-06</v>
+        <v>6.8868976888263104e-06</v>
       </c>
       <c r="E13" s="1">
-        <v>2.783673910759801e-06</v>
+        <v>2.7748099660967676e-06</v>
       </c>
       <c r="F13" s="1">
-        <v>-3.6853829897446372e-08</v>
+        <v>-3.6773853689195695e-08</v>
       </c>
       <c r="G13" s="1">
-        <v>-1.2581961039308362e-05</v>
+        <v>-1.2389563447444971e-05</v>
       </c>
       <c r="H13" s="1">
-        <v>2.2824608958703406e-06</v>
+        <v>5.1059922726100389e-06</v>
       </c>
       <c r="I13" s="1">
-        <v>4.2514068329513915e-07</v>
+        <v>4.1922518109911971e-07</v>
       </c>
       <c r="J13" s="1">
-        <v>2.5034828064415815e-07</v>
+        <v>2.0561052418220679e-07</v>
       </c>
       <c r="K13" s="1">
-        <v>-1.2219199791975057e-05</v>
+        <v>-1.2184396624705386e-05</v>
       </c>
       <c r="L13" s="1">
-        <v>-8.1960887204834618e-06</v>
+        <v>-4.9771657460124315e-06</v>
       </c>
       <c r="M13" s="1">
-        <v>0.0038472106926365985</v>
+        <v>0.0038418415525775292</v>
       </c>
       <c r="N13" s="1">
-        <v>0.003991470127029188</v>
+        <v>0.0039859220539116601</v>
       </c>
       <c r="O13" s="1">
-        <v>0.0038473451940205898</v>
+        <v>0.0038419319820217242</v>
       </c>
       <c r="P13" s="1">
-        <v>0.0038457585624049571</v>
+        <v>0.0038402941201298546</v>
       </c>
       <c r="Q13" s="1">
-        <v>4.8680844114887663e-06</v>
+        <v>4.7823172556741065e-06</v>
       </c>
       <c r="R13" s="1">
-        <v>5.5991654326465433e-06</v>
+        <v>5.7332046613249094e-06</v>
       </c>
       <c r="S13" s="1">
-        <v>1.663722132621862e-06</v>
+        <v>1.5207776639583067e-06</v>
       </c>
       <c r="T13" s="1">
-        <v>-8.3696857423744655e-07</v>
+        <v>-9.3504788716647174e-07</v>
       </c>
       <c r="U13" s="1">
-        <v>-6.0628540737891058e-07</v>
+        <v>-4.9372881140356169e-07</v>
       </c>
       <c r="V13" s="1">
-        <v>7.3046328287541918e-06</v>
+        <v>7.5560271931183288e-06</v>
       </c>
       <c r="W13" s="1">
-        <v>-0.0038917445178012029</v>
+        <v>-0.0038861505337287358</v>
       </c>
     </row>
     <row r="14">
@@ -2836,70 +2836,70 @@
         <v>35</v>
       </c>
       <c r="B14" s="1">
-        <v>0.94536965873628676</v>
+        <v>0.9455573227459142</v>
       </c>
       <c r="C14" s="1">
-        <v>8.7989291899335663e-06</v>
+        <v>7.8650465857802842e-06</v>
       </c>
       <c r="D14" s="1">
-        <v>2.1174173330711869e-05</v>
+        <v>2.1249343137661798e-05</v>
       </c>
       <c r="E14" s="1">
-        <v>3.4051277630257844e-06</v>
+        <v>3.383482557613705e-06</v>
       </c>
       <c r="F14" s="1">
-        <v>-2.3451531396040429e-08</v>
+        <v>-2.3355900910179328e-08</v>
       </c>
       <c r="G14" s="1">
-        <v>-2.0480352189340429e-05</v>
+        <v>-2.0201016634859904e-05</v>
       </c>
       <c r="H14" s="1">
-        <v>-2.6649756888729977e-06</v>
+        <v>6.0699219609405743e-07</v>
       </c>
       <c r="I14" s="1">
-        <v>1.0464058484313692e-06</v>
+        <v>1.0366521136565462e-06</v>
       </c>
       <c r="J14" s="1">
-        <v>1.0069633202529128e-06</v>
+        <v>9.5666328646536975e-07</v>
       </c>
       <c r="K14" s="1">
-        <v>-1.6603055110125072e-05</v>
+        <v>-1.6240768286287922e-05</v>
       </c>
       <c r="L14" s="1">
-        <v>-4.8339761371643574e-06</v>
+        <v>-2.7704626009684389e-06</v>
       </c>
       <c r="M14" s="1">
-        <v>0.0038441904401582431</v>
+        <v>0.0038387996919326097</v>
       </c>
       <c r="N14" s="1">
-        <v>0.0038473451940205898</v>
+        <v>0.0038419319820217242</v>
       </c>
       <c r="O14" s="1">
-        <v>0.0039526234007165881</v>
+        <v>0.0039468744352068354</v>
       </c>
       <c r="P14" s="1">
-        <v>0.0038970952052159004</v>
+        <v>0.0038909498994385773</v>
       </c>
       <c r="Q14" s="1">
-        <v>9.3333607300665318e-06</v>
+        <v>9.3162650213201464e-06</v>
       </c>
       <c r="R14" s="1">
-        <v>7.9732898268856895e-06</v>
+        <v>8.1789526961005728e-06</v>
       </c>
       <c r="S14" s="1">
-        <v>4.1099163075669905e-06</v>
+        <v>4.0311266399494248e-06</v>
       </c>
       <c r="T14" s="1">
-        <v>6.0052442935864392e-06</v>
+        <v>5.9575126782893589e-06</v>
       </c>
       <c r="U14" s="1">
-        <v>-8.0973246843234579e-06</v>
+        <v>-8.0488162323827237e-06</v>
       </c>
       <c r="V14" s="1">
-        <v>-3.9605288332886624e-06</v>
+        <v>-3.7632534379072447e-06</v>
       </c>
       <c r="W14" s="1">
-        <v>-0.0039934308509347967</v>
+        <v>-0.0039873174286424893</v>
       </c>
     </row>
     <row r="15">
@@ -2907,70 +2907,70 @@
         <v>36</v>
       </c>
       <c r="B15" s="1">
-        <v>0.94498307324631392</v>
+        <v>0.94690466581029209</v>
       </c>
       <c r="C15" s="1">
-        <v>-2.990138706347159e-06</v>
+        <v>-4.5975823345647485e-06</v>
       </c>
       <c r="D15" s="1">
-        <v>2.5269662176656692e-05</v>
+        <v>2.544153472354195e-05</v>
       </c>
       <c r="E15" s="1">
-        <v>1.3876309071699441e-05</v>
+        <v>1.3850144464894418e-05</v>
       </c>
       <c r="F15" s="1">
-        <v>-1.0640548256306794e-07</v>
+        <v>-1.059280717983693e-07</v>
       </c>
       <c r="G15" s="1">
-        <v>2.7892074583767612e-05</v>
+        <v>2.9014332503549383e-05</v>
       </c>
       <c r="H15" s="1">
-        <v>5.429518397526915e-05</v>
+        <v>6.1891300780379127e-05</v>
       </c>
       <c r="I15" s="1">
-        <v>3.7961348574689442e-07</v>
+        <v>3.5615619050687953e-07</v>
       </c>
       <c r="J15" s="1">
-        <v>2.3916688383191385e-07</v>
+        <v>1.1368910822147471e-07</v>
       </c>
       <c r="K15" s="1">
-        <v>-1.3307436847531686e-05</v>
+        <v>-1.3008530014251178e-05</v>
       </c>
       <c r="L15" s="1">
-        <v>-2.9238300895993784e-06</v>
+        <v>-8.6291668334251823e-06</v>
       </c>
       <c r="M15" s="1">
-        <v>0.0038414293420322805</v>
+        <v>0.0038360567734635194</v>
       </c>
       <c r="N15" s="1">
-        <v>0.0038457585624049571</v>
+        <v>0.0038402941201298546</v>
       </c>
       <c r="O15" s="1">
-        <v>0.0038970952052159004</v>
+        <v>0.0038909498994385773</v>
       </c>
       <c r="P15" s="1">
-        <v>0.004178179901333008</v>
+        <v>0.0041748063666035423</v>
       </c>
       <c r="Q15" s="1">
-        <v>1.0650287444814995e-05</v>
+        <v>1.0710573270249966e-05</v>
       </c>
       <c r="R15" s="1">
-        <v>1.364845000328293e-05</v>
+        <v>1.3869398288809362e-05</v>
       </c>
       <c r="S15" s="1">
-        <v>3.1615756989559742e-06</v>
+        <v>3.1938911720362121e-06</v>
       </c>
       <c r="T15" s="1">
-        <v>8.8632784227656367e-06</v>
+        <v>8.9733935158993472e-06</v>
       </c>
       <c r="U15" s="1">
-        <v>-8.0015896798785656e-06</v>
+        <v>-7.8672676236313699e-06</v>
       </c>
       <c r="V15" s="1">
-        <v>-1.1302984719672084e-06</v>
+        <v>-8.7336383132878659e-07</v>
       </c>
       <c r="W15" s="1">
-        <v>-0.0043210913901136445</v>
+        <v>-0.0043160653025450775</v>
       </c>
     </row>
     <row r="16">
@@ -2978,70 +2978,70 @@
         <v>37</v>
       </c>
       <c r="B16" s="1">
-        <v>0.060725494854189009</v>
+        <v>0.060167542453961997</v>
       </c>
       <c r="C16" s="1">
-        <v>1.418359549836592e-06</v>
+        <v>1.4266481875186667e-06</v>
       </c>
       <c r="D16" s="1">
-        <v>7.2324730301555572e-06</v>
+        <v>7.1507093732333864e-06</v>
       </c>
       <c r="E16" s="1">
-        <v>1.1472485664569099e-07</v>
+        <v>2.1172909201144521e-07</v>
       </c>
       <c r="F16" s="1">
-        <v>-6.0164197236917718e-09</v>
+        <v>-6.9446599575316849e-09</v>
       </c>
       <c r="G16" s="1">
-        <v>-1.1533539992736011e-05</v>
+        <v>-1.1481380313973904e-05</v>
       </c>
       <c r="H16" s="1">
-        <v>-3.6690232187340375e-05</v>
+        <v>-3.6192099519415558e-05</v>
       </c>
       <c r="I16" s="1">
-        <v>8.2546436280187431e-08</v>
+        <v>8.1895241450170067e-08</v>
       </c>
       <c r="J16" s="1">
-        <v>3.5244097223112287e-07</v>
+        <v>3.435344702962418e-07</v>
       </c>
       <c r="K16" s="1">
-        <v>3.619221005362895e-06</v>
+        <v>3.3159510649391313e-06</v>
       </c>
       <c r="L16" s="1">
-        <v>-6.2256024842299172e-06</v>
+        <v>-5.2649060319684455e-06</v>
       </c>
       <c r="M16" s="1">
-        <v>3.5560028920604428e-07</v>
+        <v>3.1017900878349287e-07</v>
       </c>
       <c r="N16" s="1">
-        <v>4.8680844114887663e-06</v>
+        <v>4.7823172556741065e-06</v>
       </c>
       <c r="O16" s="1">
-        <v>9.3333607300665318e-06</v>
+        <v>9.3162650213201464e-06</v>
       </c>
       <c r="P16" s="1">
-        <v>1.0650287444814995e-05</v>
+        <v>1.0710573270249966e-05</v>
       </c>
       <c r="Q16" s="1">
-        <v>0.00047297082196416781</v>
+        <v>0.00047468264290596775</v>
       </c>
       <c r="R16" s="1">
-        <v>0.00022309574520860062</v>
+        <v>0.00022410311536021904</v>
       </c>
       <c r="S16" s="1">
-        <v>0.00022343446316894455</v>
+        <v>0.00022442915575729443</v>
       </c>
       <c r="T16" s="1">
-        <v>0.00022316203686080022</v>
+        <v>0.00022415198818720675</v>
       </c>
       <c r="U16" s="1">
-        <v>-9.8353735670421816e-06</v>
+        <v>-9.8086004207196043e-06</v>
       </c>
       <c r="V16" s="1">
-        <v>-1.0866319601751711e-05</v>
+        <v>-1.0752076587793361e-05</v>
       </c>
       <c r="W16" s="1">
-        <v>-0.00021726096828956137</v>
+        <v>-0.00022033562253399036</v>
       </c>
     </row>
     <row r="17">
@@ -3049,70 +3049,70 @@
         <v>38</v>
       </c>
       <c r="B17" s="1">
-        <v>0.036206286313374005</v>
+        <v>0.035342828407649386</v>
       </c>
       <c r="C17" s="1">
-        <v>-4.5750497250612499e-06</v>
+        <v>-4.0573417468842996e-06</v>
       </c>
       <c r="D17" s="1">
-        <v>4.8776483707620862e-06</v>
+        <v>4.7826660039098756e-06</v>
       </c>
       <c r="E17" s="1">
-        <v>-6.4923327093227776e-07</v>
+        <v>-5.4674310256688788e-07</v>
       </c>
       <c r="F17" s="1">
-        <v>2.4614601352711343e-09</v>
+        <v>1.4831178916618642e-09</v>
       </c>
       <c r="G17" s="1">
-        <v>-6.7184118269996321e-06</v>
+        <v>-6.3356340882747317e-06</v>
       </c>
       <c r="H17" s="1">
-        <v>-1.3893893935755346e-05</v>
+        <v>-1.327848981164745e-05</v>
       </c>
       <c r="I17" s="1">
-        <v>1.4202754417214848e-07</v>
+        <v>1.3508808191349195e-07</v>
       </c>
       <c r="J17" s="1">
-        <v>2.0745952692423794e-07</v>
+        <v>1.9545849693844811e-07</v>
       </c>
       <c r="K17" s="1">
-        <v>3.8604986917157608e-06</v>
+        <v>3.9550658782637565e-06</v>
       </c>
       <c r="L17" s="1">
-        <v>-2.6087041758414092e-06</v>
+        <v>-1.3790383762453034e-06</v>
       </c>
       <c r="M17" s="1">
-        <v>5.4341302991553925e-06</v>
+        <v>5.6374451354898158e-06</v>
       </c>
       <c r="N17" s="1">
-        <v>5.5991654326465433e-06</v>
+        <v>5.7332046613249094e-06</v>
       </c>
       <c r="O17" s="1">
-        <v>7.9732898268856895e-06</v>
+        <v>8.1789526961005728e-06</v>
       </c>
       <c r="P17" s="1">
-        <v>1.364845000328293e-05</v>
+        <v>1.3869398288809362e-05</v>
       </c>
       <c r="Q17" s="1">
-        <v>0.00022309574520860062</v>
+        <v>0.00022410311536021904</v>
       </c>
       <c r="R17" s="1">
-        <v>0.00059704459981641401</v>
+        <v>0.00059855079971786831</v>
       </c>
       <c r="S17" s="1">
-        <v>0.00022259210244502994</v>
+        <v>0.00022358603052440479</v>
       </c>
       <c r="T17" s="1">
-        <v>0.00022274645601283731</v>
+        <v>0.00022375195382449007</v>
       </c>
       <c r="U17" s="1">
-        <v>-7.7376406627471683e-06</v>
+        <v>-7.7718756968409081e-06</v>
       </c>
       <c r="V17" s="1">
-        <v>-8.7891283260666343e-06</v>
+        <v>-8.8695122612203292e-06</v>
       </c>
       <c r="W17" s="1">
-        <v>-0.00020866579611457836</v>
+        <v>-0.00021235542586871091</v>
       </c>
     </row>
     <row r="18">
@@ -3120,70 +3120,70 @@
         <v>39</v>
       </c>
       <c r="B18" s="1">
-        <v>-0.0015145691752181105</v>
+        <v>-0.0026338451440598588</v>
       </c>
       <c r="C18" s="1">
-        <v>-1.0961822349113866e-06</v>
+        <v>-6.5594393620895463e-07</v>
       </c>
       <c r="D18" s="1">
-        <v>5.3134129646330062e-06</v>
+        <v>5.2056130435637417e-06</v>
       </c>
       <c r="E18" s="1">
-        <v>-9.7683301282093545e-07</v>
+        <v>-8.3945386239513907e-07</v>
       </c>
       <c r="F18" s="1">
-        <v>8.2969542685938928e-09</v>
+        <v>6.9538663253764381e-09</v>
       </c>
       <c r="G18" s="1">
-        <v>-1.4132035989311953e-05</v>
+        <v>-1.4225367649214302e-05</v>
       </c>
       <c r="H18" s="1">
-        <v>-3.0082870674029078e-05</v>
+        <v>-3.0375346445064592e-05</v>
       </c>
       <c r="I18" s="1">
-        <v>1.5103166766703517e-07</v>
+        <v>1.5314358421516996e-07</v>
       </c>
       <c r="J18" s="1">
-        <v>1.0291383990149633e-07</v>
+        <v>1.0785612600802441e-07</v>
       </c>
       <c r="K18" s="1">
-        <v>-2.3528696799529254e-06</v>
+        <v>-2.6670268528999865e-06</v>
       </c>
       <c r="L18" s="1">
-        <v>-1.9676499004460388e-06</v>
+        <v>-3.396625038331445e-07</v>
       </c>
       <c r="M18" s="1">
-        <v>3.1399886148356505e-06</v>
+        <v>3.0245656729448362e-06</v>
       </c>
       <c r="N18" s="1">
-        <v>1.663722132621862e-06</v>
+        <v>1.5207776639583067e-06</v>
       </c>
       <c r="O18" s="1">
-        <v>4.1099163075669905e-06</v>
+        <v>4.0311266399494248e-06</v>
       </c>
       <c r="P18" s="1">
-        <v>3.1615756989559742e-06</v>
+        <v>3.1938911720362121e-06</v>
       </c>
       <c r="Q18" s="1">
-        <v>0.00022343446316894455</v>
+        <v>0.00022442915575729443</v>
       </c>
       <c r="R18" s="1">
-        <v>0.00022259210244502994</v>
+        <v>0.00022358603052440479</v>
       </c>
       <c r="S18" s="1">
-        <v>0.00044825267173630824</v>
+        <v>0.00044987167601915278</v>
       </c>
       <c r="T18" s="1">
-        <v>0.0002230688414468972</v>
+        <v>0.00022405557634395292</v>
       </c>
       <c r="U18" s="1">
-        <v>-8.5480195642792384e-06</v>
+        <v>-8.4761660480621442e-06</v>
       </c>
       <c r="V18" s="1">
-        <v>-6.8397931108550721e-06</v>
+        <v>-6.7466046995897358e-06</v>
       </c>
       <c r="W18" s="1">
-        <v>-0.00019159392098928627</v>
+        <v>-0.00019551760752442566</v>
       </c>
     </row>
     <row r="19">
@@ -3191,70 +3191,70 @@
         <v>40</v>
       </c>
       <c r="B19" s="1">
-        <v>0.019659787009531134</v>
+        <v>0.01862662358345522</v>
       </c>
       <c r="C19" s="1">
-        <v>-3.5048309644787845e-06</v>
+        <v>-2.9766305396855075e-06</v>
       </c>
       <c r="D19" s="1">
-        <v>7.9730480868482949e-06</v>
+        <v>7.8669895559767371e-06</v>
       </c>
       <c r="E19" s="1">
-        <v>-5.0455676659458948e-07</v>
+        <v>-3.725717720619174e-07</v>
       </c>
       <c r="F19" s="1">
-        <v>5.4690094933689386e-09</v>
+        <v>4.2157849949445075e-09</v>
       </c>
       <c r="G19" s="1">
-        <v>2.4104364669811815e-06</v>
+        <v>2.5148972496513776e-06</v>
       </c>
       <c r="H19" s="1">
-        <v>1.0052562919968829e-05</v>
+        <v>1.1321164600858695e-05</v>
       </c>
       <c r="I19" s="1">
-        <v>6.4417671425438404e-11</v>
+        <v>-1.5842281852845159e-09</v>
       </c>
       <c r="J19" s="1">
-        <v>-5.2069376460769636e-07</v>
+        <v>-5.446268964349836e-07</v>
       </c>
       <c r="K19" s="1">
-        <v>3.5218691613598335e-06</v>
+        <v>3.4161505258312362e-06</v>
       </c>
       <c r="L19" s="1">
-        <v>-7.144508944303271e-07</v>
+        <v>5.9649518845548608e-08</v>
       </c>
       <c r="M19" s="1">
-        <v>-1.9096844517154906e-06</v>
+        <v>-1.9795025279182199e-06</v>
       </c>
       <c r="N19" s="1">
-        <v>-8.3696857423744655e-07</v>
+        <v>-9.3504788716647174e-07</v>
       </c>
       <c r="O19" s="1">
-        <v>6.0052442935864392e-06</v>
+        <v>5.9575126782893589e-06</v>
       </c>
       <c r="P19" s="1">
-        <v>8.8632784227656367e-06</v>
+        <v>8.9733935158993472e-06</v>
       </c>
       <c r="Q19" s="1">
-        <v>0.00022316203686080022</v>
+        <v>0.00022415198818720675</v>
       </c>
       <c r="R19" s="1">
-        <v>0.00022274645601283731</v>
+        <v>0.00022375195382449007</v>
       </c>
       <c r="S19" s="1">
-        <v>0.0002230688414468972</v>
+        <v>0.00022405557634395292</v>
       </c>
       <c r="T19" s="1">
-        <v>0.00031655121114231661</v>
+        <v>0.00031779019208659558</v>
       </c>
       <c r="U19" s="1">
-        <v>-8.4682335000051513e-06</v>
+        <v>-8.420610600675047e-06</v>
       </c>
       <c r="V19" s="1">
-        <v>-1.2638437704789798e-05</v>
+        <v>-1.2683386901865479e-05</v>
       </c>
       <c r="W19" s="1">
-        <v>-0.00021984221009061034</v>
+        <v>-0.00022393207456956798</v>
       </c>
     </row>
     <row r="20">
@@ -3262,70 +3262,70 @@
         <v>41</v>
       </c>
       <c r="B20" s="1">
-        <v>-0.059931205870817426</v>
+        <v>-0.064009100846551661</v>
       </c>
       <c r="C20" s="1">
-        <v>8.8621898141114849e-06</v>
+        <v>7.1232668792709928e-06</v>
       </c>
       <c r="D20" s="1">
-        <v>8.3597404896726454e-06</v>
+        <v>8.4989849641290425e-06</v>
       </c>
       <c r="E20" s="1">
-        <v>1.1399644501848614e-06</v>
+        <v>1.2703234694176648e-06</v>
       </c>
       <c r="F20" s="1">
-        <v>-1.2346020759130981e-08</v>
+        <v>-1.3713343024618199e-08</v>
       </c>
       <c r="G20" s="1">
-        <v>2.1702695458857383e-05</v>
+        <v>2.152657109205947e-05</v>
       </c>
       <c r="H20" s="1">
-        <v>2.5935118247703372e-05</v>
+        <v>2.1224202453490372e-05</v>
       </c>
       <c r="I20" s="1">
-        <v>-3.7052220080687125e-07</v>
+        <v>-3.6745960787801338e-07</v>
       </c>
       <c r="J20" s="1">
-        <v>-3.4687571972642342e-07</v>
+        <v>-2.6258017616135651e-07</v>
       </c>
       <c r="K20" s="1">
-        <v>2.2253493842377868e-06</v>
+        <v>1.6329331867519496e-06</v>
       </c>
       <c r="L20" s="1">
-        <v>7.1057984517335621e-06</v>
+        <v>1.713885512262643e-05</v>
       </c>
       <c r="M20" s="1">
-        <v>-8.7428123848013825e-07</v>
+        <v>-8.8476075686785125e-07</v>
       </c>
       <c r="N20" s="1">
-        <v>-6.0628540737891058e-07</v>
+        <v>-4.9372881140356169e-07</v>
       </c>
       <c r="O20" s="1">
-        <v>-8.0973246843234579e-06</v>
+        <v>-8.0488162323827237e-06</v>
       </c>
       <c r="P20" s="1">
-        <v>-8.0015896798785656e-06</v>
+        <v>-7.8672676236313699e-06</v>
       </c>
       <c r="Q20" s="1">
-        <v>-9.8353735670421816e-06</v>
+        <v>-9.8086004207196043e-06</v>
       </c>
       <c r="R20" s="1">
-        <v>-7.7376406627471683e-06</v>
+        <v>-7.7718756968409081e-06</v>
       </c>
       <c r="S20" s="1">
-        <v>-8.5480195642792384e-06</v>
+        <v>-8.4761660480621442e-06</v>
       </c>
       <c r="T20" s="1">
-        <v>-8.4682335000051513e-06</v>
+        <v>-8.420610600675047e-06</v>
       </c>
       <c r="U20" s="1">
-        <v>0.00062012992816027615</v>
+        <v>0.00061960665408207309</v>
       </c>
       <c r="V20" s="1">
-        <v>4.4869176530117395e-05</v>
+        <v>4.4987251248203471e-05</v>
       </c>
       <c r="W20" s="1">
-        <v>-6.3265097681833906e-05</v>
+        <v>-6.5819233992412578e-05</v>
       </c>
     </row>
     <row r="21">
@@ -3333,70 +3333,70 @@
         <v>42</v>
       </c>
       <c r="B21" s="1">
-        <v>0.019748573105030347</v>
+        <v>0.021385509720049236</v>
       </c>
       <c r="C21" s="1">
-        <v>5.8721384599528764e-06</v>
+        <v>6.5015778228314949e-06</v>
       </c>
       <c r="D21" s="1">
-        <v>-5.3359079183417881e-08</v>
+        <v>-2.6676239598258193e-07</v>
       </c>
       <c r="E21" s="1">
-        <v>1.5627989592159134e-06</v>
+        <v>1.5125950993133345e-06</v>
       </c>
       <c r="F21" s="1">
-        <v>-1.8537433937113033e-08</v>
+        <v>-1.7970225794690034e-08</v>
       </c>
       <c r="G21" s="1">
-        <v>3.197009236947987e-05</v>
+        <v>3.1723533872784327e-05</v>
       </c>
       <c r="H21" s="1">
-        <v>1.2322822344190829e-05</v>
+        <v>1.6810562377383834e-05</v>
       </c>
       <c r="I21" s="1">
-        <v>-5.2676947358348086e-07</v>
+        <v>-5.2182016222927964e-07</v>
       </c>
       <c r="J21" s="1">
-        <v>-1.5879694057777503e-08</v>
+        <v>-9.6886472762624185e-08</v>
       </c>
       <c r="K21" s="1">
-        <v>5.0220430512963217e-06</v>
+        <v>4.6057638523645746e-06</v>
       </c>
       <c r="L21" s="1">
-        <v>2.8667155208742676e-06</v>
+        <v>-3.5125612236070241e-06</v>
       </c>
       <c r="M21" s="1">
-        <v>1.3192201966005016e-05</v>
+        <v>1.3404696272107716e-05</v>
       </c>
       <c r="N21" s="1">
-        <v>7.3046328287541918e-06</v>
+        <v>7.5560271931183288e-06</v>
       </c>
       <c r="O21" s="1">
-        <v>-3.9605288332886624e-06</v>
+        <v>-3.7632534379072447e-06</v>
       </c>
       <c r="P21" s="1">
-        <v>-1.1302984719672084e-06</v>
+        <v>-8.7336383132878659e-07</v>
       </c>
       <c r="Q21" s="1">
-        <v>-1.0866319601751711e-05</v>
+        <v>-1.0752076587793361e-05</v>
       </c>
       <c r="R21" s="1">
-        <v>-8.7891283260666343e-06</v>
+        <v>-8.8695122612203292e-06</v>
       </c>
       <c r="S21" s="1">
-        <v>-6.8397931108550721e-06</v>
+        <v>-6.7466046995897358e-06</v>
       </c>
       <c r="T21" s="1">
-        <v>-1.2638437704789798e-05</v>
+        <v>-1.2683386901865479e-05</v>
       </c>
       <c r="U21" s="1">
-        <v>4.4869176530117395e-05</v>
+        <v>4.4987251248203471e-05</v>
       </c>
       <c r="V21" s="1">
-        <v>0.00068728571712486626</v>
+        <v>0.00069076990866549987</v>
       </c>
       <c r="W21" s="1">
-        <v>-7.4078561737904e-05</v>
+        <v>-7.3201939868701373e-05</v>
       </c>
     </row>
     <row r="22">
@@ -3404,70 +3404,70 @@
         <v>43</v>
       </c>
       <c r="B22" s="1">
-        <v>-1.0066340535771257</v>
+        <v>-0.90724461444443261</v>
       </c>
       <c r="C22" s="1">
-        <v>-0.0010983983549437441</v>
+        <v>-0.0010554178067847199</v>
       </c>
       <c r="D22" s="1">
-        <v>-0.00025431523758683071</v>
+        <v>-0.00025830921369182809</v>
       </c>
       <c r="E22" s="1">
-        <v>-0.00029222372958148847</v>
+        <v>-0.00029703520739172268</v>
       </c>
       <c r="F22" s="1">
-        <v>2.5654461132350549e-06</v>
+        <v>2.6101551615602842e-06</v>
       </c>
       <c r="G22" s="1">
-        <v>-0.0025832682564928939</v>
+        <v>-0.0026038372942152684</v>
       </c>
       <c r="H22" s="1">
-        <v>-0.0027283472661895143</v>
+        <v>-0.0026686146061493123</v>
       </c>
       <c r="I22" s="1">
-        <v>5.202091678840161e-05</v>
+        <v>5.2406698980636378e-05</v>
       </c>
       <c r="J22" s="1">
-        <v>5.3497155535246594e-05</v>
+        <v>5.2586470474824166e-05</v>
       </c>
       <c r="K22" s="1">
-        <v>0.00021763482056469854</v>
+        <v>0.00022835663284615957</v>
       </c>
       <c r="L22" s="1">
-        <v>-0.00089901271810866273</v>
+        <v>-0.00068623586667491249</v>
       </c>
       <c r="M22" s="1">
-        <v>-0.003829995812902626</v>
+        <v>-0.0038238282309933486</v>
       </c>
       <c r="N22" s="1">
-        <v>-0.0038917445178012029</v>
+        <v>-0.0038861505337287358</v>
       </c>
       <c r="O22" s="1">
-        <v>-0.0039934308509347967</v>
+        <v>-0.0039873174286424893</v>
       </c>
       <c r="P22" s="1">
-        <v>-0.0043210913901136445</v>
+        <v>-0.0043160653025450775</v>
       </c>
       <c r="Q22" s="1">
-        <v>-0.00021726096828956137</v>
+        <v>-0.00022033562253399036</v>
       </c>
       <c r="R22" s="1">
-        <v>-0.00020866579611457836</v>
+        <v>-0.00021235542586871091</v>
       </c>
       <c r="S22" s="1">
-        <v>-0.00019159392098928627</v>
+        <v>-0.00019551760752442566</v>
       </c>
       <c r="T22" s="1">
-        <v>-0.00021984221009061034</v>
+        <v>-0.00022393207456956798</v>
       </c>
       <c r="U22" s="1">
-        <v>-6.3265097681833906e-05</v>
+        <v>-6.5819233992412578e-05</v>
       </c>
       <c r="V22" s="1">
-        <v>-7.4078561737904e-05</v>
+        <v>-7.3201939868701373e-05</v>
       </c>
       <c r="W22" s="1">
-        <v>0.011760232947161491</v>
+        <v>0.011872625690148547</v>
       </c>
     </row>
   </sheetData>
@@ -3549,64 +3549,64 @@
         <v>25</v>
       </c>
       <c r="B2" s="1">
-        <v>0.20369824396595762</v>
+        <v>0.20358612527669204</v>
       </c>
       <c r="C2" s="1">
-        <v>2.8737941674710454e-05</v>
+        <v>2.8964784122995246e-05</v>
       </c>
       <c r="D2" s="1">
-        <v>-3.0348176135874831e-07</v>
+        <v>-3.0580467134593472e-07</v>
       </c>
       <c r="E2" s="1">
-        <v>8.677357756237655e-05</v>
+        <v>8.6570398627609484e-05</v>
       </c>
       <c r="F2" s="1">
-        <v>5.9169724810349146e-05</v>
+        <v>5.2129335873587252e-05</v>
       </c>
       <c r="G2" s="1">
-        <v>-1.9861440151884924e-06</v>
+        <v>-1.9819709365491699e-06</v>
       </c>
       <c r="H2" s="1">
-        <v>-1.2257315410143131e-06</v>
+        <v>-1.0922089954529246e-06</v>
       </c>
       <c r="I2" s="1">
-        <v>-3.3771728766285646e-05</v>
+        <v>-3.4134927642802412e-05</v>
       </c>
       <c r="J2" s="1">
-        <v>0.00016245249783464706</v>
+        <v>0.00015335924095357114</v>
       </c>
       <c r="K2" s="1">
-        <v>-1.6912700878659356e-06</v>
+        <v>-1.5233378905525699e-06</v>
       </c>
       <c r="L2" s="1">
-        <v>-1.5467360083312763e-07</v>
+        <v>-9.9392082172600778e-08</v>
       </c>
       <c r="M2" s="1">
-        <v>3.0024752055162007e-06</v>
+        <v>3.0609956068016349e-06</v>
       </c>
       <c r="N2" s="1">
-        <v>2.3564747247100602e-05</v>
+        <v>2.3669135991962073e-05</v>
       </c>
       <c r="O2" s="1">
-        <v>1.6094093233746959e-06</v>
+        <v>1.6659843237926481e-06</v>
       </c>
       <c r="P2" s="1">
-        <v>3.0349993587210175e-06</v>
+        <v>2.8324372475920348e-06</v>
       </c>
       <c r="Q2" s="1">
-        <v>-5.2024808409682079e-07</v>
+        <v>-6.7628240789441789e-07</v>
       </c>
       <c r="R2" s="1">
-        <v>1.2384904953898715e-06</v>
+        <v>1.237706220488573e-06</v>
       </c>
       <c r="S2" s="1">
-        <v>-3.0482203558139592e-07</v>
+        <v>-3.4344712248334343e-07</v>
       </c>
       <c r="T2" s="1">
-        <v>-3.8224410691735699e-07</v>
+        <v>-3.1367662316262897e-07</v>
       </c>
       <c r="U2" s="1">
-        <v>-0.00060684416927367824</v>
+        <v>-0.00061200641855181897</v>
       </c>
     </row>
     <row r="3">
@@ -3614,64 +3614,64 @@
         <v>26</v>
       </c>
       <c r="B3" s="1">
-        <v>-0.0023176093645823487</v>
+        <v>-0.0023156515483605754</v>
       </c>
       <c r="C3" s="1">
-        <v>-3.0348176135874831e-07</v>
+        <v>-3.0580467134593472e-07</v>
       </c>
       <c r="D3" s="1">
-        <v>3.3892622616450745e-09</v>
+        <v>3.4129259810495867e-09</v>
       </c>
       <c r="E3" s="1">
-        <v>-2.8622376892096605e-07</v>
+        <v>-2.8464500255247345e-07</v>
       </c>
       <c r="F3" s="1">
-        <v>2.332002794011421e-08</v>
+        <v>1.0177569243912585e-07</v>
       </c>
       <c r="G3" s="1">
-        <v>5.7885930128179303e-09</v>
+        <v>5.7569391201166895e-09</v>
       </c>
       <c r="H3" s="1">
-        <v>-2.6185270367090687e-09</v>
+        <v>-4.1038185897197249e-09</v>
       </c>
       <c r="I3" s="1">
-        <v>3.6442518821678374e-07</v>
+        <v>3.6583856479650831e-07</v>
       </c>
       <c r="J3" s="1">
-        <v>-1.77084472741687e-06</v>
+        <v>-1.6943995622860904e-06</v>
       </c>
       <c r="K3" s="1">
-        <v>1.2323010252592635e-08</v>
+        <v>1.0601793888727325e-08</v>
       </c>
       <c r="L3" s="1">
-        <v>-3.2701818241622779e-09</v>
+        <v>-3.6218258816888244e-09</v>
       </c>
       <c r="M3" s="1">
-        <v>-2.827533447014885e-09</v>
+        <v>-3.1574773190429262e-09</v>
       </c>
       <c r="N3" s="1">
-        <v>-1.7331909746317233e-07</v>
+        <v>-1.7427429355495081e-07</v>
       </c>
       <c r="O3" s="1">
-        <v>-2.8197301434058223e-08</v>
+        <v>-2.8689040382927587e-08</v>
       </c>
       <c r="P3" s="1">
-        <v>-3.8141043026444714e-08</v>
+        <v>-3.5904737921844196e-08</v>
       </c>
       <c r="Q3" s="1">
-        <v>-1.6553094017191181e-09</v>
+        <v>1.5600019607145327e-10</v>
       </c>
       <c r="R3" s="1">
-        <v>-1.9240633809598504e-08</v>
+        <v>-1.9172918102372577e-08</v>
       </c>
       <c r="S3" s="1">
-        <v>-7.5720705575493119e-09</v>
+        <v>-7.1492419486544743e-09</v>
       </c>
       <c r="T3" s="1">
-        <v>-8.3438751008559219e-09</v>
+        <v>-9.1257546332900786e-09</v>
       </c>
       <c r="U3" s="1">
-        <v>6.0371289373614472e-06</v>
+        <v>6.0917971620748798e-06</v>
       </c>
     </row>
     <row r="4">
@@ -3679,64 +3679,64 @@
         <v>27</v>
       </c>
       <c r="B4" s="1">
-        <v>-0.071283414903192982</v>
+        <v>-0.069631136514065939</v>
       </c>
       <c r="C4" s="1">
-        <v>8.677357756237655e-05</v>
+        <v>8.6570398627609484e-05</v>
       </c>
       <c r="D4" s="1">
-        <v>-2.8622376892096605e-07</v>
+        <v>-2.8464500255247345e-07</v>
       </c>
       <c r="E4" s="1">
-        <v>0.0043867685213062691</v>
+        <v>0.0043827963740232</v>
       </c>
       <c r="F4" s="1">
-        <v>0.0027720761826640797</v>
+        <v>0.0027853079877335298</v>
       </c>
       <c r="G4" s="1">
-        <v>-9.4776599753100944e-05</v>
+        <v>-9.4694105812187339e-05</v>
       </c>
       <c r="H4" s="1">
-        <v>-6.1428736339675603e-05</v>
+        <v>-6.1673713642238596e-05</v>
       </c>
       <c r="I4" s="1">
-        <v>4.4272909069806078e-05</v>
+        <v>4.2010889188431096e-05</v>
       </c>
       <c r="J4" s="1">
-        <v>0.00027929043868713004</v>
+        <v>1.4169869399275121e-05</v>
       </c>
       <c r="K4" s="1">
-        <v>-2.6046522225714296e-05</v>
+        <v>-2.6245457904309255e-05</v>
       </c>
       <c r="L4" s="1">
-        <v>-4.0235605142481213e-05</v>
+        <v>-3.9907356854963279e-05</v>
       </c>
       <c r="M4" s="1">
-        <v>-6.6026515134199641e-05</v>
+        <v>-6.5652081200321113e-05</v>
       </c>
       <c r="N4" s="1">
-        <v>3.1510682439981649e-05</v>
+        <v>3.1234573519444785e-05</v>
       </c>
       <c r="O4" s="1">
-        <v>-4.2966282962757997e-05</v>
+        <v>-4.264205578565715e-05</v>
       </c>
       <c r="P4" s="1">
-        <v>9.7973997462779777e-06</v>
+        <v>9.841506540567862e-06</v>
       </c>
       <c r="Q4" s="1">
-        <v>-2.6807256883508815e-05</v>
+        <v>-2.6669148530096986e-05</v>
       </c>
       <c r="R4" s="1">
-        <v>1.4520984424207412e-05</v>
+        <v>1.4657307388924741e-05</v>
       </c>
       <c r="S4" s="1">
-        <v>2.4478330441287561e-05</v>
+        <v>2.46575133178336e-05</v>
       </c>
       <c r="T4" s="1">
-        <v>1.5154765880496575e-05</v>
+        <v>1.5160437654607358e-05</v>
       </c>
       <c r="U4" s="1">
-        <v>-0.0032637360017151937</v>
+        <v>-0.0032563749952316716</v>
       </c>
     </row>
     <row r="5">
@@ -3744,64 +3744,64 @@
         <v>28</v>
       </c>
       <c r="B5" s="1">
-        <v>-0.45972963612297119</v>
+        <v>-0.48650677601574277</v>
       </c>
       <c r="C5" s="1">
-        <v>5.9169724810349146e-05</v>
+        <v>5.2129335873587252e-05</v>
       </c>
       <c r="D5" s="1">
-        <v>2.332002794011421e-08</v>
+        <v>1.0177569243912585e-07</v>
       </c>
       <c r="E5" s="1">
-        <v>0.0027720761826640797</v>
+        <v>0.0027853079877335298</v>
       </c>
       <c r="F5" s="1">
-        <v>0.017638526470621241</v>
+        <v>0.017859624277633528</v>
       </c>
       <c r="G5" s="1">
-        <v>-6.1638011190242345e-05</v>
+        <v>-6.1890543663410208e-05</v>
       </c>
       <c r="H5" s="1">
-        <v>-0.0003487282588254355</v>
+        <v>-0.00035298626832795801</v>
       </c>
       <c r="I5" s="1">
-        <v>8.8867118570551951e-05</v>
+        <v>9.2180585165848491e-05</v>
       </c>
       <c r="J5" s="1">
-        <v>-0.0079065982410055583</v>
+        <v>-0.0068847852549692203</v>
       </c>
       <c r="K5" s="1">
-        <v>-4.12190760621055e-05</v>
+        <v>-4.1186044527889746e-05</v>
       </c>
       <c r="L5" s="1">
-        <v>-0.00011763104351105015</v>
+        <v>-0.00011840914115454313</v>
       </c>
       <c r="M5" s="1">
-        <v>-0.00015251328066123783</v>
+        <v>-0.00015383107882074003</v>
       </c>
       <c r="N5" s="1">
-        <v>-1.9373521742390359e-05</v>
+        <v>-2.0307089815686085e-05</v>
       </c>
       <c r="O5" s="1">
-        <v>-0.00012801075056115242</v>
+        <v>-0.00012274071322981118</v>
       </c>
       <c r="P5" s="1">
-        <v>-2.3788951772339656e-05</v>
+        <v>-1.6224786243510909e-05</v>
       </c>
       <c r="Q5" s="1">
-        <v>-7.3878591633196982e-05</v>
+        <v>-6.5799348859331747e-05</v>
       </c>
       <c r="R5" s="1">
-        <v>-3.4129443930021857e-06</v>
+        <v>-1.9992086739724271e-06</v>
       </c>
       <c r="S5" s="1">
-        <v>2.8550948870025924e-05</v>
+        <v>2.5469325078479404e-05</v>
       </c>
       <c r="T5" s="1">
-        <v>-1.0395554965158991e-06</v>
+        <v>-4.0480593922532691e-06</v>
       </c>
       <c r="U5" s="1">
-        <v>-0.002623908505282331</v>
+        <v>-0.0024819177313509513</v>
       </c>
     </row>
     <row r="6">
@@ -3809,64 +3809,64 @@
         <v>29</v>
       </c>
       <c r="B6" s="1">
-        <v>-0.0016305020629435061</v>
+        <v>-0.0016648951574605578</v>
       </c>
       <c r="C6" s="1">
-        <v>-1.9861440151884924e-06</v>
+        <v>-1.9819709365491699e-06</v>
       </c>
       <c r="D6" s="1">
-        <v>5.7885930128179303e-09</v>
+        <v>5.7569391201166895e-09</v>
       </c>
       <c r="E6" s="1">
-        <v>-9.4776599753100944e-05</v>
+        <v>-9.4694105812187339e-05</v>
       </c>
       <c r="F6" s="1">
-        <v>-6.1638011190242345e-05</v>
+        <v>-6.1890543663410208e-05</v>
       </c>
       <c r="G6" s="1">
-        <v>2.2264660795643104e-06</v>
+        <v>2.224704167373146e-06</v>
       </c>
       <c r="H6" s="1">
-        <v>1.4910385479872448e-06</v>
+        <v>1.4956624640466632e-06</v>
       </c>
       <c r="I6" s="1">
-        <v>-8.8254814454050852e-07</v>
+        <v>-8.3817656144682065e-07</v>
       </c>
       <c r="J6" s="1">
-        <v>-5.6948422010781474e-06</v>
+        <v>-4.3949416072954564e-07</v>
       </c>
       <c r="K6" s="1">
-        <v>5.7323800920072319e-07</v>
+        <v>5.8004918461705923e-07</v>
       </c>
       <c r="L6" s="1">
-        <v>9.895043392138758e-07</v>
+        <v>9.8484703941910146e-07</v>
       </c>
       <c r="M6" s="1">
-        <v>2.4246981755245723e-06</v>
+        <v>2.4192777959599787e-06</v>
       </c>
       <c r="N6" s="1">
-        <v>9.0178815302115698e-07</v>
+        <v>9.0824631302646535e-07</v>
       </c>
       <c r="O6" s="1">
-        <v>8.4361086075895292e-07</v>
+        <v>8.3744257604034459e-07</v>
       </c>
       <c r="P6" s="1">
-        <v>-6.5233235870770362e-08</v>
+        <v>-6.6201838631993736e-08</v>
       </c>
       <c r="Q6" s="1">
-        <v>5.9370641307391855e-07</v>
+        <v>5.9155679501683558e-07</v>
       </c>
       <c r="R6" s="1">
-        <v>2.906469781733468e-08</v>
+        <v>2.6627048383182564e-08</v>
       </c>
       <c r="S6" s="1">
-        <v>-2.8643558569532632e-07</v>
+        <v>-2.9060816620728526e-07</v>
       </c>
       <c r="T6" s="1">
-        <v>4.1326139365470706e-08</v>
+        <v>4.0993366747811243e-08</v>
       </c>
       <c r="U6" s="1">
-        <v>6.9919925277282411e-05</v>
+        <v>6.9768093934361036e-05</v>
       </c>
     </row>
     <row r="7">
@@ -3874,64 +3874,64 @@
         <v>30</v>
       </c>
       <c r="B7" s="1">
-        <v>0.0036135620931377053</v>
+        <v>0.0041214116345892667</v>
       </c>
       <c r="C7" s="1">
-        <v>-1.2257315410143131e-06</v>
+        <v>-1.0922089954529246e-06</v>
       </c>
       <c r="D7" s="1">
-        <v>-2.6185270367090687e-09</v>
+        <v>-4.1038185897197249e-09</v>
       </c>
       <c r="E7" s="1">
-        <v>-6.1428736339675603e-05</v>
+        <v>-6.1673713642238596e-05</v>
       </c>
       <c r="F7" s="1">
-        <v>-0.0003487282588254355</v>
+        <v>-0.00035298626832795801</v>
       </c>
       <c r="G7" s="1">
-        <v>1.4910385479872448e-06</v>
+        <v>1.4956624640466632e-06</v>
       </c>
       <c r="H7" s="1">
-        <v>7.4697062410817513e-06</v>
+        <v>7.5514551492141455e-06</v>
       </c>
       <c r="I7" s="1">
-        <v>-1.7088996311797684e-06</v>
+        <v>-1.7946155814230502e-06</v>
       </c>
       <c r="J7" s="1">
-        <v>0.000147998942835702</v>
+        <v>0.00012897586253484184</v>
       </c>
       <c r="K7" s="1">
-        <v>2.6841726861137348e-06</v>
+        <v>2.687281051702793e-06</v>
       </c>
       <c r="L7" s="1">
-        <v>5.2637763802021975e-06</v>
+        <v>5.2823545933536188e-06</v>
       </c>
       <c r="M7" s="1">
-        <v>7.7256870750352935e-06</v>
+        <v>7.7545530723733902e-06</v>
       </c>
       <c r="N7" s="1">
-        <v>5.6560785670773593e-06</v>
+        <v>5.676615880252902e-06</v>
       </c>
       <c r="O7" s="1">
-        <v>1.9401848157982872e-06</v>
+        <v>1.8426703139075034e-06</v>
       </c>
       <c r="P7" s="1">
-        <v>5.6742104624401131e-07</v>
+        <v>4.2828889330049403e-07</v>
       </c>
       <c r="Q7" s="1">
-        <v>7.136091584026169e-07</v>
+        <v>5.6535349589279802e-07</v>
       </c>
       <c r="R7" s="1">
-        <v>-1.1434228552623733e-07</v>
+        <v>-1.387743028014165e-07</v>
       </c>
       <c r="S7" s="1">
-        <v>-1.1089324689848942e-08</v>
+        <v>4.3594158218159083e-08</v>
       </c>
       <c r="T7" s="1">
-        <v>6.2624928036603065e-07</v>
+        <v>6.8123456760247904e-07</v>
       </c>
       <c r="U7" s="1">
-        <v>4.9567640689937594e-05</v>
+        <v>4.6881688580540101e-05</v>
       </c>
     </row>
     <row r="8">
@@ -3939,64 +3939,64 @@
         <v>31</v>
       </c>
       <c r="B8" s="1">
-        <v>-0.17672236704758013</v>
+        <v>-0.16355971895393126</v>
       </c>
       <c r="C8" s="1">
-        <v>-3.3771728766285646e-05</v>
+        <v>-3.4134927642802412e-05</v>
       </c>
       <c r="D8" s="1">
-        <v>3.6442518821678374e-07</v>
+        <v>3.6583856479650831e-07</v>
       </c>
       <c r="E8" s="1">
-        <v>4.4272909069806078e-05</v>
+        <v>4.2010889188431096e-05</v>
       </c>
       <c r="F8" s="1">
-        <v>8.8867118570551951e-05</v>
+        <v>9.2180585165848491e-05</v>
       </c>
       <c r="G8" s="1">
-        <v>-8.8254814454050852e-07</v>
+        <v>-8.3817656144682065e-07</v>
       </c>
       <c r="H8" s="1">
-        <v>-1.7088996311797684e-06</v>
+        <v>-1.7946155814230502e-06</v>
       </c>
       <c r="I8" s="1">
-        <v>0.00042014636092349973</v>
+        <v>0.00041507683601057582</v>
       </c>
       <c r="J8" s="1">
-        <v>1.3115304279262137e-05</v>
+        <v>1.1312040693877826e-05</v>
       </c>
       <c r="K8" s="1">
-        <v>-1.0462115718024375e-05</v>
+        <v>-1.2962754322543975e-05</v>
       </c>
       <c r="L8" s="1">
-        <v>-3.3172649178569848e-05</v>
+        <v>-3.3415374608117134e-05</v>
       </c>
       <c r="M8" s="1">
-        <v>-4.9383762731571815e-05</v>
+        <v>-4.9456290136536292e-05</v>
       </c>
       <c r="N8" s="1">
-        <v>-3.8386084465708985e-05</v>
+        <v>-3.8795312277691922e-05</v>
       </c>
       <c r="O8" s="1">
-        <v>-1.4079114511612554e-06</v>
+        <v>-3.2288860237441933e-06</v>
       </c>
       <c r="P8" s="1">
-        <v>-5.8547907863135958e-06</v>
+        <v>-5.5178180403388032e-06</v>
       </c>
       <c r="Q8" s="1">
-        <v>-1.120622250600702e-05</v>
+        <v>-1.11793484844285e-05</v>
       </c>
       <c r="R8" s="1">
-        <v>-7.5004822450072831e-06</v>
+        <v>-7.593836084760822e-06</v>
       </c>
       <c r="S8" s="1">
-        <v>4.2748100105354825e-07</v>
+        <v>1.8170245955002444e-06</v>
       </c>
       <c r="T8" s="1">
-        <v>-8.0363480523402209e-08</v>
+        <v>3.8856641742555149e-07</v>
       </c>
       <c r="U8" s="1">
-        <v>0.00045647219026555567</v>
+        <v>0.00047719247130240366</v>
       </c>
     </row>
     <row r="9">
@@ -4004,64 +4004,64 @@
         <v>32</v>
       </c>
       <c r="B9" s="1">
-        <v>0.21414672639630197</v>
+        <v>0.38195444174650278</v>
       </c>
       <c r="C9" s="1">
-        <v>0.00016245249783464706</v>
+        <v>0.00015335924095357114</v>
       </c>
       <c r="D9" s="1">
-        <v>-1.77084472741687e-06</v>
+        <v>-1.6943995622860904e-06</v>
       </c>
       <c r="E9" s="1">
-        <v>0.00027929043868713004</v>
+        <v>1.4169869399275121e-05</v>
       </c>
       <c r="F9" s="1">
-        <v>-0.0079065982410055583</v>
+        <v>-0.0068847852549692203</v>
       </c>
       <c r="G9" s="1">
-        <v>-5.6948422010781474e-06</v>
+        <v>-4.3949416072954564e-07</v>
       </c>
       <c r="H9" s="1">
-        <v>0.000147998942835702</v>
+        <v>0.00012897586253484184</v>
       </c>
       <c r="I9" s="1">
-        <v>1.3115304279262137e-05</v>
+        <v>1.1312040693877826e-05</v>
       </c>
       <c r="J9" s="1">
-        <v>0.12790412924389932</v>
+        <v>0.067878859350703744</v>
       </c>
       <c r="K9" s="1">
-        <v>-3.4286534867831039e-05</v>
+        <v>-3.0477021717822995e-05</v>
       </c>
       <c r="L9" s="1">
-        <v>-7.0226149650560442e-06</v>
+        <v>-6.7313920286378013e-06</v>
       </c>
       <c r="M9" s="1">
-        <v>-3.5006677386811997e-05</v>
+        <v>-2.4565652479467573e-05</v>
       </c>
       <c r="N9" s="1">
-        <v>0.00018387679205852302</v>
+        <v>0.00011199244124427909</v>
       </c>
       <c r="O9" s="1">
-        <v>-0.00019225556903765563</v>
+        <v>-0.00015254790235889757</v>
       </c>
       <c r="P9" s="1">
-        <v>-8.4411701383200354e-05</v>
+        <v>-0.00012032216446739832</v>
       </c>
       <c r="Q9" s="1">
-        <v>-4.0607076847453496e-05</v>
+        <v>-9.4717785522761076e-05</v>
       </c>
       <c r="R9" s="1">
-        <v>-2.5234962957169379e-05</v>
+        <v>-2.6489070100106055e-05</v>
       </c>
       <c r="S9" s="1">
-        <v>-1.9559843903797975e-05</v>
+        <v>2.0136383974358153e-05</v>
       </c>
       <c r="T9" s="1">
-        <v>6.6099980891723008e-05</v>
+        <v>6.9707755616013758e-05</v>
       </c>
       <c r="U9" s="1">
-        <v>-0.0034251693199069924</v>
+        <v>-0.0031673924026200365</v>
       </c>
     </row>
     <row r="10">
@@ -4069,64 +4069,64 @@
         <v>33</v>
       </c>
       <c r="B10" s="1">
-        <v>0.44513220122821712</v>
+        <v>0.44583033633895996</v>
       </c>
       <c r="C10" s="1">
-        <v>-1.6912700878659356e-06</v>
+        <v>-1.5233378905525699e-06</v>
       </c>
       <c r="D10" s="1">
-        <v>1.2323010252592635e-08</v>
+        <v>1.0601793888727325e-08</v>
       </c>
       <c r="E10" s="1">
-        <v>-2.6046522225714296e-05</v>
+        <v>-2.6245457904309255e-05</v>
       </c>
       <c r="F10" s="1">
-        <v>-4.12190760621055e-05</v>
+        <v>-4.1186044527889746e-05</v>
       </c>
       <c r="G10" s="1">
-        <v>5.7323800920072319e-07</v>
+        <v>5.8004918461705923e-07</v>
       </c>
       <c r="H10" s="1">
-        <v>2.6841726861137348e-06</v>
+        <v>2.687281051702793e-06</v>
       </c>
       <c r="I10" s="1">
-        <v>-1.0462115718024375e-05</v>
+        <v>-1.2962754322543975e-05</v>
       </c>
       <c r="J10" s="1">
-        <v>-3.4286534867831039e-05</v>
+        <v>-3.0477021717822995e-05</v>
       </c>
       <c r="K10" s="1">
-        <v>0.012480703757926289</v>
+        <v>0.01247805590259557</v>
       </c>
       <c r="L10" s="1">
-        <v>0.01117311764011085</v>
+        <v>0.011170626047177412</v>
       </c>
       <c r="M10" s="1">
-        <v>0.011177789284151389</v>
+        <v>0.011175422559618918</v>
       </c>
       <c r="N10" s="1">
-        <v>0.011175749666521914</v>
+        <v>0.011173321881289408</v>
       </c>
       <c r="O10" s="1">
-        <v>1.5969267662648294e-05</v>
+        <v>1.5954170076495944e-05</v>
       </c>
       <c r="P10" s="1">
-        <v>-1.0535124386906167e-05</v>
+        <v>-1.0600949996092385e-05</v>
       </c>
       <c r="Q10" s="1">
-        <v>4.0409460491079732e-06</v>
+        <v>3.8102252492817659e-06</v>
       </c>
       <c r="R10" s="1">
-        <v>5.6119676771161318e-07</v>
+        <v>4.8790018301229367e-07</v>
       </c>
       <c r="S10" s="1">
-        <v>-1.6753617963342804e-05</v>
+        <v>-1.6849465216042173e-05</v>
       </c>
       <c r="T10" s="1">
-        <v>4.2212713091828724e-06</v>
+        <v>4.25736712122523e-06</v>
       </c>
       <c r="U10" s="1">
-        <v>-0.011126430038011104</v>
+        <v>-0.011126039512338308</v>
       </c>
     </row>
     <row r="11">
@@ -4134,64 +4134,64 @@
         <v>34</v>
       </c>
       <c r="B11" s="1">
-        <v>0.7886163564247628</v>
+        <v>0.78796973978700846</v>
       </c>
       <c r="C11" s="1">
-        <v>-1.5467360083312763e-07</v>
+        <v>-9.9392082172600778e-08</v>
       </c>
       <c r="D11" s="1">
-        <v>-3.2701818241622779e-09</v>
+        <v>-3.6218258816888244e-09</v>
       </c>
       <c r="E11" s="1">
-        <v>-4.0235605142481213e-05</v>
+        <v>-3.9907356854963279e-05</v>
       </c>
       <c r="F11" s="1">
-        <v>-0.00011763104351105015</v>
+        <v>-0.00011840914115454313</v>
       </c>
       <c r="G11" s="1">
-        <v>9.895043392138758e-07</v>
+        <v>9.8484703941910146e-07</v>
       </c>
       <c r="H11" s="1">
-        <v>5.2637763802021975e-06</v>
+        <v>5.2823545933536188e-06</v>
       </c>
       <c r="I11" s="1">
-        <v>-3.3172649178569848e-05</v>
+        <v>-3.3415374608117134e-05</v>
       </c>
       <c r="J11" s="1">
-        <v>-7.0226149650560442e-06</v>
+        <v>-6.7313920286378013e-06</v>
       </c>
       <c r="K11" s="1">
-        <v>0.01117311764011085</v>
+        <v>0.011170626047177412</v>
       </c>
       <c r="L11" s="1">
-        <v>0.011467034623125236</v>
+        <v>0.011464339583898206</v>
       </c>
       <c r="M11" s="1">
-        <v>0.011194975398381652</v>
+        <v>0.011192380698999783</v>
       </c>
       <c r="N11" s="1">
-        <v>0.011196363422331981</v>
+        <v>0.011193787788118099</v>
       </c>
       <c r="O11" s="1">
-        <v>8.0421318482719043e-06</v>
+        <v>8.1599737114731753e-06</v>
       </c>
       <c r="P11" s="1">
-        <v>-1.2239379692018152e-05</v>
+        <v>-1.2325564939422056e-05</v>
       </c>
       <c r="Q11" s="1">
-        <v>-2.7749970234971397e-06</v>
+        <v>-3.1403441155558915e-06</v>
       </c>
       <c r="R11" s="1">
-        <v>-1.0497889165467779e-05</v>
+        <v>-1.0567072402655313e-05</v>
       </c>
       <c r="S11" s="1">
-        <v>-2.4346797453498523e-05</v>
+        <v>-2.444833971838204e-05</v>
       </c>
       <c r="T11" s="1">
-        <v>3.9767231751625442e-06</v>
+        <v>4.0029405355176756e-06</v>
       </c>
       <c r="U11" s="1">
-        <v>-0.011157860118229787</v>
+        <v>-0.011157041297398749</v>
       </c>
     </row>
     <row r="12">
@@ -4199,64 +4199,64 @@
         <v>35</v>
       </c>
       <c r="B12" s="1">
-        <v>0.94997396411635304</v>
+        <v>0.94879584345140966</v>
       </c>
       <c r="C12" s="1">
-        <v>3.0024752055162007e-06</v>
+        <v>3.0609956068016349e-06</v>
       </c>
       <c r="D12" s="1">
-        <v>-2.827533447014885e-09</v>
+        <v>-3.1574773190429262e-09</v>
       </c>
       <c r="E12" s="1">
-        <v>-6.6026515134199641e-05</v>
+        <v>-6.5652081200321113e-05</v>
       </c>
       <c r="F12" s="1">
-        <v>-0.00015251328066123783</v>
+        <v>-0.00015383107882074003</v>
       </c>
       <c r="G12" s="1">
-        <v>2.4246981755245723e-06</v>
+        <v>2.4192777959599787e-06</v>
       </c>
       <c r="H12" s="1">
-        <v>7.7256870750352935e-06</v>
+        <v>7.7545530723733902e-06</v>
       </c>
       <c r="I12" s="1">
-        <v>-4.9383762731571815e-05</v>
+        <v>-4.9456290136536292e-05</v>
       </c>
       <c r="J12" s="1">
-        <v>-3.5006677386811997e-05</v>
+        <v>-2.4565652479467573e-05</v>
       </c>
       <c r="K12" s="1">
-        <v>0.011177789284151389</v>
+        <v>0.011175422559618918</v>
       </c>
       <c r="L12" s="1">
-        <v>0.011194975398381652</v>
+        <v>0.011192380698999783</v>
       </c>
       <c r="M12" s="1">
-        <v>0.011383850049034484</v>
+        <v>0.011381183553354501</v>
       </c>
       <c r="N12" s="1">
-        <v>0.01129094499636075</v>
+        <v>0.011288365311769966</v>
       </c>
       <c r="O12" s="1">
-        <v>2.8171161066948875e-06</v>
+        <v>3.0149836377090028e-06</v>
       </c>
       <c r="P12" s="1">
-        <v>-1.639120745372842e-05</v>
+        <v>-1.6435500809280007e-05</v>
       </c>
       <c r="Q12" s="1">
-        <v>-1.2127125612166572e-05</v>
+        <v>-1.2429368953524705e-05</v>
       </c>
       <c r="R12" s="1">
-        <v>-6.0271341908486288e-06</v>
+        <v>-6.088328690094857e-06</v>
       </c>
       <c r="S12" s="1">
-        <v>-3.5677647281842441e-05</v>
+        <v>-3.5833383340495524e-05</v>
       </c>
       <c r="T12" s="1">
-        <v>-1.8710044195697187e-05</v>
+        <v>-1.8722282782009985e-05</v>
       </c>
       <c r="U12" s="1">
-        <v>-0.011359583865757326</v>
+        <v>-0.011359234386883301</v>
       </c>
     </row>
     <row r="13">
@@ -4264,64 +4264,64 @@
         <v>36</v>
       </c>
       <c r="B13" s="1">
-        <v>1.0207255718380488</v>
+        <v>1.0203753582518058</v>
       </c>
       <c r="C13" s="1">
-        <v>2.3564747247100602e-05</v>
+        <v>2.3669135991962073e-05</v>
       </c>
       <c r="D13" s="1">
-        <v>-1.7331909746317233e-07</v>
+        <v>-1.7427429355495081e-07</v>
       </c>
       <c r="E13" s="1">
-        <v>3.1510682439981649e-05</v>
+        <v>3.1234573519444785e-05</v>
       </c>
       <c r="F13" s="1">
-        <v>-1.9373521742390359e-05</v>
+        <v>-2.0307089815686085e-05</v>
       </c>
       <c r="G13" s="1">
-        <v>9.0178815302115698e-07</v>
+        <v>9.0824631302646535e-07</v>
       </c>
       <c r="H13" s="1">
-        <v>5.6560785670773593e-06</v>
+        <v>5.676615880252902e-06</v>
       </c>
       <c r="I13" s="1">
-        <v>-3.8386084465708985e-05</v>
+        <v>-3.8795312277691922e-05</v>
       </c>
       <c r="J13" s="1">
-        <v>0.00018387679205852302</v>
+        <v>0.00011199244124427909</v>
       </c>
       <c r="K13" s="1">
-        <v>0.011175749666521914</v>
+        <v>0.011173321881289408</v>
       </c>
       <c r="L13" s="1">
-        <v>0.011196363422331981</v>
+        <v>0.011193787788118099</v>
       </c>
       <c r="M13" s="1">
-        <v>0.01129094499636075</v>
+        <v>0.011288365311769966</v>
       </c>
       <c r="N13" s="1">
-        <v>0.01186974481097368</v>
+        <v>0.011867035237750746</v>
       </c>
       <c r="O13" s="1">
-        <v>1.4865501155438408e-05</v>
+        <v>1.4923855037260644e-05</v>
       </c>
       <c r="P13" s="1">
-        <v>1.1828092820120325e-06</v>
+        <v>8.363699031300413e-07</v>
       </c>
       <c r="Q13" s="1">
-        <v>-9.1468696041836299e-06</v>
+        <v>-9.5954668211758403e-06</v>
       </c>
       <c r="R13" s="1">
-        <v>1.2391410897251588e-05</v>
+        <v>1.225020246673414e-05</v>
       </c>
       <c r="S13" s="1">
-        <v>-3.9513362427647504e-05</v>
+        <v>-3.9518197543425719e-05</v>
       </c>
       <c r="T13" s="1">
-        <v>-2.4601158736767326e-05</v>
+        <v>-2.4527701897104489e-05</v>
       </c>
       <c r="U13" s="1">
-        <v>-0.0119816407522762</v>
+        <v>-0.011981507938177075</v>
       </c>
     </row>
     <row r="14">
@@ -4329,64 +4329,64 @@
         <v>37</v>
       </c>
       <c r="B14" s="1">
-        <v>0.073348874469100073</v>
+        <v>0.073451072546156723</v>
       </c>
       <c r="C14" s="1">
-        <v>1.6094093233746959e-06</v>
+        <v>1.6659843237926481e-06</v>
       </c>
       <c r="D14" s="1">
-        <v>-2.8197301434058223e-08</v>
+        <v>-2.8689040382927587e-08</v>
       </c>
       <c r="E14" s="1">
-        <v>-4.2966282962757997e-05</v>
+        <v>-4.264205578565715e-05</v>
       </c>
       <c r="F14" s="1">
-        <v>-0.00012801075056115242</v>
+        <v>-0.00012274071322981118</v>
       </c>
       <c r="G14" s="1">
-        <v>8.4361086075895292e-07</v>
+        <v>8.3744257604034459e-07</v>
       </c>
       <c r="H14" s="1">
-        <v>1.9401848157982872e-06</v>
+        <v>1.8426703139075034e-06</v>
       </c>
       <c r="I14" s="1">
-        <v>-1.4079114511612554e-06</v>
+        <v>-3.2288860237441933e-06</v>
       </c>
       <c r="J14" s="1">
-        <v>-0.00019225556903765563</v>
+        <v>-0.00015254790235889757</v>
       </c>
       <c r="K14" s="1">
-        <v>1.5969267662648294e-05</v>
+        <v>1.5954170076495944e-05</v>
       </c>
       <c r="L14" s="1">
-        <v>8.0421318482719043e-06</v>
+        <v>8.1599737114731753e-06</v>
       </c>
       <c r="M14" s="1">
-        <v>2.8171161066948875e-06</v>
+        <v>3.0149836377090028e-06</v>
       </c>
       <c r="N14" s="1">
-        <v>1.4865501155438408e-05</v>
+        <v>1.4923855037260644e-05</v>
       </c>
       <c r="O14" s="1">
-        <v>0.00092205015573763112</v>
+        <v>0.00092175935424856285</v>
       </c>
       <c r="P14" s="1">
-        <v>0.0004319682472363865</v>
+        <v>0.00043199379206276177</v>
       </c>
       <c r="Q14" s="1">
-        <v>0.00043278309110213512</v>
+        <v>0.00043283419459476451</v>
       </c>
       <c r="R14" s="1">
-        <v>0.00043219218949675132</v>
+        <v>0.00043211193058612129</v>
       </c>
       <c r="S14" s="1">
-        <v>-1.4137951808988625e-05</v>
+        <v>-1.4159910486496826e-05</v>
       </c>
       <c r="T14" s="1">
-        <v>-2.5486608316093698e-05</v>
+        <v>-2.5620048211891062e-05</v>
       </c>
       <c r="U14" s="1">
-        <v>-0.00044122877753291002</v>
+        <v>-0.00044145965873242522</v>
       </c>
     </row>
     <row r="15">
@@ -4394,64 +4394,64 @@
         <v>38</v>
       </c>
       <c r="B15" s="1">
-        <v>-0.02022938847126491</v>
+        <v>-0.021102600374019006</v>
       </c>
       <c r="C15" s="1">
-        <v>3.0349993587210175e-06</v>
+        <v>2.8324372475920348e-06</v>
       </c>
       <c r="D15" s="1">
-        <v>-3.8141043026444714e-08</v>
+        <v>-3.5904737921844196e-08</v>
       </c>
       <c r="E15" s="1">
-        <v>9.7973997462779777e-06</v>
+        <v>9.841506540567862e-06</v>
       </c>
       <c r="F15" s="1">
-        <v>-2.3788951772339656e-05</v>
+        <v>-1.6224786243510909e-05</v>
       </c>
       <c r="G15" s="1">
-        <v>-6.5233235870770362e-08</v>
+        <v>-6.6201838631993736e-08</v>
       </c>
       <c r="H15" s="1">
-        <v>5.6742104624401131e-07</v>
+        <v>4.2828889330049403e-07</v>
       </c>
       <c r="I15" s="1">
-        <v>-5.8547907863135958e-06</v>
+        <v>-5.5178180403388032e-06</v>
       </c>
       <c r="J15" s="1">
-        <v>-8.4411701383200354e-05</v>
+        <v>-0.00012032216446739832</v>
       </c>
       <c r="K15" s="1">
-        <v>-1.0535124386906167e-05</v>
+        <v>-1.0600949996092385e-05</v>
       </c>
       <c r="L15" s="1">
-        <v>-1.2239379692018152e-05</v>
+        <v>-1.2325564939422056e-05</v>
       </c>
       <c r="M15" s="1">
-        <v>-1.639120745372842e-05</v>
+        <v>-1.6435500809280007e-05</v>
       </c>
       <c r="N15" s="1">
-        <v>1.1828092820120325e-06</v>
+        <v>8.363699031300413e-07</v>
       </c>
       <c r="O15" s="1">
-        <v>0.0004319682472363865</v>
+        <v>0.00043199379206276177</v>
       </c>
       <c r="P15" s="1">
-        <v>0.0011305701256148417</v>
+        <v>0.0011302173216978773</v>
       </c>
       <c r="Q15" s="1">
-        <v>0.000431268519444771</v>
+        <v>0.00043126829704103175</v>
       </c>
       <c r="R15" s="1">
-        <v>0.00043232623494095977</v>
+        <v>0.00043222220129023238</v>
       </c>
       <c r="S15" s="1">
-        <v>-1.2197036870164296e-05</v>
+        <v>-1.2267372061469675e-05</v>
       </c>
       <c r="T15" s="1">
-        <v>-1.6060472209391362e-05</v>
+        <v>-1.6260009663709777e-05</v>
       </c>
       <c r="U15" s="1">
-        <v>-0.0004709281971202791</v>
+        <v>-0.00046680015462196515</v>
       </c>
     </row>
     <row r="16">
@@ -4459,64 +4459,64 @@
         <v>39</v>
       </c>
       <c r="B16" s="1">
-        <v>-0.033735542521369601</v>
+        <v>-0.034591050676585702</v>
       </c>
       <c r="C16" s="1">
-        <v>-5.2024808409682079e-07</v>
+        <v>-6.7628240789441789e-07</v>
       </c>
       <c r="D16" s="1">
-        <v>-1.6553094017191181e-09</v>
+        <v>1.5600019607145327e-10</v>
       </c>
       <c r="E16" s="1">
-        <v>-2.6807256883508815e-05</v>
+        <v>-2.6669148530096986e-05</v>
       </c>
       <c r="F16" s="1">
-        <v>-7.3878591633196982e-05</v>
+        <v>-6.5799348859331747e-05</v>
       </c>
       <c r="G16" s="1">
-        <v>5.9370641307391855e-07</v>
+        <v>5.9155679501683558e-07</v>
       </c>
       <c r="H16" s="1">
-        <v>7.136091584026169e-07</v>
+        <v>5.6535349589279802e-07</v>
       </c>
       <c r="I16" s="1">
-        <v>-1.120622250600702e-05</v>
+        <v>-1.11793484844285e-05</v>
       </c>
       <c r="J16" s="1">
-        <v>-4.0607076847453496e-05</v>
+        <v>-9.4717785522761076e-05</v>
       </c>
       <c r="K16" s="1">
-        <v>4.0409460491079732e-06</v>
+        <v>3.8102252492817659e-06</v>
       </c>
       <c r="L16" s="1">
-        <v>-2.7749970234971397e-06</v>
+        <v>-3.1403441155558915e-06</v>
       </c>
       <c r="M16" s="1">
-        <v>-1.2127125612166572e-05</v>
+        <v>-1.2429368953524705e-05</v>
       </c>
       <c r="N16" s="1">
-        <v>-9.1468696041836299e-06</v>
+        <v>-9.5954668211758403e-06</v>
       </c>
       <c r="O16" s="1">
-        <v>0.00043278309110213512</v>
+        <v>0.00043283419459476451</v>
       </c>
       <c r="P16" s="1">
-        <v>0.000431268519444771</v>
+        <v>0.00043126829704103175</v>
       </c>
       <c r="Q16" s="1">
-        <v>0.00086607472905374521</v>
+        <v>0.00086589606266216409</v>
       </c>
       <c r="R16" s="1">
-        <v>0.00043203610022066608</v>
+        <v>0.00043193914920436436</v>
       </c>
       <c r="S16" s="1">
-        <v>-8.9871093280602874e-06</v>
+        <v>-8.9685393433282226e-06</v>
       </c>
       <c r="T16" s="1">
-        <v>-1.6234501380216852e-05</v>
+        <v>-1.6370657586540698e-05</v>
       </c>
       <c r="U16" s="1">
-        <v>-0.00038447065858590807</v>
+        <v>-0.00038112758163610504</v>
       </c>
     </row>
     <row r="17">
@@ -4524,64 +4524,64 @@
         <v>40</v>
       </c>
       <c r="B17" s="1">
-        <v>0.0021324956173100268</v>
+        <v>0.0018365763743745643</v>
       </c>
       <c r="C17" s="1">
-        <v>1.2384904953898715e-06</v>
+        <v>1.237706220488573e-06</v>
       </c>
       <c r="D17" s="1">
-        <v>-1.9240633809598504e-08</v>
+        <v>-1.9172918102372577e-08</v>
       </c>
       <c r="E17" s="1">
-        <v>1.4520984424207412e-05</v>
+        <v>1.4657307388924741e-05</v>
       </c>
       <c r="F17" s="1">
-        <v>-3.4129443930021857e-06</v>
+        <v>-1.9992086739724271e-06</v>
       </c>
       <c r="G17" s="1">
-        <v>2.906469781733468e-08</v>
+        <v>2.6627048383182564e-08</v>
       </c>
       <c r="H17" s="1">
-        <v>-1.1434228552623733e-07</v>
+        <v>-1.387743028014165e-07</v>
       </c>
       <c r="I17" s="1">
-        <v>-7.5004822450072831e-06</v>
+        <v>-7.593836084760822e-06</v>
       </c>
       <c r="J17" s="1">
-        <v>-2.5234962957169379e-05</v>
+        <v>-2.6489070100106055e-05</v>
       </c>
       <c r="K17" s="1">
-        <v>5.6119676771161318e-07</v>
+        <v>4.8790018301229367e-07</v>
       </c>
       <c r="L17" s="1">
-        <v>-1.0497889165467779e-05</v>
+        <v>-1.0567072402655313e-05</v>
       </c>
       <c r="M17" s="1">
-        <v>-6.0271341908486288e-06</v>
+        <v>-6.088328690094857e-06</v>
       </c>
       <c r="N17" s="1">
-        <v>1.2391410897251588e-05</v>
+        <v>1.225020246673414e-05</v>
       </c>
       <c r="O17" s="1">
-        <v>0.00043219218949675132</v>
+        <v>0.00043211193058612129</v>
       </c>
       <c r="P17" s="1">
-        <v>0.00043232623494095977</v>
+        <v>0.00043222220129023238</v>
       </c>
       <c r="Q17" s="1">
-        <v>0.00043203610022066608</v>
+        <v>0.00043193914920436436</v>
       </c>
       <c r="R17" s="1">
-        <v>0.00060510229171278473</v>
+        <v>0.00060493023259023911</v>
       </c>
       <c r="S17" s="1">
-        <v>-1.210879314253073e-05</v>
+        <v>-1.2081766268414292e-05</v>
       </c>
       <c r="T17" s="1">
-        <v>-2.5219288578953319e-05</v>
+        <v>-2.5314845850081497e-05</v>
       </c>
       <c r="U17" s="1">
-        <v>-0.00044343152738088461</v>
+        <v>-0.00044336246855281757</v>
       </c>
     </row>
     <row r="18">
@@ -4589,64 +4589,64 @@
         <v>41</v>
       </c>
       <c r="B18" s="1">
-        <v>-0.18537506695291303</v>
+        <v>-0.18581875052852362</v>
       </c>
       <c r="C18" s="1">
-        <v>-3.0482203558139592e-07</v>
+        <v>-3.4344712248334343e-07</v>
       </c>
       <c r="D18" s="1">
-        <v>-7.5720705575493119e-09</v>
+        <v>-7.1492419486544743e-09</v>
       </c>
       <c r="E18" s="1">
-        <v>2.4478330441287561e-05</v>
+        <v>2.46575133178336e-05</v>
       </c>
       <c r="F18" s="1">
-        <v>2.8550948870025924e-05</v>
+        <v>2.5469325078479404e-05</v>
       </c>
       <c r="G18" s="1">
-        <v>-2.8643558569532632e-07</v>
+        <v>-2.9060816620728526e-07</v>
       </c>
       <c r="H18" s="1">
-        <v>-1.1089324689848942e-08</v>
+        <v>4.3594158218159083e-08</v>
       </c>
       <c r="I18" s="1">
-        <v>4.2748100105354825e-07</v>
+        <v>1.8170245955002444e-06</v>
       </c>
       <c r="J18" s="1">
-        <v>-1.9559843903797975e-05</v>
+        <v>2.0136383974358153e-05</v>
       </c>
       <c r="K18" s="1">
-        <v>-1.6753617963342804e-05</v>
+        <v>-1.6849465216042173e-05</v>
       </c>
       <c r="L18" s="1">
-        <v>-2.4346797453498523e-05</v>
+        <v>-2.444833971838204e-05</v>
       </c>
       <c r="M18" s="1">
-        <v>-3.5677647281842441e-05</v>
+        <v>-3.5833383340495524e-05</v>
       </c>
       <c r="N18" s="1">
-        <v>-3.9513362427647504e-05</v>
+        <v>-3.9518197543425719e-05</v>
       </c>
       <c r="O18" s="1">
-        <v>-1.4137951808988625e-05</v>
+        <v>-1.4159910486496826e-05</v>
       </c>
       <c r="P18" s="1">
-        <v>-1.2197036870164296e-05</v>
+        <v>-1.2267372061469675e-05</v>
       </c>
       <c r="Q18" s="1">
-        <v>-8.9871093280602874e-06</v>
+        <v>-8.9685393433282226e-06</v>
       </c>
       <c r="R18" s="1">
-        <v>-1.210879314253073e-05</v>
+        <v>-1.2081766268414292e-05</v>
       </c>
       <c r="S18" s="1">
-        <v>0.00099168011050491988</v>
+        <v>0.00099104665912430048</v>
       </c>
       <c r="T18" s="1">
-        <v>8.7231160419774123e-05</v>
+        <v>8.72278823209478e-05</v>
       </c>
       <c r="U18" s="1">
-        <v>-2.1771142384699685e-05</v>
+        <v>-2.1825354690591048e-05</v>
       </c>
     </row>
     <row r="19">
@@ -4654,64 +4654,64 @@
         <v>42</v>
       </c>
       <c r="B19" s="1">
-        <v>-0.055807770551068246</v>
+        <v>-0.055742854096631017</v>
       </c>
       <c r="C19" s="1">
-        <v>-3.8224410691735699e-07</v>
+        <v>-3.1367662316262897e-07</v>
       </c>
       <c r="D19" s="1">
-        <v>-8.3438751008559219e-09</v>
+        <v>-9.1257546332900786e-09</v>
       </c>
       <c r="E19" s="1">
-        <v>1.5154765880496575e-05</v>
+        <v>1.5160437654607358e-05</v>
       </c>
       <c r="F19" s="1">
-        <v>-1.0395554965158991e-06</v>
+        <v>-4.0480593922532691e-06</v>
       </c>
       <c r="G19" s="1">
-        <v>4.1326139365470706e-08</v>
+        <v>4.0993366747811243e-08</v>
       </c>
       <c r="H19" s="1">
-        <v>6.2624928036603065e-07</v>
+        <v>6.8123456760247904e-07</v>
       </c>
       <c r="I19" s="1">
-        <v>-8.0363480523402209e-08</v>
+        <v>3.8856641742555149e-07</v>
       </c>
       <c r="J19" s="1">
-        <v>6.6099980891723008e-05</v>
+        <v>6.9707755616013758e-05</v>
       </c>
       <c r="K19" s="1">
-        <v>4.2212713091828724e-06</v>
+        <v>4.25736712122523e-06</v>
       </c>
       <c r="L19" s="1">
-        <v>3.9767231751625442e-06</v>
+        <v>4.0029405355176756e-06</v>
       </c>
       <c r="M19" s="1">
-        <v>-1.8710044195697187e-05</v>
+        <v>-1.8722282782009985e-05</v>
       </c>
       <c r="N19" s="1">
-        <v>-2.4601158736767326e-05</v>
+        <v>-2.4527701897104489e-05</v>
       </c>
       <c r="O19" s="1">
-        <v>-2.5486608316093698e-05</v>
+        <v>-2.5620048211891062e-05</v>
       </c>
       <c r="P19" s="1">
-        <v>-1.6060472209391362e-05</v>
+        <v>-1.6260009663709777e-05</v>
       </c>
       <c r="Q19" s="1">
-        <v>-1.6234501380216852e-05</v>
+        <v>-1.6370657586540698e-05</v>
       </c>
       <c r="R19" s="1">
-        <v>-2.5219288578953319e-05</v>
+        <v>-2.5314845850081497e-05</v>
       </c>
       <c r="S19" s="1">
-        <v>8.7231160419774123e-05</v>
+        <v>8.72278823209478e-05</v>
       </c>
       <c r="T19" s="1">
-        <v>0.0012544037478336421</v>
+        <v>0.0012544308440062433</v>
       </c>
       <c r="U19" s="1">
-        <v>-3.075578315740324e-05</v>
+        <v>-3.2369094098510547e-05</v>
       </c>
     </row>
     <row r="20">
@@ -4719,64 +4719,64 @@
         <v>43</v>
       </c>
       <c r="B20" s="1">
-        <v>-3.3550588871675142</v>
+        <v>-3.3639342266845937</v>
       </c>
       <c r="C20" s="1">
-        <v>-0.00060684416927367824</v>
+        <v>-0.00061200641855181897</v>
       </c>
       <c r="D20" s="1">
-        <v>6.0371289373614472e-06</v>
+        <v>6.0917971620748798e-06</v>
       </c>
       <c r="E20" s="1">
-        <v>-0.0032637360017151937</v>
+        <v>-0.0032563749952316716</v>
       </c>
       <c r="F20" s="1">
-        <v>-0.002623908505282331</v>
+        <v>-0.0024819177313509513</v>
       </c>
       <c r="G20" s="1">
-        <v>6.9919925277282411e-05</v>
+        <v>6.9768093934361036e-05</v>
       </c>
       <c r="H20" s="1">
-        <v>4.9567640689937594e-05</v>
+        <v>4.6881688580540101e-05</v>
       </c>
       <c r="I20" s="1">
-        <v>0.00045647219026555567</v>
+        <v>0.00047719247130240366</v>
       </c>
       <c r="J20" s="1">
-        <v>-0.0034251693199069924</v>
+        <v>-0.0031673924026200365</v>
       </c>
       <c r="K20" s="1">
-        <v>-0.011126430038011104</v>
+        <v>-0.011126039512338308</v>
       </c>
       <c r="L20" s="1">
-        <v>-0.011157860118229787</v>
+        <v>-0.011157041297398749</v>
       </c>
       <c r="M20" s="1">
-        <v>-0.011359583865757326</v>
+        <v>-0.011359234386883301</v>
       </c>
       <c r="N20" s="1">
-        <v>-0.0119816407522762</v>
+        <v>-0.011981507938177075</v>
       </c>
       <c r="O20" s="1">
-        <v>-0.00044122877753291002</v>
+        <v>-0.00044145965873242522</v>
       </c>
       <c r="P20" s="1">
-        <v>-0.0004709281971202791</v>
+        <v>-0.00046680015462196515</v>
       </c>
       <c r="Q20" s="1">
-        <v>-0.00038447065858590807</v>
+        <v>-0.00038112758163610504</v>
       </c>
       <c r="R20" s="1">
-        <v>-0.00044343152738088461</v>
+        <v>-0.00044336246855281757</v>
       </c>
       <c r="S20" s="1">
-        <v>-2.1771142384699685e-05</v>
+        <v>-2.1825354690591048e-05</v>
       </c>
       <c r="T20" s="1">
-        <v>-3.075578315740324e-05</v>
+        <v>-3.2369094098510547e-05</v>
       </c>
       <c r="U20" s="1">
-        <v>0.025530367920239778</v>
+        <v>0.025630226942049285</v>
       </c>
     </row>
   </sheetData>
@@ -4858,64 +4858,64 @@
         <v>25</v>
       </c>
       <c r="B2" s="1">
-        <v>0.1290550784314051</v>
+        <v>0.12865650630359843</v>
       </c>
       <c r="C2" s="1">
-        <v>2.5372229717461687e-05</v>
+        <v>2.5633065539506622e-05</v>
       </c>
       <c r="D2" s="1">
-        <v>-2.4719745666535293e-07</v>
+        <v>-2.4971894919604735e-07</v>
       </c>
       <c r="E2" s="1">
-        <v>0.00012404712103329898</v>
+        <v>0.00012475434486147391</v>
       </c>
       <c r="F2" s="1">
-        <v>0.0001409982471418917</v>
+        <v>0.00013535290497208258</v>
       </c>
       <c r="G2" s="1">
-        <v>-2.769163884754514e-06</v>
+        <v>-2.7843761274489451e-06</v>
       </c>
       <c r="H2" s="1">
-        <v>-3.003187256027996e-06</v>
+        <v>-2.9015436830474769e-06</v>
       </c>
       <c r="I2" s="1">
-        <v>-3.5268664486796196e-05</v>
+        <v>-3.592891166197734e-05</v>
       </c>
       <c r="J2" s="1">
-        <v>0.00011259467505759306</v>
+        <v>0.00010810428761616173</v>
       </c>
       <c r="K2" s="1">
-        <v>-3.6609200714691767e-06</v>
+        <v>-3.710685196202883e-06</v>
       </c>
       <c r="L2" s="1">
-        <v>-2.2815698502796602e-06</v>
+        <v>-2.2891310678841236e-06</v>
       </c>
       <c r="M2" s="1">
-        <v>-4.4632918653074346e-06</v>
+        <v>-4.5233877271275376e-06</v>
       </c>
       <c r="N2" s="1">
-        <v>1.5807825649789206e-05</v>
+        <v>1.5647887388135678e-05</v>
       </c>
       <c r="O2" s="1">
-        <v>1.5244236748816195e-06</v>
+        <v>1.3367012488745612e-06</v>
       </c>
       <c r="P2" s="1">
-        <v>-9.3127769862534026e-07</v>
+        <v>-9.2710632236149529e-07</v>
       </c>
       <c r="Q2" s="1">
-        <v>-8.8035729792767415e-07</v>
+        <v>-8.4528613444535497e-07</v>
       </c>
       <c r="R2" s="1">
-        <v>-4.3390260688678819e-07</v>
+        <v>-4.5384413556777477e-07</v>
       </c>
       <c r="S2" s="1">
-        <v>-3.2758105011786471e-07</v>
+        <v>-2.0228992578141567e-07</v>
       </c>
       <c r="T2" s="1">
-        <v>8.1396242043655888e-07</v>
+        <v>9.8782267764550145e-07</v>
       </c>
       <c r="U2" s="1">
-        <v>-0.00056705828223935716</v>
+        <v>-0.00057285624541074116</v>
       </c>
     </row>
     <row r="3">
@@ -4923,64 +4923,64 @@
         <v>26</v>
       </c>
       <c r="B3" s="1">
-        <v>-0.0015642370072520523</v>
+        <v>-0.0015602417075983972</v>
       </c>
       <c r="C3" s="1">
-        <v>-2.4719745666535293e-07</v>
+        <v>-2.4971894919604735e-07</v>
       </c>
       <c r="D3" s="1">
-        <v>2.6159466969547512e-09</v>
+        <v>2.6406247591459865e-09</v>
       </c>
       <c r="E3" s="1">
-        <v>-4.4889853876788989e-07</v>
+        <v>-4.5587105710181097e-07</v>
       </c>
       <c r="F3" s="1">
-        <v>-6.2934602799289736e-07</v>
+        <v>-5.6938153162636427e-07</v>
       </c>
       <c r="G3" s="1">
-        <v>9.8555241302239499e-09</v>
+        <v>1.0004965473843345e-08</v>
       </c>
       <c r="H3" s="1">
-        <v>1.229260472570688e-08</v>
+        <v>1.1205437065064671e-08</v>
       </c>
       <c r="I3" s="1">
-        <v>3.2018637539068647e-07</v>
+        <v>3.2486972384854985e-07</v>
       </c>
       <c r="J3" s="1">
-        <v>-1.1939865178688979e-06</v>
+        <v>-1.1399131614551098e-06</v>
       </c>
       <c r="K3" s="1">
-        <v>3.5737385296607603e-08</v>
+        <v>3.622103742936196e-08</v>
       </c>
       <c r="L3" s="1">
-        <v>1.3104673562696144e-08</v>
+        <v>1.3196735023309307e-08</v>
       </c>
       <c r="M3" s="1">
-        <v>7.479700962192396e-08</v>
+        <v>7.5334955401151047e-08</v>
       </c>
       <c r="N3" s="1">
-        <v>-9.0905177978563677e-08</v>
+        <v>-8.9279089134547392e-08</v>
       </c>
       <c r="O3" s="1">
-        <v>-2.7649337339026022e-08</v>
+        <v>-2.5470379862233073e-08</v>
       </c>
       <c r="P3" s="1">
-        <v>4.0057711494397657e-09</v>
+        <v>4.0959443102370172e-09</v>
       </c>
       <c r="Q3" s="1">
-        <v>6.3649288151740889e-09</v>
+        <v>6.2344892928901008e-09</v>
       </c>
       <c r="R3" s="1">
-        <v>5.4325126830681041e-09</v>
+        <v>5.7493802655987705e-09</v>
       </c>
       <c r="S3" s="1">
-        <v>3.7882392058201014e-09</v>
+        <v>2.4871573304386446e-09</v>
       </c>
       <c r="T3" s="1">
-        <v>-1.5183892099121193e-08</v>
+        <v>-1.6945706889078909e-08</v>
       </c>
       <c r="U3" s="1">
-        <v>5.0701967759764037e-06</v>
+        <v>5.1266081378157583e-06</v>
       </c>
     </row>
     <row r="4">
@@ -4988,64 +4988,64 @@
         <v>27</v>
       </c>
       <c r="B4" s="1">
-        <v>0.12141789279928761</v>
+        <v>0.11850699260539437</v>
       </c>
       <c r="C4" s="1">
-        <v>0.00012404712103329898</v>
+        <v>0.00012475434486147391</v>
       </c>
       <c r="D4" s="1">
-        <v>-4.4889853876788989e-07</v>
+        <v>-4.5587105710181097e-07</v>
       </c>
       <c r="E4" s="1">
-        <v>0.005306930305136617</v>
+        <v>0.0053073963665179165</v>
       </c>
       <c r="F4" s="1">
-        <v>0.0041524741722964538</v>
+        <v>0.0041384589705746773</v>
       </c>
       <c r="G4" s="1">
-        <v>-0.00010857862720212057</v>
+        <v>-0.00010859626344618802</v>
       </c>
       <c r="H4" s="1">
-        <v>-8.5355743879852734e-05</v>
+        <v>-8.5108853798993852e-05</v>
       </c>
       <c r="I4" s="1">
-        <v>3.5200391290237809e-05</v>
+        <v>3.0160657647656164e-05</v>
       </c>
       <c r="J4" s="1">
-        <v>0.00022820178929513837</v>
+        <v>0.00022912112761242829</v>
       </c>
       <c r="K4" s="1">
-        <v>-2.8485959653921157e-05</v>
+        <v>-2.8663923742298765e-05</v>
       </c>
       <c r="L4" s="1">
-        <v>-6.1291250182307318e-05</v>
+        <v>-6.1269524305992081e-05</v>
       </c>
       <c r="M4" s="1">
-        <v>-9.0143278799688977e-05</v>
+        <v>-9.0052864216856997e-05</v>
       </c>
       <c r="N4" s="1">
-        <v>-2.4799912304670378e-05</v>
+        <v>-2.5331231034010718e-05</v>
       </c>
       <c r="O4" s="1">
-        <v>-2.6384403151939858e-05</v>
+        <v>-2.6994304810170735e-05</v>
       </c>
       <c r="P4" s="1">
-        <v>1.3986906991703348e-06</v>
+        <v>1.5351740476534268e-06</v>
       </c>
       <c r="Q4" s="1">
-        <v>-1.0870471788471564e-05</v>
+        <v>-1.0900746984181467e-05</v>
       </c>
       <c r="R4" s="1">
-        <v>1.4018050207121894e-05</v>
+        <v>1.3918553611674225e-05</v>
       </c>
       <c r="S4" s="1">
-        <v>4.5692509462751238e-05</v>
+        <v>4.5770978619707321e-05</v>
       </c>
       <c r="T4" s="1">
-        <v>2.6856107981527838e-05</v>
+        <v>2.6909307835798186e-05</v>
       </c>
       <c r="U4" s="1">
-        <v>-0.0048380791927874296</v>
+        <v>-0.0048505278507125667</v>
       </c>
     </row>
     <row r="5">
@@ -5053,64 +5053,64 @@
         <v>28</v>
       </c>
       <c r="B5" s="1">
-        <v>-0.3484079191842045</v>
+        <v>-0.32998345918194105</v>
       </c>
       <c r="C5" s="1">
-        <v>0.0001409982471418917</v>
+        <v>0.00013535290497208258</v>
       </c>
       <c r="D5" s="1">
-        <v>-6.2934602799289736e-07</v>
+        <v>-5.6938153162636427e-07</v>
       </c>
       <c r="E5" s="1">
-        <v>0.0041524741722964538</v>
+        <v>0.0041384589705746773</v>
       </c>
       <c r="F5" s="1">
-        <v>0.01135974836696255</v>
+        <v>0.011596580140479693</v>
       </c>
       <c r="G5" s="1">
-        <v>-8.5697123379546369e-05</v>
+        <v>-8.5398957716474537e-05</v>
       </c>
       <c r="H5" s="1">
-        <v>-0.00022632133834310194</v>
+        <v>-0.00023059660387304726</v>
       </c>
       <c r="I5" s="1">
-        <v>4.7417752508920001e-05</v>
+        <v>4.4457161932191084e-05</v>
       </c>
       <c r="J5" s="1">
-        <v>-0.0044200840815834955</v>
+        <v>-0.0038335505722474992</v>
       </c>
       <c r="K5" s="1">
-        <v>-1.8532095740760482e-05</v>
+        <v>-1.7726998595642255e-05</v>
       </c>
       <c r="L5" s="1">
-        <v>-8.5171563860764627e-05</v>
+        <v>-8.5167403059395938e-05</v>
       </c>
       <c r="M5" s="1">
-        <v>-0.00010448921512903422</v>
+        <v>-0.00010474922038305635</v>
       </c>
       <c r="N5" s="1">
-        <v>-1.9426766588722168e-05</v>
+        <v>-1.4039465979736573e-05</v>
       </c>
       <c r="O5" s="1">
-        <v>-9.063788167212869e-05</v>
+        <v>-8.0020069585625493e-05</v>
       </c>
       <c r="P5" s="1">
-        <v>-1.6898918431832705e-05</v>
+        <v>-1.4454100623765817e-05</v>
       </c>
       <c r="Q5" s="1">
-        <v>-6.4808061991224674e-05</v>
+        <v>-6.1707559536502957e-05</v>
       </c>
       <c r="R5" s="1">
-        <v>2.7813740445902769e-05</v>
+        <v>3.0978150152265777e-05</v>
       </c>
       <c r="S5" s="1">
-        <v>4.588849816358849e-05</v>
+        <v>4.1888357856907799e-05</v>
       </c>
       <c r="T5" s="1">
-        <v>2.4355831192570402e-05</v>
+        <v>1.9843789435663707e-05</v>
       </c>
       <c r="U5" s="1">
-        <v>-0.0051861372303744942</v>
+        <v>-0.0050655650189119494</v>
       </c>
     </row>
     <row r="6">
@@ -5118,64 +5118,64 @@
         <v>29</v>
       </c>
       <c r="B6" s="1">
-        <v>-0.0029425397664613034</v>
+        <v>-0.0028857005262549608</v>
       </c>
       <c r="C6" s="1">
-        <v>-2.769163884754514e-06</v>
+        <v>-2.7843761274489451e-06</v>
       </c>
       <c r="D6" s="1">
-        <v>9.8555241302239499e-09</v>
+        <v>1.0004965473843345e-08</v>
       </c>
       <c r="E6" s="1">
-        <v>-0.00010857862720212057</v>
+        <v>-0.00010859626344618802</v>
       </c>
       <c r="F6" s="1">
-        <v>-8.5697123379546369e-05</v>
+        <v>-8.5398957716474537e-05</v>
       </c>
       <c r="G6" s="1">
-        <v>2.4312910201182817e-06</v>
+        <v>2.4317586157319805e-06</v>
       </c>
       <c r="H6" s="1">
-        <v>1.9299659292786231e-06</v>
+        <v>1.9246700758621795e-06</v>
       </c>
       <c r="I6" s="1">
-        <v>-4.0096604906683501e-07</v>
+        <v>-2.999877469030501e-07</v>
       </c>
       <c r="J6" s="1">
-        <v>-4.7456136556091353e-06</v>
+        <v>-4.9334254128792553e-06</v>
       </c>
       <c r="K6" s="1">
-        <v>5.5974500535847017e-07</v>
+        <v>5.6360700503616756e-07</v>
       </c>
       <c r="L6" s="1">
-        <v>1.5536530825235455e-06</v>
+        <v>1.5532415327865058e-06</v>
       </c>
       <c r="M6" s="1">
-        <v>2.8461130049606742e-06</v>
+        <v>2.8446726446387284e-06</v>
       </c>
       <c r="N6" s="1">
-        <v>1.9871450957834328e-06</v>
+        <v>1.9979041582441441e-06</v>
       </c>
       <c r="O6" s="1">
-        <v>1.8023272379378136e-07</v>
+        <v>1.9325226852656437e-07</v>
       </c>
       <c r="P6" s="1">
-        <v>-1.0431424282768715e-07</v>
+        <v>-1.0655884336029327e-07</v>
       </c>
       <c r="Q6" s="1">
-        <v>-6.7209103490735969e-08</v>
+        <v>-6.6722765783835597e-08</v>
       </c>
       <c r="R6" s="1">
-        <v>-3.4014397370706085e-07</v>
+        <v>-3.3784407197107484e-07</v>
       </c>
       <c r="S6" s="1">
-        <v>-7.3887566848427507e-07</v>
+        <v>-7.4138313855891113e-07</v>
       </c>
       <c r="T6" s="1">
-        <v>-4.2329188330309129e-07</v>
+        <v>-4.2545168866030223e-07</v>
       </c>
       <c r="U6" s="1">
-        <v>9.9531573470728715e-05</v>
+        <v>9.9809500981720443e-05</v>
       </c>
     </row>
     <row r="7">
@@ -5183,64 +5183,64 @@
         <v>30</v>
       </c>
       <c r="B7" s="1">
-        <v>0.0041080173284476816</v>
+        <v>0.0037650311913719975</v>
       </c>
       <c r="C7" s="1">
-        <v>-3.003187256027996e-06</v>
+        <v>-2.9015436830474769e-06</v>
       </c>
       <c r="D7" s="1">
-        <v>1.229260472570688e-08</v>
+        <v>1.1205437065064671e-08</v>
       </c>
       <c r="E7" s="1">
-        <v>-8.5355743879852734e-05</v>
+        <v>-8.5108853798993852e-05</v>
       </c>
       <c r="F7" s="1">
-        <v>-0.00022632133834310194</v>
+        <v>-0.00023059660387304726</v>
       </c>
       <c r="G7" s="1">
-        <v>1.9299659292786231e-06</v>
+        <v>1.9246700758621795e-06</v>
       </c>
       <c r="H7" s="1">
-        <v>4.9867197046323748e-06</v>
+        <v>5.0638611267757421e-06</v>
       </c>
       <c r="I7" s="1">
-        <v>1.5700363475098628e-07</v>
+        <v>2.3392403856126129e-07</v>
       </c>
       <c r="J7" s="1">
-        <v>8.1874377478047202e-05</v>
+        <v>7.043195089895901e-05</v>
       </c>
       <c r="K7" s="1">
-        <v>-9.8282396417161516e-08</v>
+        <v>-1.1340184253014274e-07</v>
       </c>
       <c r="L7" s="1">
-        <v>1.8170524511256787e-06</v>
+        <v>1.8160502209427133e-06</v>
       </c>
       <c r="M7" s="1">
-        <v>3.2913300536160663e-06</v>
+        <v>3.2975351582591502e-06</v>
       </c>
       <c r="N7" s="1">
-        <v>2.2698843270369256e-06</v>
+        <v>2.1709223339643549e-06</v>
       </c>
       <c r="O7" s="1">
-        <v>1.1631097216500488e-06</v>
+        <v>9.6493378371589648e-07</v>
       </c>
       <c r="P7" s="1">
-        <v>1.7222315110145989e-07</v>
+        <v>1.2583186782966163e-07</v>
       </c>
       <c r="Q7" s="1">
-        <v>3.9637183947395347e-07</v>
+        <v>3.3589401358005242e-07</v>
       </c>
       <c r="R7" s="1">
-        <v>-1.311877284962333e-06</v>
+        <v>-1.3710430171136523e-06</v>
       </c>
       <c r="S7" s="1">
-        <v>-5.7400629842798024e-07</v>
+        <v>-5.0166072718962023e-07</v>
       </c>
       <c r="T7" s="1">
-        <v>-1.0644983348544287e-07</v>
+        <v>-2.574096075025388e-08</v>
       </c>
       <c r="U7" s="1">
-        <v>0.00010408304776515641</v>
+        <v>0.00010192050702065635</v>
       </c>
     </row>
     <row r="8">
@@ -5248,64 +5248,64 @@
         <v>31</v>
       </c>
       <c r="B8" s="1">
-        <v>0.14266897744860821</v>
+        <v>0.13924069081939969</v>
       </c>
       <c r="C8" s="1">
-        <v>-3.5268664486796196e-05</v>
+        <v>-3.592891166197734e-05</v>
       </c>
       <c r="D8" s="1">
-        <v>3.2018637539068647e-07</v>
+        <v>3.2486972384854985e-07</v>
       </c>
       <c r="E8" s="1">
-        <v>3.5200391290237809e-05</v>
+        <v>3.0160657647656164e-05</v>
       </c>
       <c r="F8" s="1">
-        <v>4.7417752508920001e-05</v>
+        <v>4.4457161932191084e-05</v>
       </c>
       <c r="G8" s="1">
-        <v>-4.0096604906683501e-07</v>
+        <v>-2.999877469030501e-07</v>
       </c>
       <c r="H8" s="1">
-        <v>1.5700363475098628e-07</v>
+        <v>2.3392403856126129e-07</v>
       </c>
       <c r="I8" s="1">
-        <v>0.00046637124170738727</v>
+        <v>0.00046806391917013536</v>
       </c>
       <c r="J8" s="1">
-        <v>-7.8409807335443616e-05</v>
+        <v>-6.767328259376382e-05</v>
       </c>
       <c r="K8" s="1">
-        <v>4.7612336607544827e-06</v>
+        <v>4.8971029213998165e-06</v>
       </c>
       <c r="L8" s="1">
-        <v>-2.7718911476455571e-06</v>
+        <v>-2.6349911538086757e-06</v>
       </c>
       <c r="M8" s="1">
-        <v>-4.6555956715312616e-06</v>
+        <v>-3.6278722126144631e-06</v>
       </c>
       <c r="N8" s="1">
-        <v>5.9514917974893744e-06</v>
+        <v>6.1445959420708411e-06</v>
       </c>
       <c r="O8" s="1">
-        <v>-2.1288013900004273e-06</v>
+        <v>-3.4524052512350786e-06</v>
       </c>
       <c r="P8" s="1">
-        <v>1.142039512144827e-06</v>
+        <v>4.6817946563759978e-07</v>
       </c>
       <c r="Q8" s="1">
-        <v>-1.2379171423166372e-05</v>
+        <v>-1.3736817999363243e-05</v>
       </c>
       <c r="R8" s="1">
-        <v>1.8466723143560717e-07</v>
+        <v>-3.9461011789073033e-07</v>
       </c>
       <c r="S8" s="1">
-        <v>1.8895119978766135e-06</v>
+        <v>1.4942162142190766e-06</v>
       </c>
       <c r="T8" s="1">
-        <v>7.9592600821274514e-06</v>
+        <v>6.9374760244850411e-06</v>
       </c>
       <c r="U8" s="1">
-        <v>0.0005407313485469628</v>
+        <v>0.00056111458660694025</v>
       </c>
     </row>
     <row r="9">
@@ -5313,64 +5313,64 @@
         <v>32</v>
       </c>
       <c r="B9" s="1">
-        <v>0.65114234918579639</v>
+        <v>-0.10215910768622928</v>
       </c>
       <c r="C9" s="1">
-        <v>0.00011259467505759306</v>
+        <v>0.00010810428761616173</v>
       </c>
       <c r="D9" s="1">
-        <v>-1.1939865178688979e-06</v>
+        <v>-1.1399131614551098e-06</v>
       </c>
       <c r="E9" s="1">
-        <v>0.00022820178929513837</v>
+        <v>0.00022912112761242829</v>
       </c>
       <c r="F9" s="1">
-        <v>-0.0044200840815834955</v>
+        <v>-0.0038335505722474992</v>
       </c>
       <c r="G9" s="1">
-        <v>-4.7456136556091353e-06</v>
+        <v>-4.9334254128792553e-06</v>
       </c>
       <c r="H9" s="1">
-        <v>8.1874377478047202e-05</v>
+        <v>7.043195089895901e-05</v>
       </c>
       <c r="I9" s="1">
-        <v>-7.8409807335443616e-05</v>
+        <v>-6.767328259376382e-05</v>
       </c>
       <c r="J9" s="1">
-        <v>0.28137038305056294</v>
+        <v>0.046987740568991222</v>
       </c>
       <c r="K9" s="1">
-        <v>-1.5702452196111417e-05</v>
+        <v>-1.5267251485265726e-05</v>
       </c>
       <c r="L9" s="1">
-        <v>-5.1561640785542054e-06</v>
+        <v>1.6634388531637933e-06</v>
       </c>
       <c r="M9" s="1">
-        <v>9.315926318404116e-06</v>
+        <v>1.4550950460289242e-05</v>
       </c>
       <c r="N9" s="1">
-        <v>7.5074895456872816e-05</v>
+        <v>-4.7999280588710943e-05</v>
       </c>
       <c r="O9" s="1">
-        <v>-0.00013322830854816073</v>
+        <v>-0.00016172416141642856</v>
       </c>
       <c r="P9" s="1">
-        <v>-6.1699623373261207e-05</v>
+        <v>-4.8246347565924756e-05</v>
       </c>
       <c r="Q9" s="1">
-        <v>-0.0001376581249160255</v>
+        <v>-8.6865770100635648e-05</v>
       </c>
       <c r="R9" s="1">
-        <v>-4.5185962515093366e-05</v>
+        <v>-5.1273158058105614e-05</v>
       </c>
       <c r="S9" s="1">
-        <v>6.0203495934073931e-05</v>
+        <v>6.508036892464331e-05</v>
       </c>
       <c r="T9" s="1">
-        <v>6.9980440054005094e-05</v>
+        <v>7.5241212426564952e-05</v>
       </c>
       <c r="U9" s="1">
-        <v>-0.0023282943754771991</v>
+        <v>-0.0022474894764952604</v>
       </c>
     </row>
     <row r="10">
@@ -5378,64 +5378,64 @@
         <v>33</v>
       </c>
       <c r="B10" s="1">
-        <v>0.34391330980274615</v>
+        <v>0.34399460824641026</v>
       </c>
       <c r="C10" s="1">
-        <v>-3.6609200714691767e-06</v>
+        <v>-3.710685196202883e-06</v>
       </c>
       <c r="D10" s="1">
-        <v>3.5737385296607603e-08</v>
+        <v>3.622103742936196e-08</v>
       </c>
       <c r="E10" s="1">
-        <v>-2.8485959653921157e-05</v>
+        <v>-2.8663923742298765e-05</v>
       </c>
       <c r="F10" s="1">
-        <v>-1.8532095740760482e-05</v>
+        <v>-1.7726998595642255e-05</v>
       </c>
       <c r="G10" s="1">
-        <v>5.5974500535847017e-07</v>
+        <v>5.6360700503616756e-07</v>
       </c>
       <c r="H10" s="1">
-        <v>-9.8282396417161516e-08</v>
+        <v>-1.1340184253014274e-07</v>
       </c>
       <c r="I10" s="1">
-        <v>4.7612336607544827e-06</v>
+        <v>4.8971029213998165e-06</v>
       </c>
       <c r="J10" s="1">
-        <v>-1.5702452196111417e-05</v>
+        <v>-1.5267251485265726e-05</v>
       </c>
       <c r="K10" s="1">
-        <v>0.0077954473568646286</v>
+        <v>0.0077951327307296519</v>
       </c>
       <c r="L10" s="1">
-        <v>0.0068480892069469708</v>
+        <v>0.0068477959535006398</v>
       </c>
       <c r="M10" s="1">
-        <v>0.0068475789656990268</v>
+        <v>0.0068472933888096398</v>
       </c>
       <c r="N10" s="1">
-        <v>0.0068451479717149084</v>
+        <v>0.006844866661235704</v>
       </c>
       <c r="O10" s="1">
-        <v>1.6387705341274449e-05</v>
+        <v>1.6476005059209202e-05</v>
       </c>
       <c r="P10" s="1">
-        <v>1.3970222328958082e-05</v>
+        <v>1.401856061533799e-05</v>
       </c>
       <c r="Q10" s="1">
-        <v>-8.9758671531937883e-07</v>
+        <v>-8.7617384851009793e-07</v>
       </c>
       <c r="R10" s="1">
-        <v>-6.5357902449927912e-06</v>
+        <v>-6.5337299136875072e-06</v>
       </c>
       <c r="S10" s="1">
-        <v>-2.7472367023015654e-06</v>
+        <v>-2.7984065370442457e-06</v>
       </c>
       <c r="T10" s="1">
-        <v>4.6178438494252462e-05</v>
+        <v>4.6145236016874636e-05</v>
       </c>
       <c r="U10" s="1">
-        <v>-0.0067644243916794682</v>
+        <v>-0.006763056019630626</v>
       </c>
     </row>
     <row r="11">
@@ -5443,64 +5443,64 @@
         <v>34</v>
       </c>
       <c r="B11" s="1">
-        <v>0.84050249418149658</v>
+        <v>0.84061146653643071</v>
       </c>
       <c r="C11" s="1">
-        <v>-2.2815698502796602e-06</v>
+        <v>-2.2891310678841236e-06</v>
       </c>
       <c r="D11" s="1">
-        <v>1.3104673562696144e-08</v>
+        <v>1.3196735023309307e-08</v>
       </c>
       <c r="E11" s="1">
-        <v>-6.1291250182307318e-05</v>
+        <v>-6.1269524305992081e-05</v>
       </c>
       <c r="F11" s="1">
-        <v>-8.5171563860764627e-05</v>
+        <v>-8.5167403059395938e-05</v>
       </c>
       <c r="G11" s="1">
-        <v>1.5536530825235455e-06</v>
+        <v>1.5532415327865058e-06</v>
       </c>
       <c r="H11" s="1">
-        <v>1.8170524511256787e-06</v>
+        <v>1.8160502209427133e-06</v>
       </c>
       <c r="I11" s="1">
-        <v>-2.7718911476455571e-06</v>
+        <v>-2.6349911538086757e-06</v>
       </c>
       <c r="J11" s="1">
-        <v>-5.1561640785542054e-06</v>
+        <v>1.6634388531637933e-06</v>
       </c>
       <c r="K11" s="1">
-        <v>0.0068480892069469708</v>
+        <v>0.0068477959535006398</v>
       </c>
       <c r="L11" s="1">
-        <v>0.0071179687924154229</v>
+        <v>0.0071176071103159454</v>
       </c>
       <c r="M11" s="1">
-        <v>0.0068509505863451172</v>
+        <v>0.0068506541860618997</v>
       </c>
       <c r="N11" s="1">
-        <v>0.0068516864554011223</v>
+        <v>0.0068514044027105352</v>
       </c>
       <c r="O11" s="1">
-        <v>1.0464357277472425e-05</v>
+        <v>1.0543588387243132e-05</v>
       </c>
       <c r="P11" s="1">
-        <v>3.7762169988851155e-06</v>
+        <v>3.8093995963350508e-06</v>
       </c>
       <c r="Q11" s="1">
-        <v>-1.7829606012952034e-05</v>
+        <v>-1.7808578008296773e-05</v>
       </c>
       <c r="R11" s="1">
-        <v>-1.4497001438282053e-05</v>
+        <v>-1.4493321029006038e-05</v>
       </c>
       <c r="S11" s="1">
-        <v>1.6567015502202022e-06</v>
+        <v>1.6754360972638841e-06</v>
       </c>
       <c r="T11" s="1">
-        <v>3.6408965127432103e-05</v>
+        <v>3.634793034540649e-05</v>
       </c>
       <c r="U11" s="1">
-        <v>-0.0067763003828995418</v>
+        <v>-0.0067759956661537103</v>
       </c>
     </row>
     <row r="12">
@@ -5508,64 +5508,64 @@
         <v>35</v>
       </c>
       <c r="B12" s="1">
-        <v>1.0389815340947459</v>
+        <v>1.0393025674354379</v>
       </c>
       <c r="C12" s="1">
-        <v>-4.4632918653074346e-06</v>
+        <v>-4.5233877271275376e-06</v>
       </c>
       <c r="D12" s="1">
-        <v>7.479700962192396e-08</v>
+        <v>7.5334955401151047e-08</v>
       </c>
       <c r="E12" s="1">
-        <v>-9.0143278799688977e-05</v>
+        <v>-9.0052864216856997e-05</v>
       </c>
       <c r="F12" s="1">
-        <v>-0.00010448921512903422</v>
+        <v>-0.00010474922038305635</v>
       </c>
       <c r="G12" s="1">
-        <v>2.8461130049606742e-06</v>
+        <v>2.8446726446387284e-06</v>
       </c>
       <c r="H12" s="1">
-        <v>3.2913300536160663e-06</v>
+        <v>3.2975351582591502e-06</v>
       </c>
       <c r="I12" s="1">
-        <v>-4.6555956715312616e-06</v>
+        <v>-3.6278722126144631e-06</v>
       </c>
       <c r="J12" s="1">
-        <v>9.315926318404116e-06</v>
+        <v>1.4550950460289242e-05</v>
       </c>
       <c r="K12" s="1">
-        <v>0.0068475789656990268</v>
+        <v>0.0068472933888096398</v>
       </c>
       <c r="L12" s="1">
-        <v>0.0068509505863451172</v>
+        <v>0.0068506541860618997</v>
       </c>
       <c r="M12" s="1">
-        <v>0.007039784559686308</v>
+        <v>0.0070394487544362264</v>
       </c>
       <c r="N12" s="1">
-        <v>0.0069431696845458305</v>
+        <v>0.0069428421387842847</v>
       </c>
       <c r="O12" s="1">
-        <v>1.0603536796473842e-05</v>
+        <v>1.0673002756107174e-05</v>
       </c>
       <c r="P12" s="1">
-        <v>1.0115762680008264e-05</v>
+        <v>1.0181296710006079e-05</v>
       </c>
       <c r="Q12" s="1">
-        <v>-1.2329161232572344e-05</v>
+        <v>-1.2302436389523406e-05</v>
       </c>
       <c r="R12" s="1">
-        <v>-4.3813791969198926e-06</v>
+        <v>-4.3340041445908276e-06</v>
       </c>
       <c r="S12" s="1">
-        <v>-1.6161043795994327e-05</v>
+        <v>-1.6160368397991903e-05</v>
       </c>
       <c r="T12" s="1">
-        <v>1.745264322339525e-05</v>
+        <v>1.7443042705723729e-05</v>
       </c>
       <c r="U12" s="1">
-        <v>-0.0068859587546995296</v>
+        <v>-0.0068849386945654982</v>
       </c>
     </row>
     <row r="13">
@@ -5573,64 +5573,64 @@
         <v>36</v>
       </c>
       <c r="B13" s="1">
-        <v>1.0900837857683476</v>
+        <v>1.0900588985825801</v>
       </c>
       <c r="C13" s="1">
-        <v>1.5807825649789206e-05</v>
+        <v>1.5647887388135678e-05</v>
       </c>
       <c r="D13" s="1">
-        <v>-9.0905177978563677e-08</v>
+        <v>-8.9279089134547392e-08</v>
       </c>
       <c r="E13" s="1">
-        <v>-2.4799912304670378e-05</v>
+        <v>-2.5331231034010718e-05</v>
       </c>
       <c r="F13" s="1">
-        <v>-1.9426766588722168e-05</v>
+        <v>-1.4039465979736573e-05</v>
       </c>
       <c r="G13" s="1">
-        <v>1.9871450957834328e-06</v>
+        <v>1.9979041582441441e-06</v>
       </c>
       <c r="H13" s="1">
-        <v>2.2698843270369256e-06</v>
+        <v>2.1709223339643549e-06</v>
       </c>
       <c r="I13" s="1">
-        <v>5.9514917974893744e-06</v>
+        <v>6.1445959420708411e-06</v>
       </c>
       <c r="J13" s="1">
-        <v>7.5074895456872816e-05</v>
+        <v>-4.7999280588710943e-05</v>
       </c>
       <c r="K13" s="1">
-        <v>0.0068451479717149084</v>
+        <v>0.006844866661235704</v>
       </c>
       <c r="L13" s="1">
-        <v>0.0068516864554011223</v>
+        <v>0.0068514044027105352</v>
       </c>
       <c r="M13" s="1">
-        <v>0.0069431696845458305</v>
+        <v>0.0069428421387842847</v>
       </c>
       <c r="N13" s="1">
-        <v>0.0074826123980423096</v>
+        <v>0.0074822102264928718</v>
       </c>
       <c r="O13" s="1">
-        <v>1.2165168820358141e-05</v>
+        <v>1.2361337693425078e-05</v>
       </c>
       <c r="P13" s="1">
-        <v>1.3006123754164602e-05</v>
+        <v>1.3065120417280159e-05</v>
       </c>
       <c r="Q13" s="1">
-        <v>-1.5220942011260668e-05</v>
+        <v>-1.4966345177700141e-05</v>
       </c>
       <c r="R13" s="1">
-        <v>5.0626908764946782e-07</v>
+        <v>6.2169158605460037e-07</v>
       </c>
       <c r="S13" s="1">
-        <v>-1.2463594676799792e-05</v>
+        <v>-1.2505098906838797e-05</v>
       </c>
       <c r="T13" s="1">
-        <v>2.0403009605557128e-05</v>
+        <v>2.0223157610882112e-05</v>
       </c>
       <c r="U13" s="1">
-        <v>-0.0075056411170580546</v>
+        <v>-0.0075019358829996816</v>
       </c>
     </row>
     <row r="14">
@@ -5638,64 +5638,64 @@
         <v>37</v>
       </c>
       <c r="B14" s="1">
-        <v>0.044388371541880675</v>
+        <v>0.04464973722491701</v>
       </c>
       <c r="C14" s="1">
-        <v>1.5244236748816195e-06</v>
+        <v>1.3367012488745612e-06</v>
       </c>
       <c r="D14" s="1">
-        <v>-2.7649337339026022e-08</v>
+        <v>-2.5470379862233073e-08</v>
       </c>
       <c r="E14" s="1">
-        <v>-2.6384403151939858e-05</v>
+        <v>-2.6994304810170735e-05</v>
       </c>
       <c r="F14" s="1">
-        <v>-9.063788167212869e-05</v>
+        <v>-8.0020069585625493e-05</v>
       </c>
       <c r="G14" s="1">
-        <v>1.8023272379378136e-07</v>
+        <v>1.9325226852656437e-07</v>
       </c>
       <c r="H14" s="1">
-        <v>1.1631097216500488e-06</v>
+        <v>9.6493378371589648e-07</v>
       </c>
       <c r="I14" s="1">
-        <v>-2.1288013900004273e-06</v>
+        <v>-3.4524052512350786e-06</v>
       </c>
       <c r="J14" s="1">
-        <v>-0.00013322830854816073</v>
+        <v>-0.00016172416141642856</v>
       </c>
       <c r="K14" s="1">
-        <v>1.6387705341274449e-05</v>
+        <v>1.6476005059209202e-05</v>
       </c>
       <c r="L14" s="1">
-        <v>1.0464357277472425e-05</v>
+        <v>1.0543588387243132e-05</v>
       </c>
       <c r="M14" s="1">
-        <v>1.0603536796473842e-05</v>
+        <v>1.0673002756107174e-05</v>
       </c>
       <c r="N14" s="1">
-        <v>1.2165168820358141e-05</v>
+        <v>1.2361337693425078e-05</v>
       </c>
       <c r="O14" s="1">
-        <v>0.00090117468374436552</v>
+        <v>0.00090171586198419245</v>
       </c>
       <c r="P14" s="1">
-        <v>0.00043622482921517409</v>
+        <v>0.00043625583196638075</v>
       </c>
       <c r="Q14" s="1">
-        <v>0.00043697973003929593</v>
+        <v>0.00043717898971065792</v>
       </c>
       <c r="R14" s="1">
-        <v>0.00043596233815097101</v>
+        <v>0.00043601413642779108</v>
       </c>
       <c r="S14" s="1">
-        <v>-1.6523491122287601e-05</v>
+        <v>-1.6694455548911974e-05</v>
       </c>
       <c r="T14" s="1">
-        <v>-2.4734458422187117e-05</v>
+        <v>-2.4954763000967663e-05</v>
       </c>
       <c r="U14" s="1">
-        <v>-0.0004330798949731891</v>
+        <v>-0.00042866249842238882</v>
       </c>
     </row>
     <row r="15">
@@ -5703,64 +5703,64 @@
         <v>38</v>
       </c>
       <c r="B15" s="1">
-        <v>-0.053729458329757757</v>
+        <v>-0.053658861512627144</v>
       </c>
       <c r="C15" s="1">
-        <v>-9.3127769862534026e-07</v>
+        <v>-9.2710632236149529e-07</v>
       </c>
       <c r="D15" s="1">
-        <v>4.0057711494397657e-09</v>
+        <v>4.0959443102370172e-09</v>
       </c>
       <c r="E15" s="1">
-        <v>1.3986906991703348e-06</v>
+        <v>1.5351740476534268e-06</v>
       </c>
       <c r="F15" s="1">
-        <v>-1.6898918431832705e-05</v>
+        <v>-1.4454100623765817e-05</v>
       </c>
       <c r="G15" s="1">
-        <v>-1.0431424282768715e-07</v>
+        <v>-1.0655884336029327e-07</v>
       </c>
       <c r="H15" s="1">
-        <v>1.7222315110145989e-07</v>
+        <v>1.2583186782966163e-07</v>
       </c>
       <c r="I15" s="1">
-        <v>1.142039512144827e-06</v>
+        <v>4.6817946563759978e-07</v>
       </c>
       <c r="J15" s="1">
-        <v>-6.1699623373261207e-05</v>
+        <v>-4.8246347565924756e-05</v>
       </c>
       <c r="K15" s="1">
-        <v>1.3970222328958082e-05</v>
+        <v>1.401856061533799e-05</v>
       </c>
       <c r="L15" s="1">
-        <v>3.7762169988851155e-06</v>
+        <v>3.8093995963350508e-06</v>
       </c>
       <c r="M15" s="1">
-        <v>1.0115762680008264e-05</v>
+        <v>1.0181296710006079e-05</v>
       </c>
       <c r="N15" s="1">
-        <v>1.3006123754164602e-05</v>
+        <v>1.3065120417280159e-05</v>
       </c>
       <c r="O15" s="1">
-        <v>0.00043622482921517409</v>
+        <v>0.00043625583196638075</v>
       </c>
       <c r="P15" s="1">
-        <v>0.0010974322126659746</v>
+        <v>0.0010970706043922415</v>
       </c>
       <c r="Q15" s="1">
-        <v>0.00043570403643474739</v>
+        <v>0.00043567173433267089</v>
       </c>
       <c r="R15" s="1">
-        <v>0.00043565608186716217</v>
+        <v>0.00043558478134559519</v>
       </c>
       <c r="S15" s="1">
-        <v>-1.3368473432029794e-05</v>
+        <v>-1.338389697270165e-05</v>
       </c>
       <c r="T15" s="1">
-        <v>-2.4318282387089813e-05</v>
+        <v>-2.4322676934378044e-05</v>
       </c>
       <c r="U15" s="1">
-        <v>-0.00040618964473969105</v>
+        <v>-0.00040610525075488428</v>
       </c>
     </row>
     <row r="16">
@@ -5768,64 +5768,64 @@
         <v>39</v>
       </c>
       <c r="B16" s="1">
-        <v>-0.058854921133957842</v>
+        <v>-0.058554296531172292</v>
       </c>
       <c r="C16" s="1">
-        <v>-8.8035729792767415e-07</v>
+        <v>-8.4528613444535497e-07</v>
       </c>
       <c r="D16" s="1">
-        <v>6.3649288151740889e-09</v>
+        <v>6.2344892928901008e-09</v>
       </c>
       <c r="E16" s="1">
-        <v>-1.0870471788471564e-05</v>
+        <v>-1.0900746984181467e-05</v>
       </c>
       <c r="F16" s="1">
-        <v>-6.4808061991224674e-05</v>
+        <v>-6.1707559536502957e-05</v>
       </c>
       <c r="G16" s="1">
-        <v>-6.7209103490735969e-08</v>
+        <v>-6.6722765783835597e-08</v>
       </c>
       <c r="H16" s="1">
-        <v>3.9637183947395347e-07</v>
+        <v>3.3589401358005242e-07</v>
       </c>
       <c r="I16" s="1">
-        <v>-1.2379171423166372e-05</v>
+        <v>-1.3736817999363243e-05</v>
       </c>
       <c r="J16" s="1">
-        <v>-0.0001376581249160255</v>
+        <v>-8.6865770100635648e-05</v>
       </c>
       <c r="K16" s="1">
-        <v>-8.9758671531937883e-07</v>
+        <v>-8.7617384851009793e-07</v>
       </c>
       <c r="L16" s="1">
-        <v>-1.7829606012952034e-05</v>
+        <v>-1.7808578008296773e-05</v>
       </c>
       <c r="M16" s="1">
-        <v>-1.2329161232572344e-05</v>
+        <v>-1.2302436389523406e-05</v>
       </c>
       <c r="N16" s="1">
-        <v>-1.5220942011260668e-05</v>
+        <v>-1.4966345177700141e-05</v>
       </c>
       <c r="O16" s="1">
-        <v>0.00043697973003929593</v>
+        <v>0.00043717898971065792</v>
       </c>
       <c r="P16" s="1">
-        <v>0.00043570403643474739</v>
+        <v>0.00043567173433267089</v>
       </c>
       <c r="Q16" s="1">
-        <v>0.00084122487216817244</v>
+        <v>0.00084121619388464021</v>
       </c>
       <c r="R16" s="1">
-        <v>0.00043631528479750589</v>
+        <v>0.00043629418553138533</v>
       </c>
       <c r="S16" s="1">
-        <v>-1.6593807361918248e-05</v>
+        <v>-1.6609231381459883e-05</v>
       </c>
       <c r="T16" s="1">
-        <v>-1.6399181574662756e-05</v>
+        <v>-1.6461996538144522e-05</v>
       </c>
       <c r="U16" s="1">
-        <v>-0.00037181810181122015</v>
+        <v>-0.00037222003268838936</v>
       </c>
     </row>
     <row r="17">
@@ -5833,64 +5833,64 @@
         <v>40</v>
       </c>
       <c r="B17" s="1">
-        <v>-0.01735304344164559</v>
+        <v>-0.017287613556846961</v>
       </c>
       <c r="C17" s="1">
-        <v>-4.3390260688678819e-07</v>
+        <v>-4.5384413556777477e-07</v>
       </c>
       <c r="D17" s="1">
-        <v>5.4325126830681041e-09</v>
+        <v>5.7493802655987705e-09</v>
       </c>
       <c r="E17" s="1">
-        <v>1.4018050207121894e-05</v>
+        <v>1.3918553611674225e-05</v>
       </c>
       <c r="F17" s="1">
-        <v>2.7813740445902769e-05</v>
+        <v>3.0978150152265777e-05</v>
       </c>
       <c r="G17" s="1">
-        <v>-3.4014397370706085e-07</v>
+        <v>-3.3784407197107484e-07</v>
       </c>
       <c r="H17" s="1">
-        <v>-1.311877284962333e-06</v>
+        <v>-1.3710430171136523e-06</v>
       </c>
       <c r="I17" s="1">
-        <v>1.8466723143560717e-07</v>
+        <v>-3.9461011789073033e-07</v>
       </c>
       <c r="J17" s="1">
-        <v>-4.5185962515093366e-05</v>
+        <v>-5.1273158058105614e-05</v>
       </c>
       <c r="K17" s="1">
-        <v>-6.5357902449927912e-06</v>
+        <v>-6.5337299136875072e-06</v>
       </c>
       <c r="L17" s="1">
-        <v>-1.4497001438282053e-05</v>
+        <v>-1.4493321029006038e-05</v>
       </c>
       <c r="M17" s="1">
-        <v>-4.3813791969198926e-06</v>
+        <v>-4.3340041445908276e-06</v>
       </c>
       <c r="N17" s="1">
-        <v>5.0626908764946782e-07</v>
+        <v>6.2169158605460037e-07</v>
       </c>
       <c r="O17" s="1">
-        <v>0.00043596233815097101</v>
+        <v>0.00043601413642779108</v>
       </c>
       <c r="P17" s="1">
-        <v>0.00043565608186716217</v>
+        <v>0.00043558478134559519</v>
       </c>
       <c r="Q17" s="1">
-        <v>0.00043631528479750589</v>
+        <v>0.00043629418553138533</v>
       </c>
       <c r="R17" s="1">
-        <v>0.00060607465043004279</v>
+        <v>0.00060597496305861876</v>
       </c>
       <c r="S17" s="1">
-        <v>-1.4669249836127124e-05</v>
+        <v>-1.466315216708603e-05</v>
       </c>
       <c r="T17" s="1">
-        <v>-2.5135524103097539e-05</v>
+        <v>-2.5223155362406316e-05</v>
       </c>
       <c r="U17" s="1">
-        <v>-0.00041546688589019998</v>
+        <v>-0.00041485236180595711</v>
       </c>
     </row>
     <row r="18">
@@ -5898,64 +5898,64 @@
         <v>41</v>
       </c>
       <c r="B18" s="1">
-        <v>-0.14584260182801398</v>
+        <v>-0.14628110000520919</v>
       </c>
       <c r="C18" s="1">
-        <v>-3.2758105011786471e-07</v>
+        <v>-2.0228992578141567e-07</v>
       </c>
       <c r="D18" s="1">
-        <v>3.7882392058201014e-09</v>
+        <v>2.4871573304386446e-09</v>
       </c>
       <c r="E18" s="1">
-        <v>4.5692509462751238e-05</v>
+        <v>4.5770978619707321e-05</v>
       </c>
       <c r="F18" s="1">
-        <v>4.588849816358849e-05</v>
+        <v>4.1888357856907799e-05</v>
       </c>
       <c r="G18" s="1">
-        <v>-7.3887566848427507e-07</v>
+        <v>-7.4138313855891113e-07</v>
       </c>
       <c r="H18" s="1">
-        <v>-5.7400629842798024e-07</v>
+        <v>-5.0166072718962023e-07</v>
       </c>
       <c r="I18" s="1">
-        <v>1.8895119978766135e-06</v>
+        <v>1.4942162142190766e-06</v>
       </c>
       <c r="J18" s="1">
-        <v>6.0203495934073931e-05</v>
+        <v>6.508036892464331e-05</v>
       </c>
       <c r="K18" s="1">
-        <v>-2.7472367023015654e-06</v>
+        <v>-2.7984065370442457e-06</v>
       </c>
       <c r="L18" s="1">
-        <v>1.6567015502202022e-06</v>
+        <v>1.6754360972638841e-06</v>
       </c>
       <c r="M18" s="1">
-        <v>-1.6161043795994327e-05</v>
+        <v>-1.6160368397991903e-05</v>
       </c>
       <c r="N18" s="1">
-        <v>-1.2463594676799792e-05</v>
+        <v>-1.2505098906838797e-05</v>
       </c>
       <c r="O18" s="1">
-        <v>-1.6523491122287601e-05</v>
+        <v>-1.6694455548911974e-05</v>
       </c>
       <c r="P18" s="1">
-        <v>-1.3368473432029794e-05</v>
+        <v>-1.338389697270165e-05</v>
       </c>
       <c r="Q18" s="1">
-        <v>-1.6593807361918248e-05</v>
+        <v>-1.6609231381459883e-05</v>
       </c>
       <c r="R18" s="1">
-        <v>-1.4669249836127124e-05</v>
+        <v>-1.466315216708603e-05</v>
       </c>
       <c r="S18" s="1">
-        <v>0.00099766480442068295</v>
+        <v>0.00099753049791134101</v>
       </c>
       <c r="T18" s="1">
-        <v>8.2673601611571933e-05</v>
+        <v>8.2743175737534866e-05</v>
       </c>
       <c r="U18" s="1">
-        <v>-6.2946590844315859e-05</v>
+        <v>-6.5377898458079711e-05</v>
       </c>
     </row>
     <row r="19">
@@ -5963,64 +5963,64 @@
         <v>42</v>
       </c>
       <c r="B19" s="1">
-        <v>0.040594882137808042</v>
+        <v>0.039887886944477709</v>
       </c>
       <c r="C19" s="1">
-        <v>8.1396242043655888e-07</v>
+        <v>9.8782267764550145e-07</v>
       </c>
       <c r="D19" s="1">
-        <v>-1.5183892099121193e-08</v>
+        <v>-1.6945706889078909e-08</v>
       </c>
       <c r="E19" s="1">
-        <v>2.6856107981527838e-05</v>
+        <v>2.6909307835798186e-05</v>
       </c>
       <c r="F19" s="1">
-        <v>2.4355831192570402e-05</v>
+        <v>1.9843789435663707e-05</v>
       </c>
       <c r="G19" s="1">
-        <v>-4.2329188330309129e-07</v>
+        <v>-4.2545168866030223e-07</v>
       </c>
       <c r="H19" s="1">
-        <v>-1.0644983348544287e-07</v>
+        <v>-2.574096075025388e-08</v>
       </c>
       <c r="I19" s="1">
-        <v>7.9592600821274514e-06</v>
+        <v>6.9374760244850411e-06</v>
       </c>
       <c r="J19" s="1">
-        <v>6.9980440054005094e-05</v>
+        <v>7.5241212426564952e-05</v>
       </c>
       <c r="K19" s="1">
-        <v>4.6178438494252462e-05</v>
+        <v>4.6145236016874636e-05</v>
       </c>
       <c r="L19" s="1">
-        <v>3.6408965127432103e-05</v>
+        <v>3.634793034540649e-05</v>
       </c>
       <c r="M19" s="1">
-        <v>1.745264322339525e-05</v>
+        <v>1.7443042705723729e-05</v>
       </c>
       <c r="N19" s="1">
-        <v>2.0403009605557128e-05</v>
+        <v>2.0223157610882112e-05</v>
       </c>
       <c r="O19" s="1">
-        <v>-2.4734458422187117e-05</v>
+        <v>-2.4954763000967663e-05</v>
       </c>
       <c r="P19" s="1">
-        <v>-2.4318282387089813e-05</v>
+        <v>-2.4322676934378044e-05</v>
       </c>
       <c r="Q19" s="1">
-        <v>-1.6399181574662756e-05</v>
+        <v>-1.6461996538144522e-05</v>
       </c>
       <c r="R19" s="1">
-        <v>-2.5135524103097539e-05</v>
+        <v>-2.5223155362406316e-05</v>
       </c>
       <c r="S19" s="1">
-        <v>8.2673601611571933e-05</v>
+        <v>8.2743175737534866e-05</v>
       </c>
       <c r="T19" s="1">
-        <v>0.0013261681473998737</v>
+        <v>0.0013257634054158862</v>
       </c>
       <c r="U19" s="1">
-        <v>-0.00010095247709361356</v>
+        <v>-0.00010398965868986374</v>
       </c>
     </row>
     <row r="20">
@@ -6028,64 +6028,64 @@
         <v>43</v>
       </c>
       <c r="B20" s="1">
-        <v>-1.8115048098847559</v>
+        <v>-1.7994286435178206</v>
       </c>
       <c r="C20" s="1">
-        <v>-0.00056705828223935716</v>
+        <v>-0.00057285624541074116</v>
       </c>
       <c r="D20" s="1">
-        <v>5.0701967759764037e-06</v>
+        <v>5.1266081378157583e-06</v>
       </c>
       <c r="E20" s="1">
-        <v>-0.0048380791927874296</v>
+        <v>-0.0048505278507125667</v>
       </c>
       <c r="F20" s="1">
-        <v>-0.0051861372303744942</v>
+        <v>-0.0050655650189119494</v>
       </c>
       <c r="G20" s="1">
-        <v>9.9531573470728715e-05</v>
+        <v>9.9809500981720443e-05</v>
       </c>
       <c r="H20" s="1">
-        <v>0.00010408304776515641</v>
+        <v>0.00010192050702065635</v>
       </c>
       <c r="I20" s="1">
-        <v>0.0005407313485469628</v>
+        <v>0.00056111458660694025</v>
       </c>
       <c r="J20" s="1">
-        <v>-0.0023282943754771991</v>
+        <v>-0.0022474894764952604</v>
       </c>
       <c r="K20" s="1">
-        <v>-0.0067644243916794682</v>
+        <v>-0.006763056019630626</v>
       </c>
       <c r="L20" s="1">
-        <v>-0.0067763003828995418</v>
+        <v>-0.0067759956661537103</v>
       </c>
       <c r="M20" s="1">
-        <v>-0.0068859587546995296</v>
+        <v>-0.0068849386945654982</v>
       </c>
       <c r="N20" s="1">
-        <v>-0.0075056411170580546</v>
+        <v>-0.0075019358829996816</v>
       </c>
       <c r="O20" s="1">
-        <v>-0.0004330798949731891</v>
+        <v>-0.00042866249842238882</v>
       </c>
       <c r="P20" s="1">
-        <v>-0.00040618964473969105</v>
+        <v>-0.00040610525075488428</v>
       </c>
       <c r="Q20" s="1">
-        <v>-0.00037181810181122015</v>
+        <v>-0.00037222003268838936</v>
       </c>
       <c r="R20" s="1">
-        <v>-0.00041546688589019998</v>
+        <v>-0.00041485236180595711</v>
       </c>
       <c r="S20" s="1">
-        <v>-6.2946590844315859e-05</v>
+        <v>-6.5377898458079711e-05</v>
       </c>
       <c r="T20" s="1">
-        <v>-0.00010095247709361356</v>
+        <v>-0.00010398965868986374</v>
       </c>
       <c r="U20" s="1">
-        <v>0.021469279398265213</v>
+        <v>0.021591862231982527</v>
       </c>
     </row>
   </sheetData>
